--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122423935</v>
+        <v>122422959</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508980</v>
+        <v>508833</v>
       </c>
       <c r="R2" t="n">
-        <v>7008294</v>
+        <v>7008097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,11 +758,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424676</v>
+        <v>122422838</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -856,19 +846,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508779</v>
+        <v>508855</v>
       </c>
       <c r="R3" t="n">
-        <v>7008383</v>
+        <v>7008046</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +908,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,7 +949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429024</v>
+        <v>122423467</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -965,17 +985,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508746</v>
+        <v>508900</v>
       </c>
       <c r="R4" t="n">
-        <v>7008449</v>
+        <v>7008203</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1038,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1168,7 +1188,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122422838</v>
+        <v>122429239</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1204,7 +1224,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1214,17 +1234,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508855</v>
+        <v>508765</v>
       </c>
       <c r="R6" t="n">
-        <v>7008046</v>
+        <v>7008466</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,7 +1330,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122423588</v>
+        <v>122424308</v>
       </c>
       <c r="B7" t="n">
         <v>78646</v>
@@ -1350,13 +1370,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508975</v>
+        <v>508903</v>
       </c>
       <c r="R7" t="n">
-        <v>7008243</v>
+        <v>7008351</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,6 +1406,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122426582</v>
+        <v>122427444</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,44 +1478,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508771</v>
+        <v>508541</v>
       </c>
       <c r="R8" t="n">
-        <v>7008433</v>
+        <v>7008422</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1527,7 +1542,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,27 +1556,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122426947</v>
+        <v>122428725</v>
       </c>
       <c r="B9" t="n">
-        <v>56576</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,16 +1610,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1612,14 +1627,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1628,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508535</v>
+        <v>508919</v>
       </c>
       <c r="R9" t="n">
-        <v>7008440</v>
+        <v>7008295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,6 +1675,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,7 +1706,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122427763</v>
+        <v>122428937</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1735,13 +1751,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508776</v>
+        <v>508739</v>
       </c>
       <c r="R10" t="n">
-        <v>7008533</v>
+        <v>7008454</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1775,7 +1791,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,6 +1802,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1802,7 +1843,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429281</v>
+        <v>122424389</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1847,13 +1888,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509109</v>
+        <v>508892</v>
       </c>
       <c r="R11" t="n">
-        <v>7008253</v>
+        <v>7008349</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1887,7 +1928,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1939,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1914,7 +1980,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430628</v>
+        <v>122423808</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1959,10 +2025,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508965</v>
+        <v>508966</v>
       </c>
       <c r="R12" t="n">
-        <v>7008296</v>
+        <v>7008356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2026,10 +2092,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423988</v>
+        <v>122430040</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>57527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,34 +2108,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508982</v>
+        <v>508930</v>
       </c>
       <c r="R13" t="n">
-        <v>7008301</v>
+        <v>7008316</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2112,31 +2187,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2153,10 +2203,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122422959</v>
+        <v>122429949</v>
       </c>
       <c r="B14" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,39 +2219,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508833</v>
+        <v>508963</v>
       </c>
       <c r="R14" t="n">
-        <v>7008097</v>
+        <v>7008307</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,6 +2286,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2244,31 +2299,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2285,10 +2315,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122428118</v>
+        <v>122424453</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2301,37 +2331,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508595</v>
+        <v>508908</v>
       </c>
       <c r="R15" t="n">
-        <v>7008516</v>
+        <v>7008354</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2365,7 +2400,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,31 +2411,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2417,10 +2427,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122424308</v>
+        <v>122424707</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,37 +2443,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508903</v>
+        <v>508781</v>
       </c>
       <c r="R16" t="n">
-        <v>7008351</v>
+        <v>7008382</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2497,7 +2512,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,31 +2523,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,7 +2539,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122422848</v>
+        <v>122427586</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2590,14 +2580,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508847</v>
+        <v>508745</v>
       </c>
       <c r="R17" t="n">
-        <v>7008039</v>
+        <v>7008511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2661,7 +2651,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423191</v>
+        <v>122430904</v>
       </c>
       <c r="B18" t="n">
         <v>78646</v>
@@ -2701,13 +2691,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508859</v>
+        <v>508916</v>
       </c>
       <c r="R18" t="n">
-        <v>7008134</v>
+        <v>7008122</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2740,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2765,12 +2755,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2788,10 +2778,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429268</v>
+        <v>122423191</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,47 +2794,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508765</v>
+        <v>508859</v>
       </c>
       <c r="R19" t="n">
-        <v>7008461</v>
+        <v>7008134</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2876,11 +2856,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2892,7 +2867,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2907,12 +2882,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2930,7 +2905,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429949</v>
+        <v>122423133</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2966,22 +2941,27 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508963</v>
+        <v>508834</v>
       </c>
       <c r="R20" t="n">
-        <v>7008307</v>
+        <v>7008117</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3015,7 +2995,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3026,6 +3006,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3042,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122423711</v>
+        <v>122430628</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3058,34 +3063,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509001</v>
+        <v>508965</v>
       </c>
       <c r="R21" t="n">
-        <v>7008256</v>
+        <v>7008296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,6 +3130,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3128,31 +3143,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3169,7 +3159,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122428937</v>
+        <v>122426823</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -3214,13 +3204,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508739</v>
+        <v>508614</v>
       </c>
       <c r="R22" t="n">
-        <v>7008454</v>
+        <v>7008464</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3254,7 +3244,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3265,31 +3255,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3306,10 +3271,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122423467</v>
+        <v>122426947</v>
       </c>
       <c r="B23" t="n">
-        <v>78646</v>
+        <v>56576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3322,37 +3287,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508900</v>
+        <v>508535</v>
       </c>
       <c r="R23" t="n">
-        <v>7008203</v>
+        <v>7008440</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3392,31 +3366,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3433,10 +3382,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424637</v>
+        <v>122429607</v>
       </c>
       <c r="B24" t="n">
-        <v>78646</v>
+        <v>82433</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3449,21 +3398,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3473,10 +3422,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508814</v>
+        <v>509034</v>
       </c>
       <c r="R24" t="n">
-        <v>7008416</v>
+        <v>7008306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3519,31 +3468,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3560,7 +3484,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423040</v>
+        <v>122426951</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3599,24 +3523,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508845</v>
+        <v>508719</v>
       </c>
       <c r="R25" t="n">
-        <v>7008072</v>
+        <v>7008377</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3650,7 +3569,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,12 +3598,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3702,10 +3621,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122424611</v>
+        <v>122429398</v>
       </c>
       <c r="B26" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3718,39 +3637,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508820</v>
+        <v>508809</v>
       </c>
       <c r="R26" t="n">
-        <v>7008398</v>
+        <v>7008468</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3785,11 +3699,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3798,6 +3707,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3814,10 +3748,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122428831</v>
+        <v>122428777</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3830,39 +3764,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508914</v>
+        <v>508909</v>
       </c>
       <c r="R27" t="n">
-        <v>7008313</v>
+        <v>7008302</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3895,11 +3824,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3926,7 +3850,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423202</v>
+        <v>122423113</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3965,19 +3889,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508881</v>
+        <v>508834</v>
       </c>
       <c r="R28" t="n">
-        <v>7008130</v>
+        <v>7008115</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4011,7 +3940,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,6 +3951,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4038,10 +3992,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122424496</v>
+        <v>122424114</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4054,39 +4008,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508891</v>
+        <v>508968</v>
       </c>
       <c r="R29" t="n">
-        <v>7008386</v>
+        <v>7008319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4123,7 +4072,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,6 +4083,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4150,10 +4124,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122427629</v>
+        <v>122427127</v>
       </c>
       <c r="B30" t="n">
-        <v>97139</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4162,36 +4136,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4200,13 +4169,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508574</v>
+        <v>508631</v>
       </c>
       <c r="R30" t="n">
-        <v>7008461</v>
+        <v>7008480</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4238,6 +4207,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4246,11 +4220,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4267,7 +4236,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122427127</v>
+        <v>122423202</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -4308,14 +4277,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508631</v>
+        <v>508881</v>
       </c>
       <c r="R31" t="n">
-        <v>7008480</v>
+        <v>7008130</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4352,7 +4321,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4379,10 +4348,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122428777</v>
+        <v>122429553</v>
       </c>
       <c r="B32" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4395,34 +4364,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508909</v>
+        <v>509048</v>
       </c>
       <c r="R32" t="n">
-        <v>7008302</v>
+        <v>7008315</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4455,6 +4429,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4481,7 +4460,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429239</v>
+        <v>122428923</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4517,12 +4496,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4531,13 +4505,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508765</v>
+        <v>508978</v>
       </c>
       <c r="R33" t="n">
-        <v>7008466</v>
+        <v>7008270</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4571,7 +4545,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4582,31 +4556,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4623,7 +4572,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423524</v>
+        <v>122427681</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4664,14 +4613,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508928</v>
+        <v>508760</v>
       </c>
       <c r="R34" t="n">
-        <v>7008172</v>
+        <v>7008533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4708,7 +4657,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4735,10 +4684,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122423484</v>
+        <v>122424772</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4751,16 +4700,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4774,16 +4723,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508920</v>
+        <v>508770</v>
       </c>
       <c r="R35" t="n">
-        <v>7008181</v>
+        <v>7008381</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4820,7 +4774,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4831,6 +4785,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4847,10 +4826,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122428487</v>
+        <v>122426582</v>
       </c>
       <c r="B36" t="n">
-        <v>79763</v>
+        <v>57390</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4859,38 +4838,48 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509041</v>
+        <v>508771</v>
       </c>
       <c r="R36" t="n">
-        <v>7008337</v>
+        <v>7008433</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4925,6 +4914,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,6 +4927,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4949,10 +4968,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430040</v>
+        <v>122423988</v>
       </c>
       <c r="B37" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4965,43 +4984,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508930</v>
+        <v>508982</v>
       </c>
       <c r="R37" t="n">
-        <v>7008316</v>
+        <v>7008301</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5044,6 +5054,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5060,7 +5095,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423113</v>
+        <v>122424038</v>
       </c>
       <c r="B38" t="n">
         <v>57374</v>
@@ -5099,24 +5134,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508834</v>
+        <v>508954</v>
       </c>
       <c r="R38" t="n">
-        <v>7008115</v>
+        <v>7008336</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5150,7 +5180,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5161,31 +5191,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5202,7 +5207,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122426951</v>
+        <v>122429268</v>
       </c>
       <c r="B39" t="n">
         <v>57374</v>
@@ -5241,16 +5246,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508719</v>
+        <v>508765</v>
       </c>
       <c r="R39" t="n">
-        <v>7008377</v>
+        <v>7008461</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5287,7 +5297,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5316,12 +5326,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5339,10 +5349,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122424304</v>
+        <v>122428831</v>
       </c>
       <c r="B40" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5355,34 +5365,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508904</v>
+        <v>508914</v>
       </c>
       <c r="R40" t="n">
-        <v>7008325</v>
+        <v>7008313</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5415,6 +5430,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5441,7 +5461,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122424589</v>
+        <v>122423040</v>
       </c>
       <c r="B41" t="n">
         <v>57374</v>
@@ -5480,19 +5500,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508831</v>
+        <v>508845</v>
       </c>
       <c r="R41" t="n">
-        <v>7008397</v>
+        <v>7008072</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5526,7 +5551,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5537,6 +5562,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5553,7 +5603,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122427227</v>
+        <v>122426743</v>
       </c>
       <c r="B42" t="n">
         <v>78646</v>
@@ -5593,10 +5643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508639</v>
+        <v>508764</v>
       </c>
       <c r="R42" t="n">
-        <v>7008388</v>
+        <v>7008423</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5631,6 +5681,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5642,17 +5697,17 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5662,7 +5717,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5680,10 +5735,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427586</v>
+        <v>122423588</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5696,39 +5751,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508745</v>
+        <v>508975</v>
       </c>
       <c r="R43" t="n">
-        <v>7008511</v>
+        <v>7008243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,11 +5813,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5776,6 +5821,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5792,10 +5862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122429607</v>
+        <v>122423979</v>
       </c>
       <c r="B44" t="n">
-        <v>82433</v>
+        <v>57527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5808,34 +5878,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509034</v>
+        <v>508958</v>
       </c>
       <c r="R44" t="n">
-        <v>7008306</v>
+        <v>7008338</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5894,7 +5973,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122424453</v>
+        <v>122429281</v>
       </c>
       <c r="B45" t="n">
         <v>57374</v>
@@ -5939,10 +6018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508908</v>
+        <v>509109</v>
       </c>
       <c r="R45" t="n">
-        <v>7008354</v>
+        <v>7008253</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6006,10 +6085,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429553</v>
+        <v>122427227</v>
       </c>
       <c r="B46" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6022,39 +6101,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509048</v>
+        <v>508639</v>
       </c>
       <c r="R46" t="n">
-        <v>7008315</v>
+        <v>7008388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6089,11 +6163,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6102,6 +6171,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6118,10 +6212,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427444</v>
+        <v>122422848</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6134,34 +6228,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508541</v>
+        <v>508847</v>
       </c>
       <c r="R47" t="n">
-        <v>7008422</v>
+        <v>7008039</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6198,7 +6297,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6209,31 +6308,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6250,10 +6324,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122428462</v>
+        <v>122424126</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6266,34 +6340,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509040</v>
+        <v>508950</v>
       </c>
       <c r="R48" t="n">
-        <v>7008336</v>
+        <v>7008334</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6326,6 +6405,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6352,10 +6436,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122424126</v>
+        <v>122424328</v>
       </c>
       <c r="B49" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6368,39 +6452,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508950</v>
+        <v>508904</v>
       </c>
       <c r="R49" t="n">
-        <v>7008334</v>
+        <v>7008325</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6437,7 +6516,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6464,10 +6543,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122428923</v>
+        <v>122427142</v>
       </c>
       <c r="B50" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6480,39 +6559,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508978</v>
+        <v>508688</v>
       </c>
       <c r="R50" t="n">
-        <v>7008270</v>
+        <v>7008395</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6547,11 +6621,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6560,6 +6629,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6576,7 +6670,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122424038</v>
+        <v>122423811</v>
       </c>
       <c r="B51" t="n">
         <v>57374</v>
@@ -6615,16 +6709,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508954</v>
+        <v>508995</v>
       </c>
       <c r="R51" t="n">
-        <v>7008336</v>
+        <v>7008282</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6661,7 +6760,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6672,6 +6771,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6688,10 +6812,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122423979</v>
+        <v>122424637</v>
       </c>
       <c r="B52" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6704,43 +6828,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508958</v>
+        <v>508814</v>
       </c>
       <c r="R52" t="n">
-        <v>7008338</v>
+        <v>7008416</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6783,6 +6898,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6799,10 +6939,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122423626</v>
+        <v>122424676</v>
       </c>
       <c r="B53" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6815,36 +6955,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6853,10 +6984,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508994</v>
+        <v>508779</v>
       </c>
       <c r="R53" t="n">
-        <v>7008252</v>
+        <v>7008383</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6893,7 +7024,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6904,11 +7035,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6925,7 +7051,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122424389</v>
+        <v>122424589</v>
       </c>
       <c r="B54" t="n">
         <v>57374</v>
@@ -6970,13 +7096,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508892</v>
+        <v>508831</v>
       </c>
       <c r="R54" t="n">
-        <v>7008349</v>
+        <v>7008397</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7010,7 +7136,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7021,31 +7147,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7062,10 +7163,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122423811</v>
+        <v>122428487</v>
       </c>
       <c r="B55" t="n">
-        <v>57374</v>
+        <v>79763</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7074,48 +7175,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508995</v>
+        <v>509041</v>
       </c>
       <c r="R55" t="n">
-        <v>7008282</v>
+        <v>7008337</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7150,11 +7241,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7163,31 +7249,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7204,10 +7265,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122427681</v>
+        <v>122428118</v>
       </c>
       <c r="B56" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7220,42 +7281,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508760</v>
+        <v>508595</v>
       </c>
       <c r="R56" t="n">
-        <v>7008533</v>
+        <v>7008516</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7289,7 +7345,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7300,6 +7356,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7316,10 +7397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122428725</v>
+        <v>122423626</v>
       </c>
       <c r="B57" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7332,27 +7413,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7361,10 +7451,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508919</v>
+        <v>508994</v>
       </c>
       <c r="R57" t="n">
-        <v>7008295</v>
+        <v>7008252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7401,7 +7491,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7412,6 +7502,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7428,7 +7523,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424707</v>
+        <v>122423935</v>
       </c>
       <c r="B58" t="n">
         <v>57374</v>
@@ -7464,7 +7559,12 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7473,10 +7573,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508781</v>
+        <v>508980</v>
       </c>
       <c r="R58" t="n">
-        <v>7008382</v>
+        <v>7008294</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7513,7 +7613,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7524,6 +7624,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7540,10 +7665,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122429398</v>
+        <v>122424496</v>
       </c>
       <c r="B59" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7556,34 +7681,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508809</v>
+        <v>508891</v>
       </c>
       <c r="R59" t="n">
-        <v>7008468</v>
+        <v>7008386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7618,6 +7748,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7626,31 +7761,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7667,10 +7777,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122424772</v>
+        <v>122428462</v>
       </c>
       <c r="B60" t="n">
-        <v>57390</v>
+        <v>79727</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7683,44 +7793,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508770</v>
+        <v>509040</v>
       </c>
       <c r="R60" t="n">
-        <v>7008381</v>
+        <v>7008336</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7755,11 +7855,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7768,31 +7863,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7809,10 +7879,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122423808</v>
+        <v>122423287</v>
       </c>
       <c r="B61" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7825,42 +7895,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508966</v>
+        <v>508887</v>
       </c>
       <c r="R61" t="n">
-        <v>7008356</v>
+        <v>7008167</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7892,11 +7957,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7905,6 +7965,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7921,10 +8006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122423287</v>
+        <v>122429210</v>
       </c>
       <c r="B62" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7937,37 +8022,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508887</v>
+        <v>509071</v>
       </c>
       <c r="R62" t="n">
-        <v>7008167</v>
+        <v>7008310</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7999,6 +8084,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8007,31 +8097,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8048,10 +8113,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426743</v>
+        <v>122424611</v>
       </c>
       <c r="B63" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8064,34 +8129,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508764</v>
+        <v>508820</v>
       </c>
       <c r="R63" t="n">
-        <v>7008423</v>
+        <v>7008398</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8128,7 +8198,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8139,31 +8209,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8180,10 +8225,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427142</v>
+        <v>122427629</v>
       </c>
       <c r="B64" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8192,41 +8237,51 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508688</v>
+        <v>508574</v>
       </c>
       <c r="R64" t="n">
-        <v>7008395</v>
+        <v>7008461</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8270,26 +8325,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8307,7 +8342,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122426823</v>
+        <v>122427763</v>
       </c>
       <c r="B65" t="n">
         <v>57374</v>
@@ -8352,10 +8387,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508614</v>
+        <v>508776</v>
       </c>
       <c r="R65" t="n">
-        <v>7008464</v>
+        <v>7008533</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8419,10 +8454,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122429210</v>
+        <v>122423484</v>
       </c>
       <c r="B66" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8435,34 +8470,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509071</v>
+        <v>508920</v>
       </c>
       <c r="R66" t="n">
-        <v>7008310</v>
+        <v>7008181</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8499,7 +8539,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8526,10 +8566,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122424114</v>
+        <v>122423524</v>
       </c>
       <c r="B67" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8542,34 +8582,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508968</v>
+        <v>508928</v>
       </c>
       <c r="R67" t="n">
-        <v>7008319</v>
+        <v>7008172</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8606,7 +8651,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8617,31 +8662,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8658,10 +8678,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122423133</v>
+        <v>122423711</v>
       </c>
       <c r="B68" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8674,47 +8694,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508834</v>
+        <v>509001</v>
       </c>
       <c r="R68" t="n">
-        <v>7008117</v>
+        <v>7008256</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8746,11 +8756,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8777,12 +8782,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8800,7 +8805,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122430904</v>
+        <v>122429024</v>
       </c>
       <c r="B69" t="n">
         <v>78646</v>
@@ -8836,17 +8841,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508916</v>
+        <v>508746</v>
       </c>
       <c r="R69" t="n">
-        <v>7008122</v>
+        <v>7008449</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8904,12 +8909,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430707</v>
+        <v>122424308</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,42 +1092,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508959</v>
+        <v>508903</v>
       </c>
       <c r="R5" t="n">
-        <v>7008280</v>
+        <v>7008351</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1161,7 +1156,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,6 +1167,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1330,7 +1350,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122424308</v>
+        <v>122427444</v>
       </c>
       <c r="B7" t="n">
         <v>78646</v>
@@ -1370,13 +1390,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508903</v>
+        <v>508541</v>
       </c>
       <c r="R7" t="n">
-        <v>7008351</v>
+        <v>7008422</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,17 +1444,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1444,7 +1464,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,10 +1482,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427444</v>
+        <v>122428937</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,37 +1498,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508541</v>
+        <v>508739</v>
       </c>
       <c r="R8" t="n">
-        <v>7008422</v>
+        <v>7008454</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1567,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,27 +1581,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,7 +1619,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122428725</v>
+        <v>122424389</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1639,13 +1664,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508919</v>
+        <v>508892</v>
       </c>
       <c r="R9" t="n">
-        <v>7008295</v>
+        <v>7008349</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1704,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,6 +1715,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1706,10 +1756,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428937</v>
+        <v>122430904</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1722,42 +1772,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508739</v>
+        <v>508916</v>
       </c>
       <c r="R10" t="n">
-        <v>7008454</v>
+        <v>7008122</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1787,11 +1832,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,7 +1883,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122424389</v>
+        <v>122424707</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1879,7 +1919,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1888,13 +1928,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508892</v>
+        <v>508781</v>
       </c>
       <c r="R11" t="n">
-        <v>7008349</v>
+        <v>7008382</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1928,7 +1968,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,31 +1979,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1980,7 +1995,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423808</v>
+        <v>122427586</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -2025,10 +2040,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508966</v>
+        <v>508745</v>
       </c>
       <c r="R12" t="n">
-        <v>7008356</v>
+        <v>7008511</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,10 +2107,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122430040</v>
+        <v>122423191</v>
       </c>
       <c r="B13" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2108,46 +2123,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508930</v>
+        <v>508859</v>
       </c>
       <c r="R13" t="n">
-        <v>7008316</v>
+        <v>7008134</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2187,6 +2193,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2203,7 +2234,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429949</v>
+        <v>122423133</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2239,22 +2270,27 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508963</v>
+        <v>508834</v>
       </c>
       <c r="R14" t="n">
-        <v>7008307</v>
+        <v>7008117</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2288,7 +2324,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2299,6 +2335,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2315,7 +2376,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122424453</v>
+        <v>122426823</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2351,7 +2412,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2360,10 +2421,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508908</v>
+        <v>508614</v>
       </c>
       <c r="R15" t="n">
-        <v>7008354</v>
+        <v>7008464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2400,7 +2461,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2427,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122424707</v>
+        <v>122426947</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>56576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2443,16 +2504,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2460,10 +2521,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2472,10 +2537,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508781</v>
+        <v>508535</v>
       </c>
       <c r="R16" t="n">
-        <v>7008382</v>
+        <v>7008440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2508,11 +2573,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2539,7 +2599,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122427586</v>
+        <v>122426951</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2584,10 +2644,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508745</v>
+        <v>508719</v>
       </c>
       <c r="R17" t="n">
-        <v>7008511</v>
+        <v>7008377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2624,7 +2684,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2635,6 +2695,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2651,7 +2736,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122430904</v>
+        <v>122429398</v>
       </c>
       <c r="B18" t="n">
         <v>78646</v>
@@ -2687,14 +2772,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508916</v>
+        <v>508809</v>
       </c>
       <c r="R18" t="n">
-        <v>7008122</v>
+        <v>7008468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2755,12 +2840,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2778,10 +2863,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122423191</v>
+        <v>122423113</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2794,34 +2879,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508859</v>
+        <v>508834</v>
       </c>
       <c r="R19" t="n">
-        <v>7008134</v>
+        <v>7008115</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2856,6 +2951,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2867,7 +2967,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2882,12 +2982,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2905,10 +3005,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423133</v>
+        <v>122424114</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2921,47 +3021,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508834</v>
+        <v>508968</v>
       </c>
       <c r="R20" t="n">
-        <v>7008117</v>
+        <v>7008319</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,7 +3085,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3024,12 +3114,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3047,7 +3137,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122430628</v>
+        <v>122427127</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -3092,10 +3182,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508965</v>
+        <v>508631</v>
       </c>
       <c r="R21" t="n">
-        <v>7008296</v>
+        <v>7008480</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3132,7 +3222,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3159,7 +3249,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122426823</v>
+        <v>122427681</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -3195,7 +3285,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3204,10 +3294,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508614</v>
+        <v>508760</v>
       </c>
       <c r="R22" t="n">
-        <v>7008464</v>
+        <v>7008533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3244,7 +3334,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3271,10 +3361,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122426947</v>
+        <v>122429268</v>
       </c>
       <c r="B23" t="n">
-        <v>56576</v>
+        <v>57374</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3287,16 +3377,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3304,14 +3394,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3320,10 +3411,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508535</v>
+        <v>508765</v>
       </c>
       <c r="R23" t="n">
-        <v>7008440</v>
+        <v>7008461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3358,6 +3449,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3462,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3382,10 +3503,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122429607</v>
+        <v>122424772</v>
       </c>
       <c r="B24" t="n">
-        <v>82433</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3398,34 +3519,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509034</v>
+        <v>508770</v>
       </c>
       <c r="R24" t="n">
-        <v>7008306</v>
+        <v>7008381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3460,6 +3591,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3468,6 +3604,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3484,10 +3645,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122426951</v>
+        <v>122426582</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,16 +3661,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,16 +3684,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508719</v>
+        <v>508771</v>
       </c>
       <c r="R25" t="n">
-        <v>7008377</v>
+        <v>7008433</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3569,7 +3735,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3621,7 +3787,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429398</v>
+        <v>122423988</v>
       </c>
       <c r="B26" t="n">
         <v>78646</v>
@@ -3661,10 +3827,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508809</v>
+        <v>508982</v>
       </c>
       <c r="R26" t="n">
-        <v>7008468</v>
+        <v>7008301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,12 +3891,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3748,10 +3914,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122428777</v>
+        <v>122423040</v>
       </c>
       <c r="B27" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3764,37 +3930,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508909</v>
+        <v>508845</v>
       </c>
       <c r="R27" t="n">
-        <v>7008302</v>
+        <v>7008072</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3826,6 +4002,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3834,6 +4015,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3850,10 +4056,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423113</v>
+        <v>122426743</v>
       </c>
       <c r="B28" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3866,47 +4072,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508834</v>
+        <v>508764</v>
       </c>
       <c r="R28" t="n">
-        <v>7008115</v>
+        <v>7008423</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3940,7 +4136,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,12 +4165,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3992,7 +4188,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122424114</v>
+        <v>122423588</v>
       </c>
       <c r="B29" t="n">
         <v>78646</v>
@@ -4032,10 +4228,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508968</v>
+        <v>508975</v>
       </c>
       <c r="R29" t="n">
-        <v>7008319</v>
+        <v>7008243</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,11 +4264,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,10 +4315,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122427127</v>
+        <v>122427227</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4140,39 +4331,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508631</v>
+        <v>508639</v>
       </c>
       <c r="R30" t="n">
-        <v>7008480</v>
+        <v>7008388</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4207,11 +4393,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4220,6 +4401,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4236,7 +4442,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122423202</v>
+        <v>122429281</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -4277,14 +4483,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508881</v>
+        <v>509109</v>
       </c>
       <c r="R31" t="n">
-        <v>7008130</v>
+        <v>7008253</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4348,7 +4554,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122429553</v>
+        <v>122423811</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -4387,16 +4593,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509048</v>
+        <v>508995</v>
       </c>
       <c r="R32" t="n">
-        <v>7008315</v>
+        <v>7008282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4433,7 +4644,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4444,6 +4655,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4460,10 +4696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122428923</v>
+        <v>122427142</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4476,39 +4712,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508978</v>
+        <v>508688</v>
       </c>
       <c r="R33" t="n">
-        <v>7008270</v>
+        <v>7008395</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4543,11 +4774,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4556,6 +4782,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4572,10 +4823,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122427681</v>
+        <v>122424637</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4588,39 +4839,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508760</v>
+        <v>508814</v>
       </c>
       <c r="R34" t="n">
-        <v>7008533</v>
+        <v>7008416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4655,11 +4901,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +4909,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4684,10 +4950,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122424772</v>
+        <v>122424676</v>
       </c>
       <c r="B35" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4700,16 +4966,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4723,21 +4989,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508770</v>
+        <v>508779</v>
       </c>
       <c r="R35" t="n">
-        <v>7008381</v>
+        <v>7008383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4774,7 +5035,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4785,31 +5046,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4826,10 +5062,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122426582</v>
+        <v>122424589</v>
       </c>
       <c r="B36" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4842,16 +5078,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4865,21 +5101,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508771</v>
+        <v>508831</v>
       </c>
       <c r="R36" t="n">
-        <v>7008433</v>
+        <v>7008397</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4916,7 +5147,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4927,31 +5158,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4968,7 +5174,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122423988</v>
+        <v>122428118</v>
       </c>
       <c r="B37" t="n">
         <v>78646</v>
@@ -5008,13 +5214,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508982</v>
+        <v>508595</v>
       </c>
       <c r="R37" t="n">
-        <v>7008301</v>
+        <v>7008516</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5046,6 +5252,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5057,7 +5268,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5095,10 +5306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122424038</v>
+        <v>122423626</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5111,27 +5322,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5140,10 +5360,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508954</v>
+        <v>508994</v>
       </c>
       <c r="R38" t="n">
-        <v>7008336</v>
+        <v>7008252</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5180,7 +5400,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5191,6 +5411,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5207,7 +5432,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122429268</v>
+        <v>122423935</v>
       </c>
       <c r="B39" t="n">
         <v>57374</v>
@@ -5257,10 +5482,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508765</v>
+        <v>508980</v>
       </c>
       <c r="R39" t="n">
-        <v>7008461</v>
+        <v>7008294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5297,7 +5522,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5349,7 +5574,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122428831</v>
+        <v>122424496</v>
       </c>
       <c r="B40" t="n">
         <v>57374</v>
@@ -5394,10 +5619,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508914</v>
+        <v>508891</v>
       </c>
       <c r="R40" t="n">
-        <v>7008313</v>
+        <v>7008386</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5461,10 +5686,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122423040</v>
+        <v>122423287</v>
       </c>
       <c r="B41" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5477,47 +5702,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508845</v>
+        <v>508887</v>
       </c>
       <c r="R41" t="n">
-        <v>7008072</v>
+        <v>7008167</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5549,11 +5764,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5565,7 +5775,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5580,12 +5790,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5603,10 +5813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122426743</v>
+        <v>122424611</v>
       </c>
       <c r="B42" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5619,34 +5829,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508764</v>
+        <v>508820</v>
       </c>
       <c r="R42" t="n">
-        <v>7008423</v>
+        <v>7008398</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5683,7 +5898,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5694,31 +5909,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5735,10 +5925,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122423588</v>
+        <v>122427629</v>
       </c>
       <c r="B43" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5747,41 +5937,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508975</v>
+        <v>508574</v>
       </c>
       <c r="R43" t="n">
-        <v>7008243</v>
+        <v>7008461</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5824,27 +6024,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5862,10 +6042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423979</v>
+        <v>122427763</v>
       </c>
       <c r="B44" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5878,31 +6058,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5911,10 +6087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508958</v>
+        <v>508776</v>
       </c>
       <c r="R44" t="n">
-        <v>7008338</v>
+        <v>7008533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5947,6 +6123,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5973,10 +6154,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122429281</v>
+        <v>122423711</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5989,39 +6170,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509109</v>
+        <v>509001</v>
       </c>
       <c r="R45" t="n">
-        <v>7008253</v>
+        <v>7008256</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6056,11 +6232,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6069,6 +6240,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6085,7 +6281,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122427227</v>
+        <v>122429024</v>
       </c>
       <c r="B46" t="n">
         <v>78646</v>
@@ -6125,13 +6321,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508639</v>
+        <v>508746</v>
       </c>
       <c r="R46" t="n">
-        <v>7008388</v>
+        <v>7008449</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6174,17 +6370,17 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -6194,7 +6390,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6212,10 +6408,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122422848</v>
+        <v>122428462</v>
       </c>
       <c r="B47" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6228,39 +6424,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508847</v>
+        <v>509040</v>
       </c>
       <c r="R47" t="n">
-        <v>7008039</v>
+        <v>7008336</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6295,19 +6489,40 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6324,10 +6539,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122424126</v>
+        <v>122429949</v>
       </c>
       <c r="B48" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6358,21 +6573,24 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508950</v>
+        <v>508963</v>
       </c>
       <c r="R48" t="n">
-        <v>7008334</v>
+        <v>7008307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6409,7 +6627,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6420,6 +6638,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6436,10 +6679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122424328</v>
+        <v>122430040</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>57532</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6452,34 +6695,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508904</v>
+        <v>508930</v>
       </c>
       <c r="R49" t="n">
-        <v>7008325</v>
+        <v>7008316</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6514,11 +6773,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6527,6 +6781,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6543,10 +6802,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122427142</v>
+        <v>122424304</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6559,34 +6818,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508688</v>
+        <v>508904</v>
       </c>
       <c r="R50" t="n">
-        <v>7008395</v>
+        <v>7008325</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6627,32 +6893,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6670,10 +6937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122423811</v>
+        <v>122429210</v>
       </c>
       <c r="B51" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6686,44 +6953,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508995</v>
+        <v>509071</v>
       </c>
       <c r="R51" t="n">
-        <v>7008282</v>
+        <v>7008310</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6760,7 +7020,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6769,6 +7029,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6787,14 +7048,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6812,10 +7068,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122424637</v>
+        <v>122423484</v>
       </c>
       <c r="B52" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6828,34 +7084,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508814</v>
+        <v>508920</v>
       </c>
       <c r="R52" t="n">
-        <v>7008416</v>
+        <v>7008181</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6890,6 +7154,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6901,27 +7170,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6939,10 +7208,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122424676</v>
+        <v>122424126</v>
       </c>
       <c r="B53" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6973,21 +7242,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508779</v>
+        <v>508950</v>
       </c>
       <c r="R53" t="n">
-        <v>7008383</v>
+        <v>7008334</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7024,7 +7296,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7035,6 +7307,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7051,10 +7348,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122424589</v>
+        <v>122428725</v>
       </c>
       <c r="B54" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7085,21 +7382,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508831</v>
+        <v>508919</v>
       </c>
       <c r="R54" t="n">
-        <v>7008397</v>
+        <v>7008295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7136,7 +7436,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7147,6 +7447,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7166,7 +7491,7 @@
         <v>122428487</v>
       </c>
       <c r="B55" t="n">
-        <v>79763</v>
+        <v>79768</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7197,6 +7522,9 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
@@ -7247,8 +7575,34 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7265,10 +7619,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122428118</v>
+        <v>122424038</v>
       </c>
       <c r="B56" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7281,37 +7635,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508595</v>
+        <v>508954</v>
       </c>
       <c r="R56" t="n">
-        <v>7008516</v>
+        <v>7008336</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7345,7 +7707,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7359,7 +7721,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7374,12 +7736,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7397,10 +7759,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122423626</v>
+        <v>122423202</v>
       </c>
       <c r="B57" t="n">
-        <v>57527</v>
+        <v>57379</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7413,48 +7775,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508994</v>
+        <v>508881</v>
       </c>
       <c r="R57" t="n">
-        <v>7008252</v>
+        <v>7008130</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7491,7 +7847,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7506,6 +7862,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7523,10 +7899,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122423935</v>
+        <v>122428777</v>
       </c>
       <c r="B58" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7539,44 +7915,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508980</v>
+        <v>508909</v>
       </c>
       <c r="R58" t="n">
-        <v>7008294</v>
+        <v>7008302</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7611,17 +7984,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7632,22 +8001,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7665,10 +8034,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424496</v>
+        <v>122424453</v>
       </c>
       <c r="B59" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7699,21 +8068,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508891</v>
+        <v>508908</v>
       </c>
       <c r="R59" t="n">
-        <v>7008386</v>
+        <v>7008354</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7750,7 +8122,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7761,6 +8133,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7777,10 +8174,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428462</v>
+        <v>122428831</v>
       </c>
       <c r="B60" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7793,34 +8190,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>509040</v>
+        <v>508914</v>
       </c>
       <c r="R60" t="n">
-        <v>7008336</v>
+        <v>7008313</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7855,6 +8260,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7863,6 +8273,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7879,10 +8314,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122423287</v>
+        <v>122429553</v>
       </c>
       <c r="B61" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7895,37 +8330,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508887</v>
+        <v>509048</v>
       </c>
       <c r="R61" t="n">
-        <v>7008167</v>
+        <v>7008315</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7957,6 +8400,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7968,7 +8416,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -7983,12 +8431,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8006,10 +8454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122429210</v>
+        <v>122423524</v>
       </c>
       <c r="B62" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8022,34 +8470,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>509071</v>
+        <v>508928</v>
       </c>
       <c r="R62" t="n">
-        <v>7008310</v>
+        <v>7008172</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8086,7 +8542,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8097,6 +8553,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8113,10 +8594,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424611</v>
+        <v>122423979</v>
       </c>
       <c r="B63" t="n">
-        <v>57374</v>
+        <v>57532</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8129,27 +8610,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8158,10 +8650,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508820</v>
+        <v>508958</v>
       </c>
       <c r="R63" t="n">
-        <v>7008398</v>
+        <v>7008338</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8196,11 +8688,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8209,6 +8696,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8225,10 +8717,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427629</v>
+        <v>122429607</v>
       </c>
       <c r="B64" t="n">
-        <v>97139</v>
+        <v>82438</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8237,51 +8729,44 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508574</v>
+        <v>509034</v>
       </c>
       <c r="R64" t="n">
-        <v>7008461</v>
+        <v>7008306</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8319,12 +8804,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8342,10 +8843,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427763</v>
+        <v>122430707</v>
       </c>
       <c r="B65" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,21 +8877,24 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508776</v>
+        <v>508959</v>
       </c>
       <c r="R65" t="n">
-        <v>7008533</v>
+        <v>7008280</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8427,7 +8931,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8438,6 +8942,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8454,10 +8983,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122423484</v>
+        <v>122423808</v>
       </c>
       <c r="B66" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8488,21 +9017,24 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508920</v>
+        <v>508966</v>
       </c>
       <c r="R66" t="n">
-        <v>7008181</v>
+        <v>7008356</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8539,7 +9071,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8550,6 +9082,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8566,10 +9123,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122423524</v>
+        <v>122422848</v>
       </c>
       <c r="B67" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8600,21 +9157,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508928</v>
+        <v>508847</v>
       </c>
       <c r="R67" t="n">
-        <v>7008172</v>
+        <v>7008039</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8651,7 +9211,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8662,6 +9222,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8678,10 +9263,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122423711</v>
+        <v>122430628</v>
       </c>
       <c r="B68" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8694,34 +9279,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509001</v>
+        <v>508965</v>
       </c>
       <c r="R68" t="n">
-        <v>7008256</v>
+        <v>7008296</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8756,6 +9349,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8782,12 +9380,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8805,10 +9403,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122429024</v>
+        <v>122428923</v>
       </c>
       <c r="B69" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8821,37 +9419,45 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508746</v>
+        <v>508978</v>
       </c>
       <c r="R69" t="n">
-        <v>7008449</v>
+        <v>7008270</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8883,6 +9489,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8909,12 +9520,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122422959</v>
+        <v>122423811</v>
       </c>
       <c r="B2" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508833</v>
+        <v>508995</v>
       </c>
       <c r="R2" t="n">
-        <v>7008097</v>
+        <v>7008282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +763,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -784,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122422838</v>
+        <v>122423040</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -857,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508855</v>
+        <v>508845</v>
       </c>
       <c r="R3" t="n">
-        <v>7008046</v>
+        <v>7008072</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +907,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -949,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122423467</v>
+        <v>122424611</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,37 +975,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508900</v>
+        <v>508820</v>
       </c>
       <c r="R4" t="n">
-        <v>7008203</v>
+        <v>7008398</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,6 +1042,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1035,31 +1055,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1076,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122424308</v>
+        <v>122427227</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1116,13 +1111,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508903</v>
+        <v>508639</v>
       </c>
       <c r="R5" t="n">
-        <v>7008351</v>
+        <v>7008388</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,11 +1149,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,17 +1160,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1190,7 +1180,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1208,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429239</v>
+        <v>122428118</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,47 +1214,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508765</v>
+        <v>508595</v>
       </c>
       <c r="R6" t="n">
-        <v>7008466</v>
+        <v>7008516</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,7 +1292,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1327,12 +1307,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427444</v>
+        <v>122423626</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,34 +1346,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508541</v>
+        <v>508994</v>
       </c>
       <c r="R7" t="n">
-        <v>7008422</v>
+        <v>7008252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1424,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,27 +1438,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1482,10 +1456,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122428937</v>
+        <v>122424308</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,42 +1472,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508739</v>
+        <v>508903</v>
       </c>
       <c r="R8" t="n">
-        <v>7008454</v>
+        <v>7008351</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1567,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,12 +1565,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1619,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122424389</v>
+        <v>122426823</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1655,7 +1624,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1664,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508892</v>
+        <v>508614</v>
       </c>
       <c r="R9" t="n">
-        <v>7008349</v>
+        <v>7008464</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1704,7 +1673,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,31 +1684,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1756,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430904</v>
+        <v>122423133</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1772,37 +1716,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508916</v>
+        <v>508834</v>
       </c>
       <c r="R10" t="n">
-        <v>7008122</v>
+        <v>7008117</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1832,6 +1786,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1883,10 +1842,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122424707</v>
+        <v>122429398</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1899,39 +1858,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508781</v>
+        <v>508809</v>
       </c>
       <c r="R11" t="n">
-        <v>7008382</v>
+        <v>7008468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1966,11 +1920,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1979,6 +1928,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1995,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427586</v>
+        <v>122423467</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2011,42 +1985,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508745</v>
+        <v>508900</v>
       </c>
       <c r="R12" t="n">
-        <v>7008511</v>
+        <v>7008203</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2078,11 +2047,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2091,6 +2055,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2107,10 +2096,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423191</v>
+        <v>122424637</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2143,17 +2132,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508859</v>
+        <v>508814</v>
       </c>
       <c r="R13" t="n">
-        <v>7008134</v>
+        <v>7008416</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2196,7 +2185,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2211,12 +2200,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2234,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423133</v>
+        <v>122426743</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2250,47 +2239,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508834</v>
+        <v>508764</v>
       </c>
       <c r="R14" t="n">
-        <v>7008117</v>
+        <v>7008423</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2324,7 +2303,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2353,12 +2332,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2376,10 +2355,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122426823</v>
+        <v>122429281</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2412,7 +2391,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2421,10 +2400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508614</v>
+        <v>509109</v>
       </c>
       <c r="R15" t="n">
-        <v>7008464</v>
+        <v>7008253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2461,7 +2440,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2488,10 +2467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122426947</v>
+        <v>122429239</v>
       </c>
       <c r="B16" t="n">
-        <v>56576</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2504,16 +2483,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2521,14 +2500,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2537,13 +2517,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508535</v>
+        <v>508765</v>
       </c>
       <c r="R16" t="n">
-        <v>7008440</v>
+        <v>7008466</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2575,6 +2555,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack främst på stambasen.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2583,6 +2568,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2599,10 +2609,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426951</v>
+        <v>122422838</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2638,19 +2648,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508719</v>
+        <v>508855</v>
       </c>
       <c r="R17" t="n">
-        <v>7008377</v>
+        <v>7008046</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2684,7 +2699,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2713,12 +2728,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2736,10 +2751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429398</v>
+        <v>122427681</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2752,34 +2767,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508809</v>
+        <v>508760</v>
       </c>
       <c r="R18" t="n">
-        <v>7008468</v>
+        <v>7008533</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2814,6 +2834,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2822,31 +2847,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2863,10 +2863,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122423113</v>
+        <v>122424676</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2902,24 +2902,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508834</v>
+        <v>508779</v>
       </c>
       <c r="R19" t="n">
-        <v>7008115</v>
+        <v>7008383</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2964,31 +2959,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3005,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122424114</v>
+        <v>122429268</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3021,34 +2991,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508968</v>
+        <v>508765</v>
       </c>
       <c r="R20" t="n">
-        <v>7008319</v>
+        <v>7008461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3085,7 +3065,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3114,12 +3094,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3137,10 +3117,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427127</v>
+        <v>122427444</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3153,39 +3133,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508631</v>
+        <v>508541</v>
       </c>
       <c r="R21" t="n">
-        <v>7008480</v>
+        <v>7008422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3222,7 +3197,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3233,6 +3208,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427681</v>
+        <v>122422959</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>90819</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,39 +3265,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508760</v>
+        <v>508833</v>
       </c>
       <c r="R22" t="n">
-        <v>7008533</v>
+        <v>7008097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,11 +3332,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3345,6 +3340,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3361,10 +3381,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122429268</v>
+        <v>122426947</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>56581</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3377,16 +3397,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3394,15 +3414,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3411,10 +3430,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508765</v>
+        <v>508535</v>
       </c>
       <c r="R23" t="n">
-        <v>7008461</v>
+        <v>7008440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3449,11 +3468,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3462,31 +3476,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3503,10 +3492,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424772</v>
+        <v>122427142</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3519,44 +3508,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508770</v>
+        <v>508688</v>
       </c>
       <c r="R24" t="n">
-        <v>7008381</v>
+        <v>7008395</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3591,11 +3570,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3607,7 +3581,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3622,12 +3596,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3645,10 +3619,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122426582</v>
+        <v>122424389</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3661,16 +3635,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3684,24 +3658,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508771</v>
+        <v>508892</v>
       </c>
       <c r="R25" t="n">
-        <v>7008433</v>
+        <v>7008349</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3735,7 +3704,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3764,12 +3733,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3787,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423988</v>
+        <v>122427586</v>
       </c>
       <c r="B26" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3803,34 +3772,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508982</v>
+        <v>508745</v>
       </c>
       <c r="R26" t="n">
-        <v>7008301</v>
+        <v>7008511</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3865,6 +3839,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3873,31 +3852,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3914,10 +3868,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423040</v>
+        <v>122424589</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3953,24 +3907,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508845</v>
+        <v>508831</v>
       </c>
       <c r="R27" t="n">
-        <v>7008072</v>
+        <v>7008397</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4004,7 +3953,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,31 +3964,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4056,10 +3980,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122426743</v>
+        <v>122423711</v>
       </c>
       <c r="B28" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4096,10 +4020,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508764</v>
+        <v>509001</v>
       </c>
       <c r="R28" t="n">
-        <v>7008423</v>
+        <v>7008256</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4132,11 +4056,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4191,7 +4110,7 @@
         <v>122423588</v>
       </c>
       <c r="B29" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4315,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122427227</v>
+        <v>122424707</v>
       </c>
       <c r="B30" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4331,34 +4250,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508639</v>
+        <v>508781</v>
       </c>
       <c r="R30" t="n">
-        <v>7008388</v>
+        <v>7008382</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4393,6 +4317,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4401,31 +4330,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4442,10 +4346,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122429281</v>
+        <v>122426582</v>
       </c>
       <c r="B31" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4458,16 +4362,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4481,16 +4385,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509109</v>
+        <v>508771</v>
       </c>
       <c r="R31" t="n">
-        <v>7008253</v>
+        <v>7008433</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4527,7 +4436,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4538,6 +4447,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4554,10 +4488,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423811</v>
+        <v>122430904</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4570,44 +4504,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508995</v>
+        <v>508916</v>
       </c>
       <c r="R32" t="n">
-        <v>7008282</v>
+        <v>7008122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4640,11 +4564,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4696,10 +4615,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122427142</v>
+        <v>122423988</v>
       </c>
       <c r="B33" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4736,10 +4655,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508688</v>
+        <v>508982</v>
       </c>
       <c r="R33" t="n">
-        <v>7008395</v>
+        <v>7008301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4785,7 +4704,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4800,12 +4719,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4823,10 +4742,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122424637</v>
+        <v>122427127</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4839,34 +4758,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508814</v>
+        <v>508631</v>
       </c>
       <c r="R34" t="n">
-        <v>7008416</v>
+        <v>7008480</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4901,6 +4825,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4909,31 +4838,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4950,10 +4854,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122424676</v>
+        <v>122429024</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4966,42 +4870,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508779</v>
+        <v>508746</v>
       </c>
       <c r="R35" t="n">
-        <v>7008383</v>
+        <v>7008449</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5033,11 +4932,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5046,6 +4940,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5062,10 +4981,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424589</v>
+        <v>122424772</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5078,16 +4997,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5101,16 +5020,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508831</v>
+        <v>508770</v>
       </c>
       <c r="R36" t="n">
-        <v>7008397</v>
+        <v>7008381</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5147,7 +5071,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5158,6 +5082,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5174,10 +5123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122428118</v>
+        <v>122423935</v>
       </c>
       <c r="B37" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5190,37 +5139,47 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508595</v>
+        <v>508980</v>
       </c>
       <c r="R37" t="n">
-        <v>7008516</v>
+        <v>7008294</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5254,7 +5213,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5268,7 +5227,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5283,12 +5242,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5306,10 +5265,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423626</v>
+        <v>122424114</v>
       </c>
       <c r="B38" t="n">
-        <v>57527</v>
+        <v>78651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5322,48 +5281,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508994</v>
+        <v>508968</v>
       </c>
       <c r="R38" t="n">
-        <v>7008252</v>
+        <v>7008319</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5400,7 +5345,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5415,6 +5360,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5432,10 +5397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122423935</v>
+        <v>122427763</v>
       </c>
       <c r="B39" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5468,12 +5433,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5482,10 +5442,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508980</v>
+        <v>508776</v>
       </c>
       <c r="R39" t="n">
-        <v>7008294</v>
+        <v>7008533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5522,7 +5482,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5533,31 +5493,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5574,10 +5509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122424496</v>
+        <v>122426951</v>
       </c>
       <c r="B40" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5619,10 +5554,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508891</v>
+        <v>508719</v>
       </c>
       <c r="R40" t="n">
-        <v>7008386</v>
+        <v>7008377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5659,7 +5594,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5670,6 +5605,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5686,10 +5646,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122423287</v>
+        <v>122423191</v>
       </c>
       <c r="B41" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5726,13 +5686,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508887</v>
+        <v>508859</v>
       </c>
       <c r="R41" t="n">
-        <v>7008167</v>
+        <v>7008134</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5790,12 +5750,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5813,10 +5773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122424611</v>
+        <v>122423287</v>
       </c>
       <c r="B42" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5829,42 +5789,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508820</v>
+        <v>508887</v>
       </c>
       <c r="R42" t="n">
-        <v>7008398</v>
+        <v>7008167</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5896,11 +5851,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5909,6 +5859,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5928,7 +5903,7 @@
         <v>122427629</v>
       </c>
       <c r="B43" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6042,10 +6017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427763</v>
+        <v>122423113</v>
       </c>
       <c r="B44" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6078,22 +6053,27 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508776</v>
+        <v>508834</v>
       </c>
       <c r="R44" t="n">
-        <v>7008533</v>
+        <v>7008115</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6127,7 +6107,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6138,6 +6118,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6154,10 +6159,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122423711</v>
+        <v>122424496</v>
       </c>
       <c r="B45" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6170,34 +6175,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509001</v>
+        <v>508891</v>
       </c>
       <c r="R45" t="n">
-        <v>7008256</v>
+        <v>7008386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6232,6 +6242,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6240,31 +6255,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6281,10 +6271,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429024</v>
+        <v>122428937</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6297,37 +6287,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508746</v>
+        <v>508739</v>
       </c>
       <c r="R46" t="n">
-        <v>7008449</v>
+        <v>7008454</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6359,6 +6354,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6408,10 +6408,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428462</v>
+        <v>122429949</v>
       </c>
       <c r="B47" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6424,26 +6424,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6451,10 +6456,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509040</v>
+        <v>508963</v>
       </c>
       <c r="R47" t="n">
-        <v>7008336</v>
+        <v>7008307</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6489,13 +6494,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6506,22 +6515,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6539,7 +6548,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122429949</v>
+        <v>122423524</v>
       </c>
       <c r="B48" t="n">
         <v>57379</v>
@@ -6583,14 +6592,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508963</v>
+        <v>508928</v>
       </c>
       <c r="R48" t="n">
-        <v>7008307</v>
+        <v>7008172</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6627,7 +6636,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6641,17 +6650,17 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -6661,7 +6670,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6679,10 +6688,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430040</v>
+        <v>122424453</v>
       </c>
       <c r="B49" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6695,50 +6704,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508930</v>
+        <v>508908</v>
       </c>
       <c r="R49" t="n">
-        <v>7008316</v>
+        <v>7008354</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6773,6 +6774,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6785,6 +6791,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6802,10 +6828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122424304</v>
+        <v>122429553</v>
       </c>
       <c r="B50" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6818,28 +6844,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6849,10 +6876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508904</v>
+        <v>509048</v>
       </c>
       <c r="R50" t="n">
-        <v>7008325</v>
+        <v>7008315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6887,13 +6914,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6904,22 +6935,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6937,7 +6968,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122429210</v>
+        <v>122428462</v>
       </c>
       <c r="B51" t="n">
         <v>79732</v>
@@ -6980,10 +7011,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509071</v>
+        <v>509040</v>
       </c>
       <c r="R51" t="n">
-        <v>7008310</v>
+        <v>7008336</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7018,11 +7049,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7040,17 +7066,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7068,10 +7099,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122423484</v>
+        <v>122429210</v>
       </c>
       <c r="B52" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7084,42 +7115,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508920</v>
+        <v>509071</v>
       </c>
       <c r="R52" t="n">
-        <v>7008181</v>
+        <v>7008310</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7156,7 +7182,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7165,32 +7191,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7208,10 +7230,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122424126</v>
+        <v>122423979</v>
       </c>
       <c r="B53" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7224,42 +7246,50 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508950</v>
+        <v>508958</v>
       </c>
       <c r="R53" t="n">
-        <v>7008334</v>
+        <v>7008338</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7294,11 +7324,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7311,26 +7336,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7348,10 +7353,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428725</v>
+        <v>122428487</v>
       </c>
       <c r="B54" t="n">
-        <v>57379</v>
+        <v>79768</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7360,35 +7365,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508919</v>
+        <v>509041</v>
       </c>
       <c r="R54" t="n">
-        <v>7008295</v>
+        <v>7008337</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7434,17 +7434,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7455,22 +7451,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7488,10 +7484,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428487</v>
+        <v>122430707</v>
       </c>
       <c r="B55" t="n">
-        <v>79768</v>
+        <v>57379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7500,30 +7496,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7531,10 +7532,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509041</v>
+        <v>508959</v>
       </c>
       <c r="R55" t="n">
-        <v>7008337</v>
+        <v>7008280</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7569,13 +7570,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7586,22 +7591,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7619,7 +7624,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122424038</v>
+        <v>122428831</v>
       </c>
       <c r="B56" t="n">
         <v>57379</v>
@@ -7667,10 +7672,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508954</v>
+        <v>508914</v>
       </c>
       <c r="R56" t="n">
-        <v>7008336</v>
+        <v>7008313</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7759,7 +7764,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122423202</v>
+        <v>122424038</v>
       </c>
       <c r="B57" t="n">
         <v>57379</v>
@@ -7803,14 +7808,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508881</v>
+        <v>508954</v>
       </c>
       <c r="R57" t="n">
-        <v>7008130</v>
+        <v>7008336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7899,10 +7904,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122428777</v>
+        <v>122429607</v>
       </c>
       <c r="B58" t="n">
-        <v>79732</v>
+        <v>82438</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7915,30 +7920,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7946,10 +7947,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508909</v>
+        <v>509034</v>
       </c>
       <c r="R58" t="n">
-        <v>7008302</v>
+        <v>7008306</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8001,22 +8002,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8034,7 +8030,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424453</v>
+        <v>122423202</v>
       </c>
       <c r="B59" t="n">
         <v>57379</v>
@@ -8078,14 +8074,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508908</v>
+        <v>508881</v>
       </c>
       <c r="R59" t="n">
-        <v>7008354</v>
+        <v>7008130</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8174,7 +8170,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428831</v>
+        <v>122423484</v>
       </c>
       <c r="B60" t="n">
         <v>57379</v>
@@ -8218,14 +8214,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508914</v>
+        <v>508920</v>
       </c>
       <c r="R60" t="n">
-        <v>7008313</v>
+        <v>7008181</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8262,7 +8258,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8276,17 +8272,17 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -8296,7 +8292,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8314,7 +8310,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122429553</v>
+        <v>122430628</v>
       </c>
       <c r="B61" t="n">
         <v>57379</v>
@@ -8362,10 +8358,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>509048</v>
+        <v>508965</v>
       </c>
       <c r="R61" t="n">
-        <v>7008315</v>
+        <v>7008296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8454,10 +8450,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122423524</v>
+        <v>122424304</v>
       </c>
       <c r="B62" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8470,42 +8466,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508928</v>
+        <v>508904</v>
       </c>
       <c r="R62" t="n">
-        <v>7008172</v>
+        <v>7008325</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8540,43 +8535,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8594,10 +8585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122423979</v>
+        <v>122428725</v>
       </c>
       <c r="B63" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8610,50 +8601,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508958</v>
+        <v>508919</v>
       </c>
       <c r="R63" t="n">
-        <v>7008338</v>
+        <v>7008295</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8688,6 +8671,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8700,6 +8688,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8717,10 +8725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122429607</v>
+        <v>122430040</v>
       </c>
       <c r="B64" t="n">
-        <v>82438</v>
+        <v>57532</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8733,37 +8741,50 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509034</v>
+        <v>508930</v>
       </c>
       <c r="R64" t="n">
-        <v>7008306</v>
+        <v>7008316</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8804,28 +8825,12 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8843,7 +8848,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122430707</v>
+        <v>122428923</v>
       </c>
       <c r="B65" t="n">
         <v>57379</v>
@@ -8891,10 +8896,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508959</v>
+        <v>508978</v>
       </c>
       <c r="R65" t="n">
-        <v>7008280</v>
+        <v>7008270</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9263,7 +9268,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122430628</v>
+        <v>122424126</v>
       </c>
       <c r="B68" t="n">
         <v>57379</v>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508965</v>
+        <v>508950</v>
       </c>
       <c r="R68" t="n">
-        <v>7008296</v>
+        <v>7008334</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9403,10 +9408,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428923</v>
+        <v>122428777</v>
       </c>
       <c r="B69" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9419,29 +9424,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9451,10 +9455,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508978</v>
+        <v>508909</v>
       </c>
       <c r="R69" t="n">
-        <v>7008270</v>
+        <v>7008302</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9489,17 +9493,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9510,22 +9510,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122423811</v>
+        <v>122424676</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -714,21 +714,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508995</v>
+        <v>508779</v>
       </c>
       <c r="R2" t="n">
-        <v>7008282</v>
+        <v>7008383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122423040</v>
+        <v>122423191</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,47 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508845</v>
+        <v>508859</v>
       </c>
       <c r="R3" t="n">
-        <v>7008072</v>
+        <v>7008134</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,11 +865,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -921,7 +876,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -936,12 +891,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424611</v>
+        <v>122426823</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -995,7 +950,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1004,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508820</v>
+        <v>508614</v>
       </c>
       <c r="R4" t="n">
-        <v>7008398</v>
+        <v>7008464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1044,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427227</v>
+        <v>122424114</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1111,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508639</v>
+        <v>508968</v>
       </c>
       <c r="R5" t="n">
-        <v>7008388</v>
+        <v>7008319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,6 +1104,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1160,17 +1120,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1180,7 +1140,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122428118</v>
+        <v>122426947</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>56581</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,37 +1174,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508595</v>
+        <v>508535</v>
       </c>
       <c r="R6" t="n">
-        <v>7008516</v>
+        <v>7008440</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,11 +1245,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1289,31 +1253,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1330,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122423626</v>
+        <v>122424611</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,36 +1285,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1384,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508994</v>
+        <v>508820</v>
       </c>
       <c r="R7" t="n">
-        <v>7008252</v>
+        <v>7008398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,11 +1365,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1456,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122424308</v>
+        <v>122422838</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,37 +1397,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508903</v>
+        <v>508855</v>
       </c>
       <c r="R8" t="n">
-        <v>7008351</v>
+        <v>7008046</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1536,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,12 +1500,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1588,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122426823</v>
+        <v>122423588</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1604,39 +1539,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508614</v>
+        <v>508975</v>
       </c>
       <c r="R9" t="n">
-        <v>7008464</v>
+        <v>7008243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1671,11 +1601,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1684,6 +1609,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1700,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423133</v>
+        <v>122423467</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,44 +1666,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508834</v>
+        <v>508900</v>
       </c>
       <c r="R10" t="n">
-        <v>7008117</v>
+        <v>7008203</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1788,11 +1728,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1804,7 +1739,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1819,12 +1754,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1842,7 +1777,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429398</v>
+        <v>122427444</v>
       </c>
       <c r="B11" t="n">
         <v>78651</v>
@@ -1882,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508809</v>
+        <v>508541</v>
       </c>
       <c r="R11" t="n">
-        <v>7008468</v>
+        <v>7008422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1920,6 +1855,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1931,27 +1871,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423467</v>
+        <v>122426582</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,37 +1925,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508900</v>
+        <v>508771</v>
       </c>
       <c r="R12" t="n">
-        <v>7008203</v>
+        <v>7008433</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,6 +1997,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2013,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2073,12 +2028,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2096,7 +2051,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122424637</v>
+        <v>122423711</v>
       </c>
       <c r="B13" t="n">
         <v>78651</v>
@@ -2136,10 +2091,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508814</v>
+        <v>509001</v>
       </c>
       <c r="R13" t="n">
-        <v>7008416</v>
+        <v>7008256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2223,7 +2178,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122426743</v>
+        <v>122427142</v>
       </c>
       <c r="B14" t="n">
         <v>78651</v>
@@ -2263,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508764</v>
+        <v>508688</v>
       </c>
       <c r="R14" t="n">
-        <v>7008423</v>
+        <v>7008395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2301,11 +2256,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2317,7 +2267,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2332,12 +2282,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2355,10 +2305,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122429281</v>
+        <v>122422959</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>90826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2371,39 +2321,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509109</v>
+        <v>508833</v>
       </c>
       <c r="R15" t="n">
-        <v>7008253</v>
+        <v>7008097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,11 +2388,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2451,6 +2396,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2467,7 +2437,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122429239</v>
+        <v>122427586</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2503,12 +2473,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2517,13 +2482,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508765</v>
+        <v>508745</v>
       </c>
       <c r="R16" t="n">
-        <v>7008466</v>
+        <v>7008511</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2557,7 +2522,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2568,31 +2533,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2609,7 +2549,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122422838</v>
+        <v>122426951</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2648,24 +2588,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508855</v>
+        <v>508719</v>
       </c>
       <c r="R17" t="n">
-        <v>7008046</v>
+        <v>7008377</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2699,7 +2634,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2728,12 +2663,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2751,10 +2686,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122427681</v>
+        <v>122426743</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2767,39 +2702,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508760</v>
+        <v>508764</v>
       </c>
       <c r="R18" t="n">
-        <v>7008533</v>
+        <v>7008423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2836,7 +2766,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2847,6 +2777,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2863,7 +2818,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122424676</v>
+        <v>122423040</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2902,19 +2857,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508779</v>
+        <v>508845</v>
       </c>
       <c r="R19" t="n">
-        <v>7008383</v>
+        <v>7008072</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2948,7 +2908,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2959,6 +2919,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2975,10 +2960,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429268</v>
+        <v>122428118</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2991,47 +2976,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508765</v>
+        <v>508595</v>
       </c>
       <c r="R20" t="n">
-        <v>7008461</v>
+        <v>7008516</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3065,7 +3040,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3079,7 +3054,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3094,12 +3069,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3117,10 +3092,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427444</v>
+        <v>122427681</v>
       </c>
       <c r="B21" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3133,34 +3108,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508541</v>
+        <v>508760</v>
       </c>
       <c r="R21" t="n">
-        <v>7008422</v>
+        <v>7008533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3197,7 +3177,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3208,31 +3188,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3249,10 +3204,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122422959</v>
+        <v>122427763</v>
       </c>
       <c r="B22" t="n">
-        <v>90819</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,39 +3220,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508833</v>
+        <v>508776</v>
       </c>
       <c r="R22" t="n">
-        <v>7008097</v>
+        <v>7008533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3332,6 +3287,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3340,31 +3300,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3381,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122426947</v>
+        <v>122423935</v>
       </c>
       <c r="B23" t="n">
-        <v>56581</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3397,16 +3332,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3414,14 +3349,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3430,10 +3366,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508535</v>
+        <v>508980</v>
       </c>
       <c r="R23" t="n">
-        <v>7008440</v>
+        <v>7008294</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3468,6 +3404,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3476,6 +3417,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3492,10 +3458,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427142</v>
+        <v>122424707</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3508,34 +3474,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508688</v>
+        <v>508781</v>
       </c>
       <c r="R24" t="n">
-        <v>7008395</v>
+        <v>7008382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3570,6 +3541,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3578,31 +3554,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3619,10 +3570,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122424389</v>
+        <v>122424637</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3635,42 +3586,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508892</v>
+        <v>508814</v>
       </c>
       <c r="R25" t="n">
-        <v>7008349</v>
+        <v>7008416</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3702,11 +3648,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3733,12 +3674,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3756,10 +3697,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122427586</v>
+        <v>122427629</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>97156</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3768,31 +3709,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3801,13 +3747,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508745</v>
+        <v>508574</v>
       </c>
       <c r="R26" t="n">
-        <v>7008511</v>
+        <v>7008461</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3839,11 +3785,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3852,6 +3793,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3868,7 +3814,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122424589</v>
+        <v>122424389</v>
       </c>
       <c r="B27" t="n">
         <v>57379</v>
@@ -3913,13 +3859,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508831</v>
+        <v>508892</v>
       </c>
       <c r="R27" t="n">
-        <v>7008397</v>
+        <v>7008349</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3953,7 +3899,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3964,6 +3910,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3980,10 +3951,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423711</v>
+        <v>122423133</v>
       </c>
       <c r="B28" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3996,37 +3967,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509001</v>
+        <v>508834</v>
       </c>
       <c r="R28" t="n">
-        <v>7008256</v>
+        <v>7008117</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4058,6 +4039,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4084,12 +4070,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,10 +4093,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423588</v>
+        <v>122428937</v>
       </c>
       <c r="B29" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4123,37 +4109,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508975</v>
+        <v>508739</v>
       </c>
       <c r="R29" t="n">
-        <v>7008243</v>
+        <v>7008454</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4185,6 +4176,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4211,12 +4207,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4234,10 +4230,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122424707</v>
+        <v>122429398</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4250,39 +4246,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508781</v>
+        <v>508809</v>
       </c>
       <c r="R30" t="n">
-        <v>7008382</v>
+        <v>7008468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4317,11 +4308,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4330,6 +4316,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4346,10 +4357,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122426582</v>
+        <v>122424496</v>
       </c>
       <c r="B31" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4362,16 +4373,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4385,21 +4396,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508771</v>
+        <v>508891</v>
       </c>
       <c r="R31" t="n">
-        <v>7008433</v>
+        <v>7008386</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4436,7 +4442,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4447,31 +4453,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4488,10 +4469,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122430904</v>
+        <v>122429281</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4504,34 +4485,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508916</v>
+        <v>509109</v>
       </c>
       <c r="R32" t="n">
-        <v>7008122</v>
+        <v>7008253</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4566,6 +4552,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4574,31 +4565,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4742,7 +4708,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122427127</v>
+        <v>122423811</v>
       </c>
       <c r="B34" t="n">
         <v>57379</v>
@@ -4781,16 +4747,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508631</v>
+        <v>508995</v>
       </c>
       <c r="R34" t="n">
-        <v>7008480</v>
+        <v>7008282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4827,7 +4798,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4838,6 +4809,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4854,10 +4850,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122429024</v>
+        <v>122424589</v>
       </c>
       <c r="B35" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4870,37 +4866,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508746</v>
+        <v>508831</v>
       </c>
       <c r="R35" t="n">
-        <v>7008449</v>
+        <v>7008397</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4932,6 +4933,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4940,31 +4946,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4981,10 +4962,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424772</v>
+        <v>122427227</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4997,44 +4978,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508770</v>
+        <v>508639</v>
       </c>
       <c r="R36" t="n">
-        <v>7008381</v>
+        <v>7008388</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5069,11 +5040,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5085,27 +5051,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5123,10 +5089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122423935</v>
+        <v>122424308</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5139,47 +5105,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508980</v>
+        <v>508903</v>
       </c>
       <c r="R37" t="n">
-        <v>7008294</v>
+        <v>7008351</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5213,7 +5169,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5242,12 +5198,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5265,10 +5221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122424114</v>
+        <v>122423626</v>
       </c>
       <c r="B38" t="n">
-        <v>78651</v>
+        <v>57532</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5281,34 +5237,48 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508968</v>
+        <v>508994</v>
       </c>
       <c r="R38" t="n">
-        <v>7008319</v>
+        <v>7008252</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5345,7 +5315,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5360,26 +5330,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5397,10 +5347,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122427763</v>
+        <v>122430904</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5413,39 +5363,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508776</v>
+        <v>508916</v>
       </c>
       <c r="R39" t="n">
-        <v>7008533</v>
+        <v>7008122</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5480,11 +5425,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5493,6 +5433,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5509,10 +5474,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122426951</v>
+        <v>122424772</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5525,16 +5490,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5548,16 +5513,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508719</v>
+        <v>508770</v>
       </c>
       <c r="R40" t="n">
-        <v>7008377</v>
+        <v>7008381</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5594,7 +5564,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5623,12 +5593,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5646,10 +5616,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122423191</v>
+        <v>122427127</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5662,37 +5632,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508859</v>
+        <v>508631</v>
       </c>
       <c r="R41" t="n">
-        <v>7008134</v>
+        <v>7008480</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5724,6 +5699,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5732,31 +5712,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5773,10 +5728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122423287</v>
+        <v>122429268</v>
       </c>
       <c r="B42" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5789,37 +5744,47 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508887</v>
+        <v>508765</v>
       </c>
       <c r="R42" t="n">
-        <v>7008167</v>
+        <v>7008461</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5851,6 +5816,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5862,7 +5832,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5877,12 +5847,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5900,10 +5870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427629</v>
+        <v>122423113</v>
       </c>
       <c r="B43" t="n">
-        <v>97151</v>
+        <v>57379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5912,31 +5882,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5946,14 +5916,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508574</v>
+        <v>508834</v>
       </c>
       <c r="R43" t="n">
-        <v>7008461</v>
+        <v>7008115</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -5988,6 +5958,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5999,7 +5974,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6017,10 +6012,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423113</v>
+        <v>122429024</v>
       </c>
       <c r="B44" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6033,47 +6028,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508834</v>
+        <v>508746</v>
       </c>
       <c r="R44" t="n">
-        <v>7008115</v>
+        <v>7008449</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6105,11 +6090,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6136,12 +6116,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6159,10 +6139,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122424496</v>
+        <v>122423287</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6175,42 +6155,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508891</v>
+        <v>508887</v>
       </c>
       <c r="R45" t="n">
-        <v>7008386</v>
+        <v>7008167</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6242,11 +6217,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6255,6 +6225,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6271,7 +6266,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428937</v>
+        <v>122429239</v>
       </c>
       <c r="B46" t="n">
         <v>57379</v>
@@ -6310,19 +6305,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508739</v>
+        <v>508765</v>
       </c>
       <c r="R46" t="n">
-        <v>7008454</v>
+        <v>7008466</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6408,7 +6408,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429949</v>
+        <v>122423524</v>
       </c>
       <c r="B47" t="n">
         <v>57379</v>
@@ -6452,14 +6452,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508963</v>
+        <v>508928</v>
       </c>
       <c r="R47" t="n">
-        <v>7008307</v>
+        <v>7008172</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6510,17 +6510,17 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122423524</v>
+        <v>122428487</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>79768</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6560,46 +6560,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508928</v>
+        <v>509041</v>
       </c>
       <c r="R48" t="n">
-        <v>7008172</v>
+        <v>7008337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6634,43 +6629,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6688,7 +6679,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122424453</v>
+        <v>122428831</v>
       </c>
       <c r="B49" t="n">
         <v>57379</v>
@@ -6736,10 +6727,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508908</v>
+        <v>508914</v>
       </c>
       <c r="R49" t="n">
-        <v>7008354</v>
+        <v>7008313</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6828,10 +6819,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429553</v>
+        <v>122430040</v>
       </c>
       <c r="B50" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6844,42 +6835,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>509048</v>
+        <v>508930</v>
       </c>
       <c r="R50" t="n">
-        <v>7008315</v>
+        <v>7008316</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6914,11 +6913,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6931,26 +6925,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6968,10 +6942,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428462</v>
+        <v>122423808</v>
       </c>
       <c r="B51" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6984,26 +6958,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7011,10 +6990,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509040</v>
+        <v>508966</v>
       </c>
       <c r="R51" t="n">
-        <v>7008336</v>
+        <v>7008356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7049,13 +7028,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7066,22 +7049,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7099,10 +7082,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122429210</v>
+        <v>122423979</v>
       </c>
       <c r="B52" t="n">
-        <v>79732</v>
+        <v>57532</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7115,37 +7098,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>509071</v>
+        <v>508958</v>
       </c>
       <c r="R52" t="n">
-        <v>7008310</v>
+        <v>7008338</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7180,39 +7176,18 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7230,10 +7205,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122423979</v>
+        <v>122430707</v>
       </c>
       <c r="B53" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7246,50 +7221,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508958</v>
+        <v>508959</v>
       </c>
       <c r="R53" t="n">
-        <v>7008338</v>
+        <v>7008280</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7324,6 +7291,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7336,6 +7308,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7353,10 +7345,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428487</v>
+        <v>122428725</v>
       </c>
       <c r="B54" t="n">
-        <v>79768</v>
+        <v>57379</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7365,30 +7357,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7396,10 +7393,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509041</v>
+        <v>508919</v>
       </c>
       <c r="R54" t="n">
-        <v>7008337</v>
+        <v>7008295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7434,13 +7431,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7451,22 +7452,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7484,7 +7485,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122430707</v>
+        <v>122428923</v>
       </c>
       <c r="B55" t="n">
         <v>57379</v>
@@ -7532,10 +7533,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508959</v>
+        <v>508978</v>
       </c>
       <c r="R55" t="n">
-        <v>7008280</v>
+        <v>7008270</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7624,7 +7625,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122428831</v>
+        <v>122424126</v>
       </c>
       <c r="B56" t="n">
         <v>57379</v>
@@ -7672,10 +7673,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508914</v>
+        <v>508950</v>
       </c>
       <c r="R56" t="n">
-        <v>7008313</v>
+        <v>7008334</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7764,7 +7765,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122424038</v>
+        <v>122423484</v>
       </c>
       <c r="B57" t="n">
         <v>57379</v>
@@ -7808,14 +7809,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508954</v>
+        <v>508920</v>
       </c>
       <c r="R57" t="n">
-        <v>7008336</v>
+        <v>7008181</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7852,7 +7853,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7866,17 +7867,17 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -7886,7 +7887,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7904,10 +7905,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122429607</v>
+        <v>122429553</v>
       </c>
       <c r="B58" t="n">
-        <v>82438</v>
+        <v>57379</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7920,26 +7921,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7947,10 +7953,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509034</v>
+        <v>509048</v>
       </c>
       <c r="R58" t="n">
-        <v>7008306</v>
+        <v>7008315</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7985,13 +7991,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8010,9 +8020,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8030,10 +8045,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122423202</v>
+        <v>122428777</v>
       </c>
       <c r="B59" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8046,42 +8061,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508881</v>
+        <v>508909</v>
       </c>
       <c r="R59" t="n">
-        <v>7008130</v>
+        <v>7008302</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8116,17 +8130,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8137,22 +8147,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8170,7 +8180,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122423484</v>
+        <v>122423202</v>
       </c>
       <c r="B60" t="n">
         <v>57379</v>
@@ -8218,10 +8228,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508920</v>
+        <v>508881</v>
       </c>
       <c r="R60" t="n">
-        <v>7008181</v>
+        <v>7008130</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8258,7 +8268,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8272,17 +8282,17 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -8292,7 +8302,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8310,7 +8320,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122430628</v>
+        <v>122424453</v>
       </c>
       <c r="B61" t="n">
         <v>57379</v>
@@ -8358,10 +8368,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508965</v>
+        <v>508908</v>
       </c>
       <c r="R61" t="n">
-        <v>7008296</v>
+        <v>7008354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8450,10 +8460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424304</v>
+        <v>122429607</v>
       </c>
       <c r="B62" t="n">
-        <v>79732</v>
+        <v>82438</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8466,30 +8476,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8497,10 +8503,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508904</v>
+        <v>509034</v>
       </c>
       <c r="R62" t="n">
-        <v>7008325</v>
+        <v>7008306</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8552,22 +8558,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8585,7 +8586,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122428725</v>
+        <v>122429949</v>
       </c>
       <c r="B63" t="n">
         <v>57379</v>
@@ -8633,10 +8634,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508919</v>
+        <v>508963</v>
       </c>
       <c r="R63" t="n">
-        <v>7008295</v>
+        <v>7008307</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8725,10 +8726,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122430040</v>
+        <v>122428462</v>
       </c>
       <c r="B64" t="n">
-        <v>57532</v>
+        <v>79732</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8741,50 +8742,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508930</v>
+        <v>509040</v>
       </c>
       <c r="R64" t="n">
-        <v>7008316</v>
+        <v>7008336</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8825,12 +8813,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8848,10 +8857,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122428923</v>
+        <v>122424328</v>
       </c>
       <c r="B65" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8864,31 +8873,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8896,10 +8900,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508978</v>
+        <v>508904</v>
       </c>
       <c r="R65" t="n">
-        <v>7008270</v>
+        <v>7008325</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8936,7 +8940,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8945,6 +8949,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8963,14 +8968,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8988,7 +8988,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122423808</v>
+        <v>122424038</v>
       </c>
       <c r="B66" t="n">
         <v>57379</v>
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508966</v>
+        <v>508954</v>
       </c>
       <c r="R66" t="n">
-        <v>7008356</v>
+        <v>7008336</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9128,10 +9128,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122422848</v>
+        <v>122429210</v>
       </c>
       <c r="B67" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9144,42 +9144,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508847</v>
+        <v>509071</v>
       </c>
       <c r="R67" t="n">
-        <v>7008039</v>
+        <v>7008310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9216,7 +9211,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9225,6 +9220,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9243,14 +9239,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9268,7 +9259,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424126</v>
+        <v>122422848</v>
       </c>
       <c r="B68" t="n">
         <v>57379</v>
@@ -9312,14 +9303,14 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508950</v>
+        <v>508847</v>
       </c>
       <c r="R68" t="n">
-        <v>7008334</v>
+        <v>7008039</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9408,10 +9399,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428777</v>
+        <v>122430628</v>
       </c>
       <c r="B69" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9424,28 +9415,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9455,10 +9447,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508909</v>
+        <v>508965</v>
       </c>
       <c r="R69" t="n">
-        <v>7008302</v>
+        <v>7008296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9493,13 +9485,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9510,22 +9506,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122424611</v>
+        <v>122426582</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,16 +1285,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1308,16 +1308,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508820</v>
+        <v>508771</v>
       </c>
       <c r="R7" t="n">
-        <v>7008398</v>
+        <v>7008433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,6 +1370,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1381,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122422838</v>
+        <v>122424611</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1420,24 +1450,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508855</v>
+        <v>508820</v>
       </c>
       <c r="R8" t="n">
-        <v>7008046</v>
+        <v>7008398</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1496,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,31 +1507,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423588</v>
+        <v>122422838</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,37 +1539,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508975</v>
+        <v>508855</v>
       </c>
       <c r="R9" t="n">
-        <v>7008243</v>
+        <v>7008046</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,6 +1611,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1627,12 +1642,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1650,7 +1665,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423467</v>
+        <v>122423588</v>
       </c>
       <c r="B10" t="n">
         <v>78651</v>
@@ -1686,17 +1701,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508900</v>
+        <v>508975</v>
       </c>
       <c r="R10" t="n">
-        <v>7008203</v>
+        <v>7008243</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,7 +1754,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1777,7 +1792,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122427444</v>
+        <v>122423467</v>
       </c>
       <c r="B11" t="n">
         <v>78651</v>
@@ -1813,17 +1828,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508541</v>
+        <v>508900</v>
       </c>
       <c r="R11" t="n">
-        <v>7008422</v>
+        <v>7008203</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,11 +1870,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1871,17 +1881,17 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -1891,7 +1901,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122426582</v>
+        <v>122427444</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1925,44 +1935,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508771</v>
+        <v>508541</v>
       </c>
       <c r="R12" t="n">
-        <v>7008433</v>
+        <v>7008422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,27 +2013,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430904</v>
+        <v>122424772</v>
       </c>
       <c r="B39" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5363,34 +5363,44 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508916</v>
+        <v>508770</v>
       </c>
       <c r="R39" t="n">
-        <v>7008122</v>
+        <v>7008381</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5423,6 +5433,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5474,10 +5489,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122424772</v>
+        <v>122430904</v>
       </c>
       <c r="B40" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5490,44 +5505,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508770</v>
+        <v>508916</v>
       </c>
       <c r="R40" t="n">
-        <v>7008381</v>
+        <v>7008122</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5560,11 +5565,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122426582</v>
+        <v>122424611</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,16 +1285,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1308,21 +1308,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508771</v>
+        <v>508820</v>
       </c>
       <c r="R7" t="n">
-        <v>7008433</v>
+        <v>7008398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,31 +1365,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122424611</v>
+        <v>122422838</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1450,19 +1420,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508820</v>
+        <v>508855</v>
       </c>
       <c r="R8" t="n">
-        <v>7008398</v>
+        <v>7008046</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,6 +1482,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122422838</v>
+        <v>122423588</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,47 +1539,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508855</v>
+        <v>508975</v>
       </c>
       <c r="R9" t="n">
-        <v>7008046</v>
+        <v>7008243</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,11 +1601,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1642,12 +1627,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1665,7 +1650,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423588</v>
+        <v>122423467</v>
       </c>
       <c r="B10" t="n">
         <v>78651</v>
@@ -1701,17 +1686,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508975</v>
+        <v>508900</v>
       </c>
       <c r="R10" t="n">
-        <v>7008243</v>
+        <v>7008203</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1754,7 +1739,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1777,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122423467</v>
+        <v>122427444</v>
       </c>
       <c r="B11" t="n">
         <v>78651</v>
@@ -1828,17 +1813,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508900</v>
+        <v>508541</v>
       </c>
       <c r="R11" t="n">
-        <v>7008203</v>
+        <v>7008422</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1870,6 +1855,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1881,17 +1871,17 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -1901,7 +1891,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1919,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427444</v>
+        <v>122426582</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,34 +1925,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508541</v>
+        <v>508771</v>
       </c>
       <c r="R12" t="n">
-        <v>7008422</v>
+        <v>7008433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,27 +2013,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122423040</v>
+        <v>122428118</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2834,47 +2834,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508845</v>
+        <v>508595</v>
       </c>
       <c r="R19" t="n">
-        <v>7008072</v>
+        <v>7008516</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2908,7 +2898,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,7 +2912,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2937,12 +2927,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2960,10 +2950,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122428118</v>
+        <v>122423040</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2976,37 +2966,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508595</v>
+        <v>508845</v>
       </c>
       <c r="R20" t="n">
-        <v>7008516</v>
+        <v>7008072</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122424676</v>
+        <v>122426582</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,16 +709,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508779</v>
+        <v>508771</v>
       </c>
       <c r="R2" t="n">
-        <v>7008383</v>
+        <v>7008433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +771,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122423191</v>
+        <v>122424389</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +823,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508859</v>
+        <v>508892</v>
       </c>
       <c r="R3" t="n">
-        <v>7008134</v>
+        <v>7008349</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,6 +885,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,12 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -891,12 +911,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122426823</v>
+        <v>122423588</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +950,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508614</v>
+        <v>508975</v>
       </c>
       <c r="R4" t="n">
-        <v>7008464</v>
+        <v>7008243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +1007,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1015,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1026,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122424114</v>
+        <v>122424308</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,11 +1069,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1066,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508968</v>
+        <v>508903</v>
       </c>
       <c r="R5" t="n">
-        <v>7008319</v>
+        <v>7008351</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,11 +1141,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1158,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122426947</v>
+        <v>122429398</v>
       </c>
       <c r="B6" t="n">
-        <v>56581</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,43 +1189,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508535</v>
+        <v>508809</v>
       </c>
       <c r="R6" t="n">
-        <v>7008440</v>
+        <v>7008468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,6 +1254,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1269,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122424611</v>
+        <v>122427586</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1287,11 +1308,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1314,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508820</v>
+        <v>508745</v>
       </c>
       <c r="R7" t="n">
-        <v>7008398</v>
+        <v>7008511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122422838</v>
+        <v>122426823</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1399,11 +1415,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1417,27 +1428,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508855</v>
+        <v>508614</v>
       </c>
       <c r="R8" t="n">
-        <v>7008046</v>
+        <v>7008464</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1477,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,31 +1488,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1523,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423588</v>
+        <v>122427681</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,34 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508975</v>
+        <v>508760</v>
       </c>
       <c r="R9" t="n">
-        <v>7008243</v>
+        <v>7008533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,6 +1582,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1609,31 +1595,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1650,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423467</v>
+        <v>122426947</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>56581</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,37 +1627,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508900</v>
+        <v>508535</v>
       </c>
       <c r="R10" t="n">
-        <v>7008203</v>
+        <v>7008440</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,31 +1701,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1777,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122427444</v>
+        <v>122424114</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,11 +1735,6 @@
       <c r="E11" t="n">
         <v>6425</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1817,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508541</v>
+        <v>508968</v>
       </c>
       <c r="R11" t="n">
-        <v>7008422</v>
+        <v>7008319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1871,17 +1806,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -1891,7 +1821,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1909,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122426582</v>
+        <v>122428118</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1925,47 +1855,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508771</v>
+        <v>508595</v>
       </c>
       <c r="R12" t="n">
-        <v>7008433</v>
+        <v>7008516</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1999,7 +1914,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,12 +1928,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2028,12 +1938,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2051,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423711</v>
+        <v>122424676</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2067,34 +1977,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509001</v>
+        <v>508779</v>
       </c>
       <c r="R13" t="n">
-        <v>7008256</v>
+        <v>7008383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,6 +2039,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2137,31 +2052,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2178,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122427142</v>
+        <v>122423113</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2194,37 +2084,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508688</v>
+        <v>508834</v>
       </c>
       <c r="R14" t="n">
-        <v>7008395</v>
+        <v>7008115</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2256,6 +2151,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2267,12 +2167,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2282,12 +2177,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2305,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122422959</v>
+        <v>122423040</v>
       </c>
       <c r="B15" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2321,27 +2216,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2350,13 +2245,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508833</v>
+        <v>508845</v>
       </c>
       <c r="R15" t="n">
-        <v>7008097</v>
+        <v>7008072</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2388,6 +2283,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2399,12 +2299,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2414,12 +2309,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2437,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122427586</v>
+        <v>122423811</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2455,11 +2350,6 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2476,16 +2366,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508745</v>
+        <v>508995</v>
       </c>
       <c r="R16" t="n">
-        <v>7008511</v>
+        <v>7008282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2522,7 +2417,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2533,6 +2428,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2549,7 +2464,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426951</v>
+        <v>122424707</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2567,11 +2482,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2585,7 +2495,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2594,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508719</v>
+        <v>508781</v>
       </c>
       <c r="R17" t="n">
-        <v>7008377</v>
+        <v>7008382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2634,7 +2544,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,31 +2555,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2686,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122426743</v>
+        <v>122423711</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2704,11 +2589,6 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2726,10 +2606,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508764</v>
+        <v>509001</v>
       </c>
       <c r="R18" t="n">
-        <v>7008423</v>
+        <v>7008256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2764,11 +2644,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2781,11 +2656,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2818,10 +2688,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122428118</v>
+        <v>122429024</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2836,11 +2706,6 @@
       <c r="E19" t="n">
         <v>6425</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2858,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508595</v>
+        <v>508746</v>
       </c>
       <c r="R19" t="n">
-        <v>7008516</v>
+        <v>7008449</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2896,11 +2761,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2912,12 +2772,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -2950,10 +2805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423040</v>
+        <v>122423191</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2966,47 +2821,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508845</v>
+        <v>508859</v>
       </c>
       <c r="R20" t="n">
-        <v>7008072</v>
+        <v>7008134</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3038,11 +2878,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3054,12 +2889,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3069,12 +2899,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3092,7 +2922,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427681</v>
+        <v>122428937</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -3110,11 +2940,6 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3128,7 +2953,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3137,13 +2962,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508760</v>
+        <v>508739</v>
       </c>
       <c r="R21" t="n">
-        <v>7008533</v>
+        <v>7008454</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3177,7 +3002,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3188,6 +3013,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3204,7 +3049,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427763</v>
+        <v>122429239</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -3222,11 +3067,6 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3243,19 +3083,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508776</v>
+        <v>508765</v>
       </c>
       <c r="R22" t="n">
-        <v>7008533</v>
+        <v>7008466</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3289,7 +3134,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3300,6 +3145,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3334,11 +3199,6 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3421,11 +3281,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3458,10 +3313,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424707</v>
+        <v>122423988</v>
       </c>
       <c r="B24" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3474,39 +3329,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508781</v>
+        <v>508982</v>
       </c>
       <c r="R24" t="n">
-        <v>7008382</v>
+        <v>7008301</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3541,11 +3386,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3554,6 +3394,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3570,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122424637</v>
+        <v>122424496</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3586,34 +3446,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508814</v>
+        <v>508891</v>
       </c>
       <c r="R25" t="n">
-        <v>7008416</v>
+        <v>7008386</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3648,6 +3508,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3656,31 +3521,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3697,10 +3537,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122427629</v>
+        <v>122424611</v>
       </c>
       <c r="B26" t="n">
-        <v>97156</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3709,36 +3549,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3747,13 +3577,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508574</v>
+        <v>508820</v>
       </c>
       <c r="R26" t="n">
-        <v>7008461</v>
+        <v>7008398</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3785,6 +3615,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3793,11 +3628,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3814,7 +3644,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122424389</v>
+        <v>122423133</v>
       </c>
       <c r="B27" t="n">
         <v>57379</v>
@@ -3832,11 +3662,6 @@
       <c r="E27" t="n">
         <v>100109</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3850,22 +3675,27 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508892</v>
+        <v>508834</v>
       </c>
       <c r="R27" t="n">
-        <v>7008349</v>
+        <v>7008117</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3899,7 +3729,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3914,11 +3744,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -3951,10 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423133</v>
+        <v>122423626</v>
       </c>
       <c r="B28" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3967,27 +3792,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3997,17 +3821,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508834</v>
+        <v>508994</v>
       </c>
       <c r="R28" t="n">
-        <v>7008117</v>
+        <v>7008252</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4041,7 +3865,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4056,26 +3880,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4093,7 +3897,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122428937</v>
+        <v>122424589</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -4111,11 +3915,6 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4129,7 +3928,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4138,13 +3937,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508739</v>
+        <v>508831</v>
       </c>
       <c r="R29" t="n">
-        <v>7008454</v>
+        <v>7008397</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4178,7 +3977,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4189,31 +3988,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4230,10 +4004,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122429398</v>
+        <v>122422959</v>
       </c>
       <c r="B30" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4246,34 +4020,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508809</v>
+        <v>508833</v>
       </c>
       <c r="R30" t="n">
-        <v>7008468</v>
+        <v>7008097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4319,12 +4093,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4334,12 +4103,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4357,10 +4126,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122424496</v>
+        <v>122427227</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4373,39 +4142,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508891</v>
+        <v>508639</v>
       </c>
       <c r="R31" t="n">
-        <v>7008386</v>
+        <v>7008388</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4440,11 +4199,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4453,6 +4207,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4469,7 +4243,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122429281</v>
+        <v>122427127</v>
       </c>
       <c r="B32" t="n">
         <v>57379</v>
@@ -4487,11 +4261,6 @@
       <c r="E32" t="n">
         <v>100109</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4514,10 +4283,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509109</v>
+        <v>508631</v>
       </c>
       <c r="R32" t="n">
-        <v>7008253</v>
+        <v>7008480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4554,7 +4323,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4581,10 +4350,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122423988</v>
+        <v>122429281</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4597,34 +4366,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508982</v>
+        <v>509109</v>
       </c>
       <c r="R33" t="n">
-        <v>7008301</v>
+        <v>7008253</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4659,6 +4428,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4667,31 +4441,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4708,10 +4457,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423811</v>
+        <v>122423467</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4724,47 +4473,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508995</v>
+        <v>508900</v>
       </c>
       <c r="R34" t="n">
-        <v>7008282</v>
+        <v>7008203</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4796,11 +4530,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4812,12 +4541,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -4827,12 +4551,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4850,7 +4574,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122424589</v>
+        <v>122426951</v>
       </c>
       <c r="B35" t="n">
         <v>57379</v>
@@ -4868,11 +4592,6 @@
       <c r="E35" t="n">
         <v>100109</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4895,10 +4614,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508831</v>
+        <v>508719</v>
       </c>
       <c r="R35" t="n">
-        <v>7008397</v>
+        <v>7008377</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4935,7 +4654,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4946,6 +4665,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4962,10 +4701,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122427227</v>
+        <v>122427629</v>
       </c>
       <c r="B36" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4974,41 +4713,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508639</v>
+        <v>508574</v>
       </c>
       <c r="R36" t="n">
-        <v>7008388</v>
+        <v>7008461</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5052,26 +4796,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5089,10 +4813,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122424308</v>
+        <v>122427142</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5107,11 +4831,6 @@
       <c r="E37" t="n">
         <v>6425</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5129,13 +4848,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508903</v>
+        <v>508688</v>
       </c>
       <c r="R37" t="n">
-        <v>7008351</v>
+        <v>7008395</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5167,11 +4886,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5183,12 +4897,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5198,12 +4907,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5221,10 +4930,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423626</v>
+        <v>122423287</v>
       </c>
       <c r="B38" t="n">
-        <v>57532</v>
+        <v>78652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5237,51 +4946,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508994</v>
+        <v>508887</v>
       </c>
       <c r="R38" t="n">
-        <v>7008252</v>
+        <v>7008167</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5313,11 +5003,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst två individer, möjligen fler.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5329,7 +5014,22 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5347,10 +5047,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122424772</v>
+        <v>122424637</v>
       </c>
       <c r="B39" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5363,44 +5063,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508770</v>
+        <v>508814</v>
       </c>
       <c r="R39" t="n">
-        <v>7008381</v>
+        <v>7008416</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5435,11 +5120,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5454,11 +5134,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK39" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5466,12 +5141,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5489,10 +5164,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430904</v>
+        <v>122424772</v>
       </c>
       <c r="B40" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5505,34 +5180,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508916</v>
+        <v>508770</v>
       </c>
       <c r="R40" t="n">
-        <v>7008122</v>
+        <v>7008381</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5567,6 +5247,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5579,11 +5264,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -5616,7 +5296,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122427127</v>
+        <v>122429268</v>
       </c>
       <c r="B41" t="n">
         <v>57379</v>
@@ -5634,11 +5314,6 @@
       <c r="E41" t="n">
         <v>100109</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5655,16 +5330,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508631</v>
+        <v>508765</v>
       </c>
       <c r="R41" t="n">
-        <v>7008480</v>
+        <v>7008461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5701,7 +5381,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5712,6 +5392,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5728,10 +5428,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122429268</v>
+        <v>122430904</v>
       </c>
       <c r="B42" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5744,44 +5444,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508765</v>
+        <v>508916</v>
       </c>
       <c r="R42" t="n">
-        <v>7008461</v>
+        <v>7008122</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5816,11 +5501,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5833,11 +5513,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -5870,7 +5545,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122423113</v>
+        <v>122427763</v>
       </c>
       <c r="B43" t="n">
         <v>57379</v>
@@ -5888,11 +5563,6 @@
       <c r="E43" t="n">
         <v>100109</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5906,27 +5576,22 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508834</v>
+        <v>508776</v>
       </c>
       <c r="R43" t="n">
-        <v>7008115</v>
+        <v>7008533</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5960,7 +5625,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5971,31 +5636,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6012,10 +5652,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122429024</v>
+        <v>122427444</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6030,11 +5670,6 @@
       <c r="E44" t="n">
         <v>6425</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -6052,13 +5687,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508746</v>
+        <v>508541</v>
       </c>
       <c r="R44" t="n">
-        <v>7008449</v>
+        <v>7008422</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6090,6 +5725,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6101,17 +5741,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6121,7 +5756,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6139,10 +5774,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122423287</v>
+        <v>122426743</v>
       </c>
       <c r="B45" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6157,11 +5792,6 @@
       <c r="E45" t="n">
         <v>6425</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -6175,17 +5805,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508887</v>
+        <v>508764</v>
       </c>
       <c r="R45" t="n">
-        <v>7008167</v>
+        <v>7008423</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,6 +5847,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6228,12 +5863,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -6266,7 +5896,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429239</v>
+        <v>122422838</v>
       </c>
       <c r="B46" t="n">
         <v>57379</v>
@@ -6284,11 +5914,6 @@
       <c r="E46" t="n">
         <v>100109</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -6302,7 +5927,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6312,17 +5937,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508765</v>
+        <v>508855</v>
       </c>
       <c r="R46" t="n">
-        <v>7008466</v>
+        <v>7008046</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6356,7 +5981,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6371,11 +5996,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -6408,10 +6028,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122423524</v>
+        <v>122423979</v>
       </c>
       <c r="B47" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6424,42 +6044,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508928</v>
+        <v>508958</v>
       </c>
       <c r="R47" t="n">
-        <v>7008172</v>
+        <v>7008338</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6494,11 +6117,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6510,27 +6128,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6548,10 +6146,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122428487</v>
+        <v>122429949</v>
       </c>
       <c r="B48" t="n">
-        <v>79768</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6560,30 +6158,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6591,10 +6189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509041</v>
+        <v>508963</v>
       </c>
       <c r="R48" t="n">
-        <v>7008337</v>
+        <v>7008307</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6629,13 +6227,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6644,24 +6246,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6679,10 +6276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428831</v>
+        <v>122430040</v>
       </c>
       <c r="B49" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6695,42 +6292,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508914</v>
+        <v>508930</v>
       </c>
       <c r="R49" t="n">
-        <v>7008313</v>
+        <v>7008316</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6765,11 +6365,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6782,26 +6377,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6819,10 +6394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122430040</v>
+        <v>122424453</v>
       </c>
       <c r="B50" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6835,50 +6410,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508930</v>
+        <v>508908</v>
       </c>
       <c r="R50" t="n">
-        <v>7008316</v>
+        <v>7008354</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6913,6 +6475,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6925,6 +6492,21 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6942,7 +6524,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122423808</v>
+        <v>122428725</v>
       </c>
       <c r="B51" t="n">
         <v>57379</v>
@@ -6959,11 +6541,6 @@
       </c>
       <c r="E51" t="n">
         <v>100109</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6990,10 +6567,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508966</v>
+        <v>508919</v>
       </c>
       <c r="R51" t="n">
-        <v>7008356</v>
+        <v>7008295</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7045,11 +6622,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -7082,10 +6654,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122423979</v>
+        <v>122422848</v>
       </c>
       <c r="B52" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7098,50 +6670,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508958</v>
+        <v>508847</v>
       </c>
       <c r="R52" t="n">
-        <v>7008338</v>
+        <v>7008039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7176,6 +6735,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7188,6 +6752,21 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7205,10 +6784,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430707</v>
+        <v>122428487</v>
       </c>
       <c r="B53" t="n">
-        <v>57379</v>
+        <v>79769</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7217,35 +6796,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7253,10 +6822,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508959</v>
+        <v>509041</v>
       </c>
       <c r="R53" t="n">
-        <v>7008280</v>
+        <v>7008337</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7291,17 +6860,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7310,24 +6875,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7345,7 +6905,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428725</v>
+        <v>122423484</v>
       </c>
       <c r="B54" t="n">
         <v>57379</v>
@@ -7362,11 +6922,6 @@
       </c>
       <c r="E54" t="n">
         <v>100109</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7389,14 +6944,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508919</v>
+        <v>508920</v>
       </c>
       <c r="R54" t="n">
-        <v>7008295</v>
+        <v>7008181</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7433,7 +6988,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7447,17 +7002,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -7467,7 +7017,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7485,7 +7035,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428923</v>
+        <v>122423524</v>
       </c>
       <c r="B55" t="n">
         <v>57379</v>
@@ -7502,11 +7052,6 @@
       </c>
       <c r="E55" t="n">
         <v>100109</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7529,14 +7074,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508978</v>
+        <v>508928</v>
       </c>
       <c r="R55" t="n">
-        <v>7008270</v>
+        <v>7008172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7573,7 +7118,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7587,17 +7132,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -7607,7 +7147,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7643,11 +7183,6 @@
       <c r="E56" t="n">
         <v>100109</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -7730,11 +7265,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK56" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -7765,7 +7295,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122423484</v>
+        <v>122424038</v>
       </c>
       <c r="B57" t="n">
         <v>57379</v>
@@ -7782,11 +7312,6 @@
       </c>
       <c r="E57" t="n">
         <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7809,14 +7334,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508920</v>
+        <v>508954</v>
       </c>
       <c r="R57" t="n">
-        <v>7008181</v>
+        <v>7008336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7853,7 +7378,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7867,17 +7392,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -7887,7 +7407,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7905,10 +7425,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122429553</v>
+        <v>122428462</v>
       </c>
       <c r="B58" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7921,31 +7441,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7953,10 +7463,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509048</v>
+        <v>509040</v>
       </c>
       <c r="R58" t="n">
-        <v>7008315</v>
+        <v>7008336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7991,17 +7501,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8010,24 +7516,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8048,7 +7549,7 @@
         <v>122428777</v>
       </c>
       <c r="B59" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8062,11 +7563,6 @@
       </c>
       <c r="E59" t="n">
         <v>6458</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8143,11 +7639,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -8180,7 +7671,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122423202</v>
+        <v>122428923</v>
       </c>
       <c r="B60" t="n">
         <v>57379</v>
@@ -8197,11 +7688,6 @@
       </c>
       <c r="E60" t="n">
         <v>100109</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8224,14 +7710,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508881</v>
+        <v>508978</v>
       </c>
       <c r="R60" t="n">
-        <v>7008130</v>
+        <v>7008270</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8283,11 +7769,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -8320,7 +7801,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424453</v>
+        <v>122430628</v>
       </c>
       <c r="B61" t="n">
         <v>57379</v>
@@ -8337,11 +7818,6 @@
       </c>
       <c r="E61" t="n">
         <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -8368,10 +7844,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508908</v>
+        <v>508965</v>
       </c>
       <c r="R61" t="n">
-        <v>7008354</v>
+        <v>7008296</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8423,11 +7899,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -8460,10 +7931,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122429607</v>
+        <v>122428831</v>
       </c>
       <c r="B62" t="n">
-        <v>82438</v>
+        <v>57379</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8476,26 +7947,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8503,10 +7974,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>509034</v>
+        <v>508914</v>
       </c>
       <c r="R62" t="n">
-        <v>7008306</v>
+        <v>7008313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8541,13 +8012,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8556,19 +8031,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK62" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8586,10 +8061,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122429949</v>
+        <v>122429607</v>
       </c>
       <c r="B63" t="n">
-        <v>57379</v>
+        <v>82439</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8602,31 +8077,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>1312</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8634,10 +8099,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508963</v>
+        <v>509034</v>
       </c>
       <c r="R63" t="n">
-        <v>7008307</v>
+        <v>7008306</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8672,17 +8137,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8691,24 +8152,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK63" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8726,10 +8177,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122428462</v>
+        <v>122424304</v>
       </c>
       <c r="B64" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8744,11 +8195,6 @@
       <c r="E64" t="n">
         <v>6458</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8761,7 +8207,11 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8769,10 +8219,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509040</v>
+        <v>508904</v>
       </c>
       <c r="R64" t="n">
-        <v>7008336</v>
+        <v>7008325</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8820,11 +8270,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -8857,10 +8302,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424328</v>
+        <v>122423808</v>
       </c>
       <c r="B65" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8873,26 +8318,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8900,10 +8345,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508904</v>
+        <v>508966</v>
       </c>
       <c r="R65" t="n">
-        <v>7008325</v>
+        <v>7008356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8940,7 +8385,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8949,7 +8394,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8958,19 +8402,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK65" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8988,7 +8432,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424038</v>
+        <v>122423202</v>
       </c>
       <c r="B66" t="n">
         <v>57379</v>
@@ -9005,11 +8449,6 @@
       </c>
       <c r="E66" t="n">
         <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -9032,14 +8471,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508954</v>
+        <v>508881</v>
       </c>
       <c r="R66" t="n">
-        <v>7008336</v>
+        <v>7008130</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9091,11 +8530,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -9128,10 +8562,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429210</v>
+        <v>122429553</v>
       </c>
       <c r="B67" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9144,26 +8578,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9171,10 +8605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509071</v>
+        <v>509048</v>
       </c>
       <c r="R67" t="n">
-        <v>7008310</v>
+        <v>7008315</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9211,7 +8645,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9220,7 +8654,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9229,19 +8662,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK67" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9259,10 +8692,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122422848</v>
+        <v>122429210</v>
       </c>
       <c r="B68" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9275,42 +8708,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508847</v>
+        <v>509071</v>
       </c>
       <c r="R68" t="n">
-        <v>7008039</v>
+        <v>7008310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9347,7 +8770,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9356,6 +8779,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9364,24 +8788,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK68" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9399,7 +8813,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122430628</v>
+        <v>122430707</v>
       </c>
       <c r="B69" t="n">
         <v>57379</v>
@@ -9416,11 +8830,6 @@
       </c>
       <c r="E69" t="n">
         <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -9447,10 +8856,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508965</v>
+        <v>508959</v>
       </c>
       <c r="R69" t="n">
-        <v>7008296</v>
+        <v>7008280</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9502,11 +8911,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122426947</v>
+        <v>122424676</v>
       </c>
       <c r="B10" t="n">
-        <v>56581</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1639,14 +1639,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1655,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508535</v>
+        <v>508779</v>
       </c>
       <c r="R10" t="n">
-        <v>7008440</v>
+        <v>7008383</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,6 +1687,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122424114</v>
+        <v>122423113</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,32 +1734,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508968</v>
+        <v>508834</v>
       </c>
       <c r="R11" t="n">
-        <v>7008319</v>
+        <v>7008115</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,7 +1803,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,12 +1827,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1839,7 +1850,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122428118</v>
+        <v>122424114</v>
       </c>
       <c r="B12" t="n">
         <v>78652</v>
@@ -1874,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508595</v>
+        <v>508968</v>
       </c>
       <c r="R12" t="n">
-        <v>7008516</v>
+        <v>7008319</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,7 +1939,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -1961,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122424676</v>
+        <v>122428118</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,37 +1988,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508779</v>
+        <v>508595</v>
       </c>
       <c r="R13" t="n">
-        <v>7008383</v>
+        <v>7008516</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2041,7 +2047,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,6 +2058,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2068,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423113</v>
+        <v>122426947</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>56581</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,11 +2110,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2096,30 +2122,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508834</v>
+        <v>508535</v>
       </c>
       <c r="R14" t="n">
-        <v>7008115</v>
+        <v>7008440</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,11 +2176,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2164,26 +2184,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423191</v>
+        <v>122428937</v>
       </c>
       <c r="B20" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,29 +2821,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508859</v>
+        <v>508739</v>
       </c>
       <c r="R20" t="n">
-        <v>7008134</v>
+        <v>7008454</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2878,6 +2883,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2889,7 +2899,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2899,12 +2909,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2922,10 +2932,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122428937</v>
+        <v>122423191</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2938,34 +2948,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508739</v>
+        <v>508859</v>
       </c>
       <c r="R21" t="n">
-        <v>7008454</v>
+        <v>7008134</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3000,11 +3005,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423626</v>
+        <v>122424589</v>
       </c>
       <c r="B28" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3792,31 +3792,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3825,10 +3816,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508994</v>
+        <v>508831</v>
       </c>
       <c r="R28" t="n">
-        <v>7008252</v>
+        <v>7008397</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3865,7 +3856,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3876,11 +3867,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3897,10 +3883,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122424589</v>
+        <v>122423626</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3913,22 +3899,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3937,10 +3932,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508831</v>
+        <v>508994</v>
       </c>
       <c r="R29" t="n">
-        <v>7008397</v>
+        <v>7008252</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3977,7 +3972,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3988,6 +3983,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122430904</v>
+        <v>122427763</v>
       </c>
       <c r="B42" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5444,29 +5444,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508916</v>
+        <v>508776</v>
       </c>
       <c r="R42" t="n">
-        <v>7008122</v>
+        <v>7008533</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5501,6 +5506,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5509,26 +5519,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5545,10 +5535,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427763</v>
+        <v>122430904</v>
       </c>
       <c r="B43" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5561,34 +5551,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508776</v>
+        <v>508916</v>
       </c>
       <c r="R43" t="n">
-        <v>7008533</v>
+        <v>7008122</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5623,11 +5608,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5636,6 +5616,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122424676</v>
+        <v>122424114</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1627,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508779</v>
+        <v>508968</v>
       </c>
       <c r="R10" t="n">
-        <v>7008383</v>
+        <v>7008319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,6 +1697,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122423113</v>
+        <v>122428118</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,39 +1749,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508834</v>
+        <v>508595</v>
       </c>
       <c r="R11" t="n">
-        <v>7008115</v>
+        <v>7008516</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1803,7 +1808,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1827,12 +1832,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1850,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122424114</v>
+        <v>122424676</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,29 +1871,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508968</v>
+        <v>508779</v>
       </c>
       <c r="R12" t="n">
-        <v>7008319</v>
+        <v>7008383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1935,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,26 +1946,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1972,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122428118</v>
+        <v>122423113</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,29 +1978,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508595</v>
+        <v>508834</v>
       </c>
       <c r="R13" t="n">
-        <v>7008516</v>
+        <v>7008115</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122426947</v>
+        <v>122423040</v>
       </c>
       <c r="B14" t="n">
-        <v>56581</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,11 +2110,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2122,29 +2122,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508535</v>
+        <v>508845</v>
       </c>
       <c r="R14" t="n">
-        <v>7008440</v>
+        <v>7008072</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2176,6 +2177,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2184,6 +2190,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2200,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122423040</v>
+        <v>122426947</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>56581</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,11 +2242,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2228,30 +2254,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508845</v>
+        <v>508535</v>
       </c>
       <c r="R15" t="n">
-        <v>7008072</v>
+        <v>7008440</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2283,11 +2308,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2296,26 +2316,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2332,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423811</v>
+        <v>122423711</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,39 +2348,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508995</v>
+        <v>509001</v>
       </c>
       <c r="R16" t="n">
-        <v>7008282</v>
+        <v>7008256</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,11 +2405,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2441,12 +2426,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2464,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122424707</v>
+        <v>122429024</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,37 +2465,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508781</v>
+        <v>508746</v>
       </c>
       <c r="R17" t="n">
-        <v>7008382</v>
+        <v>7008449</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2542,11 +2522,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2555,6 +2530,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2571,10 +2566,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423711</v>
+        <v>122423811</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,29 +2582,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509001</v>
+        <v>508995</v>
       </c>
       <c r="R18" t="n">
-        <v>7008256</v>
+        <v>7008282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,6 +2649,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2665,12 +2675,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2688,10 +2698,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429024</v>
+        <v>122424707</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,32 +2714,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508746</v>
+        <v>508781</v>
       </c>
       <c r="R19" t="n">
-        <v>7008449</v>
+        <v>7008382</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,6 +2776,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2769,26 +2789,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122428937</v>
+        <v>122423191</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,34 +2821,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508739</v>
+        <v>508859</v>
       </c>
       <c r="R20" t="n">
-        <v>7008454</v>
+        <v>7008134</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2883,11 +2878,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2889,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2909,12 +2899,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2932,10 +2922,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122423191</v>
+        <v>122428937</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2948,29 +2938,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508859</v>
+        <v>508739</v>
       </c>
       <c r="R21" t="n">
-        <v>7008134</v>
+        <v>7008454</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3005,6 +3000,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430040</v>
+        <v>122424453</v>
       </c>
       <c r="B49" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6292,45 +6292,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508930</v>
+        <v>508908</v>
       </c>
       <c r="R49" t="n">
-        <v>7008316</v>
+        <v>7008354</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6365,6 +6357,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6377,6 +6374,21 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6394,7 +6406,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122424453</v>
+        <v>122428725</v>
       </c>
       <c r="B50" t="n">
         <v>57379</v>
@@ -6437,10 +6449,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508908</v>
+        <v>508919</v>
       </c>
       <c r="R50" t="n">
-        <v>7008354</v>
+        <v>7008295</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6524,10 +6536,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428725</v>
+        <v>122430040</v>
       </c>
       <c r="B51" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6540,37 +6552,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508919</v>
+        <v>508930</v>
       </c>
       <c r="R51" t="n">
-        <v>7008295</v>
+        <v>7008316</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6605,11 +6625,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6622,21 +6637,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122426582</v>
+        <v>122423588</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508771</v>
+        <v>508975</v>
       </c>
       <c r="R2" t="n">
-        <v>7008433</v>
+        <v>7008243</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -777,6 +767,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -784,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424389</v>
+        <v>122428118</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,37 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508892</v>
+        <v>508595</v>
       </c>
       <c r="R3" t="n">
-        <v>7008349</v>
+        <v>7008516</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +896,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122423588</v>
+        <v>122430904</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,6 +952,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -965,14 +970,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508975</v>
+        <v>508916</v>
       </c>
       <c r="R4" t="n">
-        <v>7008243</v>
+        <v>7008122</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,6 +1026,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1028,12 +1038,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122424308</v>
+        <v>122423133</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,32 +1077,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508903</v>
+        <v>508834</v>
       </c>
       <c r="R5" t="n">
-        <v>7008351</v>
+        <v>7008117</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1151,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,6 +1168,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1150,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429398</v>
+        <v>122424389</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,32 +1219,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508809</v>
+        <v>508892</v>
       </c>
       <c r="R6" t="n">
-        <v>7008468</v>
+        <v>7008349</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,6 +1286,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1260,6 +1305,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1267,12 +1317,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427586</v>
+        <v>122429024</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,37 +1356,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508745</v>
+        <v>508746</v>
       </c>
       <c r="R7" t="n">
-        <v>7008511</v>
+        <v>7008449</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,11 +1418,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1381,6 +1426,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122426823</v>
+        <v>122429239</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,6 +1485,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1431,19 +1506,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508614</v>
+        <v>508765</v>
       </c>
       <c r="R8" t="n">
-        <v>7008464</v>
+        <v>7008466</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,6 +1568,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1504,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122427681</v>
+        <v>122424114</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1625,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508760</v>
+        <v>508968</v>
       </c>
       <c r="R9" t="n">
-        <v>7008533</v>
+        <v>7008319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1689,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,6 +1700,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1611,10 +1741,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122424114</v>
+        <v>122423113</v>
       </c>
       <c r="B10" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,32 +1757,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508968</v>
+        <v>508834</v>
       </c>
       <c r="R10" t="n">
-        <v>7008319</v>
+        <v>7008115</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1831,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,6 +1848,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1710,12 +1860,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,10 +1883,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122428118</v>
+        <v>122427629</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,33 +1895,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508595</v>
+        <v>508574</v>
       </c>
       <c r="R11" t="n">
-        <v>7008516</v>
+        <v>7008461</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1806,11 +1971,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1823,21 +1983,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1855,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122424676</v>
+        <v>122424308</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,37 +2016,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508779</v>
+        <v>508903</v>
       </c>
       <c r="R12" t="n">
-        <v>7008383</v>
+        <v>7008351</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,7 +2080,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,6 +2091,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1962,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423113</v>
+        <v>122422838</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,6 +2150,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2007,10 +2182,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508834</v>
+        <v>508855</v>
       </c>
       <c r="R13" t="n">
-        <v>7008115</v>
+        <v>7008046</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2062,6 +2237,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2094,10 +2274,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423040</v>
+        <v>122423988</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,42 +2290,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508845</v>
+        <v>508982</v>
       </c>
       <c r="R14" t="n">
-        <v>7008072</v>
+        <v>7008301</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2177,11 +2352,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2196,6 +2366,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2203,12 +2378,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2226,10 +2401,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122426947</v>
+        <v>122429268</v>
       </c>
       <c r="B15" t="n">
-        <v>56581</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,11 +2417,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2254,14 +2434,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2270,10 +2451,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508535</v>
+        <v>508765</v>
       </c>
       <c r="R15" t="n">
-        <v>7008440</v>
+        <v>7008461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2308,6 +2489,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2316,6 +2502,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2332,10 +2543,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423711</v>
+        <v>122422959</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,29 +2559,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509001</v>
+        <v>508833</v>
       </c>
       <c r="R16" t="n">
-        <v>7008256</v>
+        <v>7008097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2637,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2426,12 +2652,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2449,10 +2675,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122429024</v>
+        <v>122423711</v>
       </c>
       <c r="B17" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,6 +2693,11 @@
       <c r="E17" t="n">
         <v>6425</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2484,13 +2715,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508746</v>
+        <v>509001</v>
       </c>
       <c r="R17" t="n">
-        <v>7008449</v>
+        <v>7008256</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2534,6 +2765,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2566,10 +2802,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423811</v>
+        <v>122427142</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2582,39 +2818,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508995</v>
+        <v>508688</v>
       </c>
       <c r="R18" t="n">
-        <v>7008282</v>
+        <v>7008395</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,11 +2880,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2665,7 +2891,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2675,12 +2906,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2698,10 +2929,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122424707</v>
+        <v>122426743</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2714,34 +2945,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508781</v>
+        <v>508764</v>
       </c>
       <c r="R19" t="n">
-        <v>7008382</v>
+        <v>7008423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,7 +3009,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,6 +3020,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2805,10 +3061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423191</v>
+        <v>122423935</v>
       </c>
       <c r="B20" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,32 +3077,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508859</v>
+        <v>508980</v>
       </c>
       <c r="R20" t="n">
-        <v>7008134</v>
+        <v>7008294</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2878,6 +3149,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2889,7 +3165,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2899,12 +3180,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,7 +3206,7 @@
         <v>122428937</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,6 +3221,11 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3017,6 +3303,11 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3049,10 +3340,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122429239</v>
+        <v>122427227</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3065,42 +3356,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508765</v>
+        <v>508639</v>
       </c>
       <c r="R22" t="n">
-        <v>7008466</v>
+        <v>7008388</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3132,11 +3418,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack främst på stambasen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3148,22 +3429,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3181,10 +3467,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122423935</v>
+        <v>122423040</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,6 +3485,11 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3222,17 +3513,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508980</v>
+        <v>508845</v>
       </c>
       <c r="R23" t="n">
-        <v>7008294</v>
+        <v>7008072</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3266,7 +3557,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3281,6 +3572,11 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3313,10 +3609,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122423988</v>
+        <v>122423626</v>
       </c>
       <c r="B24" t="n">
-        <v>78652</v>
+        <v>57536</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3329,29 +3625,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508982</v>
+        <v>508994</v>
       </c>
       <c r="R24" t="n">
-        <v>7008301</v>
+        <v>7008252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3386,6 +3701,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst två individer, möjligen fler.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3398,21 +3718,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3430,10 +3735,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122424496</v>
+        <v>122424637</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3446,34 +3751,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508891</v>
+        <v>508814</v>
       </c>
       <c r="R25" t="n">
-        <v>7008386</v>
+        <v>7008416</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3508,11 +3813,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3521,6 +3821,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3537,10 +3862,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122424611</v>
+        <v>122426582</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3553,11 +3878,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3571,16 +3901,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508820</v>
+        <v>508771</v>
       </c>
       <c r="R26" t="n">
-        <v>7008398</v>
+        <v>7008433</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3952,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3628,6 +3963,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3644,10 +4004,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423133</v>
+        <v>122426951</v>
       </c>
       <c r="B27" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3662,6 +4022,11 @@
       <c r="E27" t="n">
         <v>100109</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3675,27 +4040,22 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508834</v>
+        <v>508719</v>
       </c>
       <c r="R27" t="n">
-        <v>7008117</v>
+        <v>7008377</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3729,7 +4089,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,6 +4106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3753,12 +4118,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3776,10 +4141,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122424589</v>
+        <v>122429398</v>
       </c>
       <c r="B28" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3792,34 +4157,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508831</v>
+        <v>508809</v>
       </c>
       <c r="R28" t="n">
-        <v>7008397</v>
+        <v>7008468</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3854,11 +4219,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3867,6 +4227,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3883,10 +4268,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423626</v>
+        <v>122423191</v>
       </c>
       <c r="B29" t="n">
-        <v>57532</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3899,46 +4284,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508994</v>
+        <v>508859</v>
       </c>
       <c r="R29" t="n">
-        <v>7008252</v>
+        <v>7008134</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3970,11 +4346,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst två individer, möjligen fler.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3986,7 +4357,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4004,10 +4395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122422959</v>
+        <v>122423811</v>
       </c>
       <c r="B30" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4020,34 +4411,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508833</v>
+        <v>508995</v>
       </c>
       <c r="R30" t="n">
-        <v>7008097</v>
+        <v>7008282</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4082,6 +4483,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4093,7 +4499,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4103,12 +4514,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4126,10 +4537,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122427227</v>
+        <v>122423287</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4144,6 +4555,11 @@
       <c r="E31" t="n">
         <v>6425</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4157,17 +4573,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508639</v>
+        <v>508887</v>
       </c>
       <c r="R31" t="n">
-        <v>7008388</v>
+        <v>7008167</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4213,9 +4629,14 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4225,7 +4646,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4243,10 +4664,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122427127</v>
+        <v>122424772</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4259,11 +4680,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4277,16 +4703,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508631</v>
+        <v>508770</v>
       </c>
       <c r="R32" t="n">
-        <v>7008480</v>
+        <v>7008381</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4323,7 +4754,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4334,6 +4765,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4350,10 +4806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429281</v>
+        <v>122423467</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4366,37 +4822,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509109</v>
+        <v>508900</v>
       </c>
       <c r="R33" t="n">
-        <v>7008253</v>
+        <v>7008203</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4428,11 +4884,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4441,6 +4892,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4457,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423467</v>
+        <v>122429949</v>
       </c>
       <c r="B34" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4473,32 +4949,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508900</v>
+        <v>508963</v>
       </c>
       <c r="R34" t="n">
-        <v>7008203</v>
+        <v>7008307</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4530,6 +5019,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4541,7 +5035,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -4551,12 +5050,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4574,10 +5073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122426951</v>
+        <v>122429210</v>
       </c>
       <c r="B35" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,34 +5089,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508719</v>
+        <v>509071</v>
       </c>
       <c r="R35" t="n">
-        <v>7008377</v>
+        <v>7008310</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +5156,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4663,6 +5165,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4671,19 +5174,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4701,10 +5204,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122427629</v>
+        <v>122429607</v>
       </c>
       <c r="B36" t="n">
-        <v>97165</v>
+        <v>82443</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4713,46 +5216,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>1312</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508574</v>
+        <v>509034</v>
       </c>
       <c r="R36" t="n">
-        <v>7008461</v>
+        <v>7008306</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4790,12 +5291,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4813,10 +5330,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427142</v>
+        <v>122424038</v>
       </c>
       <c r="B37" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4829,29 +5346,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508688</v>
+        <v>508954</v>
       </c>
       <c r="R37" t="n">
-        <v>7008395</v>
+        <v>7008336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4886,6 +5416,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4897,7 +5432,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -4907,12 +5447,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4930,10 +5470,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423287</v>
+        <v>122423808</v>
       </c>
       <c r="B38" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4946,32 +5486,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508887</v>
+        <v>508966</v>
       </c>
       <c r="R38" t="n">
-        <v>7008167</v>
+        <v>7008356</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5003,6 +5556,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5014,7 +5572,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -5024,12 +5587,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5047,10 +5610,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122424637</v>
+        <v>122423524</v>
       </c>
       <c r="B39" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5063,29 +5626,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508814</v>
+        <v>508928</v>
       </c>
       <c r="R39" t="n">
-        <v>7008416</v>
+        <v>7008172</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5120,6 +5696,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5131,22 +5712,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5164,10 +5750,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122424772</v>
+        <v>122430040</v>
       </c>
       <c r="B40" t="n">
-        <v>57395</v>
+        <v>57536</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5180,22 +5766,33 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5209,10 +5806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508770</v>
+        <v>508930</v>
       </c>
       <c r="R40" t="n">
-        <v>7008381</v>
+        <v>7008316</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5247,11 +5844,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5264,21 +5856,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5296,10 +5873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122429268</v>
+        <v>122428777</v>
       </c>
       <c r="B41" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5312,39 +5889,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508765</v>
+        <v>508909</v>
       </c>
       <c r="R41" t="n">
-        <v>7008461</v>
+        <v>7008302</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5379,17 +5958,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5398,19 +5973,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5428,10 +6008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122427763</v>
+        <v>122428831</v>
       </c>
       <c r="B42" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5446,6 +6026,11 @@
       <c r="E42" t="n">
         <v>100109</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5457,21 +6042,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508776</v>
+        <v>508914</v>
       </c>
       <c r="R42" t="n">
-        <v>7008533</v>
+        <v>7008313</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5508,7 +6096,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5519,6 +6107,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5535,10 +6148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122430904</v>
+        <v>122424328</v>
       </c>
       <c r="B43" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5551,29 +6164,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508916</v>
+        <v>508904</v>
       </c>
       <c r="R43" t="n">
-        <v>7008122</v>
+        <v>7008325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5608,12 +6229,18 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5622,19 +6249,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK43" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5652,10 +6279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427444</v>
+        <v>122428462</v>
       </c>
       <c r="B44" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5668,29 +6295,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508541</v>
+        <v>509040</v>
       </c>
       <c r="R44" t="n">
-        <v>7008422</v>
+        <v>7008336</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5725,38 +6360,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5774,10 +6410,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122426743</v>
+        <v>122423979</v>
       </c>
       <c r="B45" t="n">
-        <v>78652</v>
+        <v>57536</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5790,29 +6426,50 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508764</v>
+        <v>508958</v>
       </c>
       <c r="R45" t="n">
-        <v>7008423</v>
+        <v>7008338</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5847,11 +6504,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5864,21 +6516,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5896,10 +6533,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122422838</v>
+        <v>122423202</v>
       </c>
       <c r="B46" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5914,6 +6551,11 @@
       <c r="E46" t="n">
         <v>100109</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5925,29 +6567,27 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508855</v>
+        <v>508881</v>
       </c>
       <c r="R46" t="n">
-        <v>7008046</v>
+        <v>7008130</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5981,7 +6621,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5996,6 +6636,11 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -6028,10 +6673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122423979</v>
+        <v>122428923</v>
       </c>
       <c r="B47" t="n">
-        <v>57532</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6044,45 +6689,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508958</v>
+        <v>508978</v>
       </c>
       <c r="R47" t="n">
-        <v>7008338</v>
+        <v>7008270</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6117,6 +6759,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6129,6 +6776,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6146,10 +6813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122429949</v>
+        <v>122422848</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6163,6 +6830,11 @@
       </c>
       <c r="E48" t="n">
         <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6185,14 +6857,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508963</v>
+        <v>508847</v>
       </c>
       <c r="R48" t="n">
-        <v>7008307</v>
+        <v>7008039</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6244,6 +6916,11 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -6276,10 +6953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122424453</v>
+        <v>122428725</v>
       </c>
       <c r="B49" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6293,6 +6970,11 @@
       </c>
       <c r="E49" t="n">
         <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6319,10 +7001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508908</v>
+        <v>508919</v>
       </c>
       <c r="R49" t="n">
-        <v>7008354</v>
+        <v>7008295</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6374,6 +7056,11 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -6406,10 +7093,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122428725</v>
+        <v>122430707</v>
       </c>
       <c r="B50" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6423,6 +7110,11 @@
       </c>
       <c r="E50" t="n">
         <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6449,10 +7141,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508919</v>
+        <v>508959</v>
       </c>
       <c r="R50" t="n">
-        <v>7008295</v>
+        <v>7008280</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6504,6 +7196,11 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -6536,10 +7233,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122430040</v>
+        <v>122424126</v>
       </c>
       <c r="B51" t="n">
-        <v>57532</v>
+        <v>57383</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6552,45 +7249,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508930</v>
+        <v>508950</v>
       </c>
       <c r="R51" t="n">
-        <v>7008316</v>
+        <v>7008334</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6625,6 +7319,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6637,6 +7336,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6654,10 +7373,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122422848</v>
+        <v>122423484</v>
       </c>
       <c r="B52" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6671,6 +7390,11 @@
       </c>
       <c r="E52" t="n">
         <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6697,10 +7421,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508847</v>
+        <v>508920</v>
       </c>
       <c r="R52" t="n">
-        <v>7008039</v>
+        <v>7008181</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,7 +7461,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6751,12 +7475,17 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -6766,7 +7495,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6784,10 +7513,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428487</v>
+        <v>122429553</v>
       </c>
       <c r="B53" t="n">
-        <v>79769</v>
+        <v>57383</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6796,25 +7525,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6822,10 +7561,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509041</v>
+        <v>509048</v>
       </c>
       <c r="R53" t="n">
-        <v>7008337</v>
+        <v>7008315</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6860,13 +7599,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6875,19 +7618,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6905,10 +7653,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122423484</v>
+        <v>122428487</v>
       </c>
       <c r="B54" t="n">
-        <v>57379</v>
+        <v>79773</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6917,41 +7665,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6464</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508920</v>
+        <v>509041</v>
       </c>
       <c r="R54" t="n">
-        <v>7008181</v>
+        <v>7008337</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6986,38 +7734,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7035,10 +7784,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122423524</v>
+        <v>122424453</v>
       </c>
       <c r="B55" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7052,6 +7801,11 @@
       </c>
       <c r="E55" t="n">
         <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7074,14 +7828,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508928</v>
+        <v>508908</v>
       </c>
       <c r="R55" t="n">
-        <v>7008172</v>
+        <v>7008354</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7118,7 +7872,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7132,12 +7886,17 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -7147,7 +7906,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7165,10 +7924,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122424126</v>
+        <v>122430628</v>
       </c>
       <c r="B56" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7182,6 +7941,11 @@
       </c>
       <c r="E56" t="n">
         <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7208,10 +7972,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508950</v>
+        <v>508965</v>
       </c>
       <c r="R56" t="n">
-        <v>7008334</v>
+        <v>7008296</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7263,6 +8027,11 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -7295,10 +8064,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122424038</v>
+        <v>122427444</v>
       </c>
       <c r="B57" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7311,26 +8080,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7338,10 +8107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508954</v>
+        <v>508541</v>
       </c>
       <c r="R57" t="n">
-        <v>7008336</v>
+        <v>7008422</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7378,7 +8147,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7387,27 +8156,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7425,10 +8200,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122428462</v>
+        <v>122424611</v>
       </c>
       <c r="B58" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7441,21 +8216,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7463,10 +8248,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509040</v>
+        <v>508820</v>
       </c>
       <c r="R58" t="n">
-        <v>7008336</v>
+        <v>7008398</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7501,13 +8286,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7516,19 +8305,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7546,10 +8340,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122428777</v>
+        <v>122429281</v>
       </c>
       <c r="B59" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7562,23 +8356,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7588,10 +8388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508909</v>
+        <v>509109</v>
       </c>
       <c r="R59" t="n">
-        <v>7008302</v>
+        <v>7008253</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7626,13 +8426,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7641,19 +8445,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7671,10 +8475,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428923</v>
+        <v>122426823</v>
       </c>
       <c r="B60" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7688,6 +8492,11 @@
       </c>
       <c r="E60" t="n">
         <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7704,7 +8513,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7714,10 +8523,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508978</v>
+        <v>508614</v>
       </c>
       <c r="R60" t="n">
-        <v>7008270</v>
+        <v>7008464</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7754,7 +8563,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7769,6 +8578,11 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -7801,10 +8615,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122430628</v>
+        <v>122427763</v>
       </c>
       <c r="B61" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7818,6 +8632,11 @@
       </c>
       <c r="E61" t="n">
         <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7834,7 +8653,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7844,10 +8663,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508965</v>
+        <v>508776</v>
       </c>
       <c r="R61" t="n">
-        <v>7008296</v>
+        <v>7008533</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,7 +8703,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7899,6 +8718,11 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -7931,10 +8755,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122428831</v>
+        <v>122424676</v>
       </c>
       <c r="B62" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7948,6 +8772,11 @@
       </c>
       <c r="E62" t="n">
         <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7974,10 +8803,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508914</v>
+        <v>508779</v>
       </c>
       <c r="R62" t="n">
-        <v>7008313</v>
+        <v>7008383</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8031,19 +8860,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK62" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8061,10 +8890,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122429607</v>
+        <v>122424707</v>
       </c>
       <c r="B63" t="n">
-        <v>82439</v>
+        <v>57383</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8077,21 +8906,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8099,10 +8938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>509034</v>
+        <v>508781</v>
       </c>
       <c r="R63" t="n">
-        <v>7008306</v>
+        <v>7008382</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8137,13 +8976,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8152,14 +8995,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK63" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8177,10 +9030,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424304</v>
+        <v>122427586</v>
       </c>
       <c r="B64" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8193,23 +9046,29 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8219,10 +9078,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508904</v>
+        <v>508745</v>
       </c>
       <c r="R64" t="n">
-        <v>7008325</v>
+        <v>7008511</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8257,13 +9116,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8272,19 +9135,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8302,10 +9165,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122423808</v>
+        <v>122427681</v>
       </c>
       <c r="B65" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8319,6 +9182,11 @@
       </c>
       <c r="E65" t="n">
         <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8345,10 +9213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508966</v>
+        <v>508760</v>
       </c>
       <c r="R65" t="n">
-        <v>7008356</v>
+        <v>7008533</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8400,6 +9268,11 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -8432,10 +9305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122423202</v>
+        <v>122427127</v>
       </c>
       <c r="B66" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8449,6 +9322,11 @@
       </c>
       <c r="E66" t="n">
         <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8471,14 +9349,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508881</v>
+        <v>508631</v>
       </c>
       <c r="R66" t="n">
-        <v>7008130</v>
+        <v>7008480</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8515,7 +9393,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8529,7 +9407,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -8537,14 +9420,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8562,10 +9440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429553</v>
+        <v>122426947</v>
       </c>
       <c r="B67" t="n">
-        <v>57379</v>
+        <v>56585</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8578,11 +9456,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>102612</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8590,12 +9473,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8605,10 +9492,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509048</v>
+        <v>508535</v>
       </c>
       <c r="R67" t="n">
-        <v>7008315</v>
+        <v>7008440</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8643,11 +9530,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8659,22 +9541,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8692,10 +9559,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122429210</v>
+        <v>122424496</v>
       </c>
       <c r="B68" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8708,21 +9575,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8730,10 +9607,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509071</v>
+        <v>508891</v>
       </c>
       <c r="R68" t="n">
-        <v>7008310</v>
+        <v>7008386</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8770,7 +9647,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8779,7 +9656,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8788,14 +9664,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK68" t="inlineStr">
         <is>
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8813,10 +9699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122430707</v>
+        <v>122424589</v>
       </c>
       <c r="B69" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8830,6 +9716,11 @@
       </c>
       <c r="E69" t="n">
         <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8856,10 +9747,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508959</v>
+        <v>508831</v>
       </c>
       <c r="R69" t="n">
-        <v>7008280</v>
+        <v>7008397</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8911,6 +9802,11 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122423588</v>
+        <v>122427142</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508975</v>
+        <v>508688</v>
       </c>
       <c r="R2" t="n">
-        <v>7008243</v>
+        <v>7008395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428118</v>
+        <v>122423811</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +818,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508595</v>
+        <v>508995</v>
       </c>
       <c r="R3" t="n">
-        <v>7008516</v>
+        <v>7008282</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +906,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -911,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430904</v>
+        <v>122426582</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,34 +960,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508916</v>
+        <v>508771</v>
       </c>
       <c r="R4" t="n">
-        <v>7008122</v>
+        <v>7008433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,6 +1032,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,12 +1063,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1086,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122423133</v>
+        <v>122428937</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1100,21 +1125,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508834</v>
+        <v>508739</v>
       </c>
       <c r="R5" t="n">
-        <v>7008117</v>
+        <v>7008454</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1151,7 +1171,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,7 +1223,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122424389</v>
+        <v>122422838</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1242,19 +1262,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508892</v>
+        <v>508855</v>
       </c>
       <c r="R6" t="n">
-        <v>7008349</v>
+        <v>7008046</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1340,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429024</v>
+        <v>122423133</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,37 +1381,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508746</v>
+        <v>508834</v>
       </c>
       <c r="R7" t="n">
-        <v>7008449</v>
+        <v>7008117</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,6 +1453,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1444,12 +1484,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1507,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429239</v>
+        <v>122429398</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,47 +1523,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508765</v>
+        <v>508809</v>
       </c>
       <c r="R8" t="n">
-        <v>7008466</v>
+        <v>7008468</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,11 +1585,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack främst på stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1586,12 +1611,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1741,10 +1766,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423113</v>
+        <v>122424308</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1757,47 +1782,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508834</v>
+        <v>508903</v>
       </c>
       <c r="R10" t="n">
-        <v>7008115</v>
+        <v>7008351</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1831,7 +1846,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1860,12 +1875,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1883,10 +1898,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122427629</v>
+        <v>122426951</v>
       </c>
       <c r="B11" t="n">
-        <v>97178</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1895,36 +1910,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1933,13 +1943,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508574</v>
+        <v>508719</v>
       </c>
       <c r="R11" t="n">
-        <v>7008461</v>
+        <v>7008377</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1971,6 +1981,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1997,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2000,10 +2035,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122424308</v>
+        <v>122427629</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2012,41 +2047,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508903</v>
+        <v>508574</v>
       </c>
       <c r="R12" t="n">
-        <v>7008351</v>
+        <v>7008461</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2078,11 +2123,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2094,27 +2134,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2132,10 +2152,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122422838</v>
+        <v>122423988</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2148,47 +2168,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508855</v>
+        <v>508982</v>
       </c>
       <c r="R13" t="n">
-        <v>7008046</v>
+        <v>7008301</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2220,11 +2230,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2251,12 +2256,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2274,10 +2279,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423988</v>
+        <v>122424389</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2290,37 +2295,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508982</v>
+        <v>508892</v>
       </c>
       <c r="R14" t="n">
-        <v>7008301</v>
+        <v>7008349</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2352,6 +2362,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2378,12 +2393,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2543,10 +2558,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122422959</v>
+        <v>122423191</v>
       </c>
       <c r="B16" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2559,42 +2574,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508833</v>
+        <v>508859</v>
       </c>
       <c r="R16" t="n">
-        <v>7008097</v>
+        <v>7008134</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2652,12 +2662,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2675,7 +2685,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122423711</v>
+        <v>122428118</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2715,13 +2725,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509001</v>
+        <v>508595</v>
       </c>
       <c r="R17" t="n">
-        <v>7008256</v>
+        <v>7008516</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2753,6 +2763,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2764,7 +2779,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2802,10 +2817,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122427142</v>
+        <v>122423113</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,37 +2833,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508688</v>
+        <v>508834</v>
       </c>
       <c r="R18" t="n">
-        <v>7008395</v>
+        <v>7008115</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2880,6 +2905,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2891,7 +2921,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2906,12 +2936,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3061,10 +3091,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423935</v>
+        <v>122422959</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3077,44 +3107,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508980</v>
+        <v>508833</v>
       </c>
       <c r="R20" t="n">
-        <v>7008294</v>
+        <v>7008097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3149,11 +3174,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3165,7 +3185,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3180,12 +3200,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3203,10 +3223,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122428937</v>
+        <v>122430904</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3219,42 +3239,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508739</v>
+        <v>508916</v>
       </c>
       <c r="R21" t="n">
-        <v>7008454</v>
+        <v>7008122</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3284,11 +3299,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3340,7 +3350,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427227</v>
+        <v>122423467</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -3376,17 +3386,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508639</v>
+        <v>508900</v>
       </c>
       <c r="R22" t="n">
-        <v>7008388</v>
+        <v>7008203</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3434,12 +3444,12 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3449,7 +3459,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3467,7 +3477,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122423040</v>
+        <v>122429239</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3503,7 +3513,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3513,14 +3523,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508845</v>
+        <v>508765</v>
       </c>
       <c r="R23" t="n">
-        <v>7008072</v>
+        <v>7008466</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -3557,7 +3567,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3609,10 +3619,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122423626</v>
+        <v>122424772</v>
       </c>
       <c r="B24" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3625,31 +3635,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3663,10 +3669,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508994</v>
+        <v>508770</v>
       </c>
       <c r="R24" t="n">
-        <v>7008252</v>
+        <v>7008381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,7 +3709,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3718,6 +3724,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3735,10 +3761,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122424637</v>
+        <v>122423935</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3751,34 +3777,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508814</v>
+        <v>508980</v>
       </c>
       <c r="R25" t="n">
-        <v>7008416</v>
+        <v>7008294</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,6 +3849,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3839,12 +3880,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3862,10 +3903,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122426582</v>
+        <v>122423588</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3878,44 +3919,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508771</v>
+        <v>508975</v>
       </c>
       <c r="R26" t="n">
-        <v>7008433</v>
+        <v>7008243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3950,11 +3981,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3981,12 +4007,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4004,10 +4030,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122426951</v>
+        <v>122429024</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4020,42 +4046,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508719</v>
+        <v>508746</v>
       </c>
       <c r="R27" t="n">
-        <v>7008377</v>
+        <v>7008449</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4087,11 +4108,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4118,12 +4134,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4141,7 +4157,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122429398</v>
+        <v>122423287</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -4177,17 +4193,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508809</v>
+        <v>508887</v>
       </c>
       <c r="R28" t="n">
-        <v>7008468</v>
+        <v>7008167</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4230,7 +4246,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4245,12 +4261,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4268,10 +4284,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423191</v>
+        <v>122423040</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4284,37 +4300,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508859</v>
+        <v>508845</v>
       </c>
       <c r="R29" t="n">
-        <v>7008134</v>
+        <v>7008072</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4346,6 +4372,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4357,7 +4388,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4372,12 +4403,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4395,10 +4426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423811</v>
+        <v>122423711</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4411,44 +4442,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508995</v>
+        <v>509001</v>
       </c>
       <c r="R30" t="n">
-        <v>7008282</v>
+        <v>7008256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4483,11 +4504,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4514,12 +4530,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4537,7 +4553,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122423287</v>
+        <v>122427227</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -4573,17 +4589,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508887</v>
+        <v>508639</v>
       </c>
       <c r="R31" t="n">
-        <v>7008167</v>
+        <v>7008388</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4631,12 +4647,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4646,7 +4662,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4664,10 +4680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122424772</v>
+        <v>122423626</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4680,27 +4696,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4714,10 +4734,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508770</v>
+        <v>508994</v>
       </c>
       <c r="R32" t="n">
-        <v>7008381</v>
+        <v>7008252</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4754,7 +4774,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4769,26 +4789,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122423467</v>
+        <v>122424637</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -4842,17 +4842,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508900</v>
+        <v>508814</v>
       </c>
       <c r="R33" t="n">
-        <v>7008203</v>
+        <v>7008416</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429949</v>
+        <v>122423202</v>
       </c>
       <c r="B34" t="n">
         <v>57383</v>
@@ -4977,14 +4977,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508963</v>
+        <v>508881</v>
       </c>
       <c r="R34" t="n">
-        <v>7008307</v>
+        <v>7008130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122429210</v>
+        <v>122429949</v>
       </c>
       <c r="B35" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5089,26 +5089,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509071</v>
+        <v>508963</v>
       </c>
       <c r="R35" t="n">
-        <v>7008310</v>
+        <v>7008307</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5156,7 +5161,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5165,7 +5170,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5184,9 +5188,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5204,10 +5213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122429607</v>
+        <v>122428462</v>
       </c>
       <c r="B36" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5220,21 +5229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5247,10 +5256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509034</v>
+        <v>509040</v>
       </c>
       <c r="R36" t="n">
-        <v>7008306</v>
+        <v>7008336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5302,17 +5311,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5330,7 +5344,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122424038</v>
+        <v>122430707</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -5378,10 +5392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508954</v>
+        <v>508959</v>
       </c>
       <c r="R37" t="n">
-        <v>7008336</v>
+        <v>7008280</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5470,7 +5484,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423808</v>
+        <v>122424126</v>
       </c>
       <c r="B38" t="n">
         <v>57383</v>
@@ -5518,10 +5532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508966</v>
+        <v>508950</v>
       </c>
       <c r="R38" t="n">
-        <v>7008356</v>
+        <v>7008334</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5610,7 +5624,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122423524</v>
+        <v>122423808</v>
       </c>
       <c r="B39" t="n">
         <v>57383</v>
@@ -5654,14 +5668,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508928</v>
+        <v>508966</v>
       </c>
       <c r="R39" t="n">
-        <v>7008172</v>
+        <v>7008356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5698,7 +5712,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5712,17 +5726,17 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -5732,7 +5746,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5750,10 +5764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430040</v>
+        <v>122428725</v>
       </c>
       <c r="B40" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5766,50 +5780,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508930</v>
+        <v>508919</v>
       </c>
       <c r="R40" t="n">
-        <v>7008316</v>
+        <v>7008295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5844,6 +5850,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5856,6 +5867,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5873,10 +5904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122428777</v>
+        <v>122424453</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5889,28 +5920,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5920,10 +5952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508909</v>
+        <v>508908</v>
       </c>
       <c r="R41" t="n">
-        <v>7008302</v>
+        <v>7008354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5958,13 +5990,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5975,22 +6011,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6008,7 +6044,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122428831</v>
+        <v>122424038</v>
       </c>
       <c r="B42" t="n">
         <v>57383</v>
@@ -6056,10 +6092,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508914</v>
+        <v>508954</v>
       </c>
       <c r="R42" t="n">
-        <v>7008313</v>
+        <v>7008336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6148,7 +6184,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122424328</v>
+        <v>122429210</v>
       </c>
       <c r="B43" t="n">
         <v>79737</v>
@@ -6191,10 +6227,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508904</v>
+        <v>509071</v>
       </c>
       <c r="R43" t="n">
-        <v>7008325</v>
+        <v>7008310</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6279,10 +6315,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122428462</v>
+        <v>122428487</v>
       </c>
       <c r="B44" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6291,25 +6327,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6322,10 +6358,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509040</v>
+        <v>509041</v>
       </c>
       <c r="R44" t="n">
-        <v>7008336</v>
+        <v>7008337</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6410,10 +6446,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122423979</v>
+        <v>122429607</v>
       </c>
       <c r="B45" t="n">
-        <v>57536</v>
+        <v>82443</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6426,50 +6462,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508958</v>
+        <v>509034</v>
       </c>
       <c r="R45" t="n">
-        <v>7008338</v>
+        <v>7008306</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6510,12 +6533,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6533,10 +6572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122423202</v>
+        <v>122424328</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6549,42 +6588,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508881</v>
+        <v>508904</v>
       </c>
       <c r="R46" t="n">
-        <v>7008130</v>
+        <v>7008325</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6621,7 +6655,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6630,6 +6664,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6648,14 +6683,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6673,7 +6703,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428923</v>
+        <v>122423524</v>
       </c>
       <c r="B47" t="n">
         <v>57383</v>
@@ -6717,14 +6747,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508978</v>
+        <v>508928</v>
       </c>
       <c r="R47" t="n">
-        <v>7008270</v>
+        <v>7008172</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6761,7 +6791,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6775,17 +6805,17 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -6795,7 +6825,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6813,7 +6843,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122422848</v>
+        <v>122430628</v>
       </c>
       <c r="B48" t="n">
         <v>57383</v>
@@ -6857,14 +6887,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508847</v>
+        <v>508965</v>
       </c>
       <c r="R48" t="n">
-        <v>7008039</v>
+        <v>7008296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6953,7 +6983,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428725</v>
+        <v>122429553</v>
       </c>
       <c r="B49" t="n">
         <v>57383</v>
@@ -7001,10 +7031,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508919</v>
+        <v>509048</v>
       </c>
       <c r="R49" t="n">
-        <v>7008295</v>
+        <v>7008315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7093,7 +7123,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122430707</v>
+        <v>122428831</v>
       </c>
       <c r="B50" t="n">
         <v>57383</v>
@@ -7141,10 +7171,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508959</v>
+        <v>508914</v>
       </c>
       <c r="R50" t="n">
-        <v>7008280</v>
+        <v>7008313</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7233,7 +7263,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122424126</v>
+        <v>122423484</v>
       </c>
       <c r="B51" t="n">
         <v>57383</v>
@@ -7277,14 +7307,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508950</v>
+        <v>508920</v>
       </c>
       <c r="R51" t="n">
-        <v>7008334</v>
+        <v>7008181</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7321,7 +7351,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7335,17 +7365,17 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -7355,7 +7385,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7373,7 +7403,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122423484</v>
+        <v>122422848</v>
       </c>
       <c r="B52" t="n">
         <v>57383</v>
@@ -7421,10 +7451,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508920</v>
+        <v>508847</v>
       </c>
       <c r="R52" t="n">
-        <v>7008181</v>
+        <v>7008039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7461,7 +7491,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7475,17 +7505,17 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7495,7 +7525,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7513,7 +7543,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122429553</v>
+        <v>122428923</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -7561,10 +7591,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509048</v>
+        <v>508978</v>
       </c>
       <c r="R53" t="n">
-        <v>7008315</v>
+        <v>7008270</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7653,10 +7683,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428487</v>
+        <v>122430040</v>
       </c>
       <c r="B54" t="n">
-        <v>79773</v>
+        <v>57536</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7665,41 +7695,54 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509041</v>
+        <v>508930</v>
       </c>
       <c r="R54" t="n">
-        <v>7008337</v>
+        <v>7008316</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7740,33 +7783,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7784,10 +7806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122424453</v>
+        <v>122428777</v>
       </c>
       <c r="B55" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7800,29 +7822,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7832,10 +7853,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508908</v>
+        <v>508909</v>
       </c>
       <c r="R55" t="n">
-        <v>7008354</v>
+        <v>7008302</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7870,17 +7891,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7891,22 +7908,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7924,10 +7941,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430628</v>
+        <v>122423979</v>
       </c>
       <c r="B56" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7940,42 +7957,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508965</v>
+        <v>508958</v>
       </c>
       <c r="R56" t="n">
-        <v>7008296</v>
+        <v>7008338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8010,11 +8035,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8027,26 +8047,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427444</v>
+        <v>122424676</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8080,26 +8080,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8107,10 +8112,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508541</v>
+        <v>508779</v>
       </c>
       <c r="R57" t="n">
-        <v>7008422</v>
+        <v>7008383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8147,7 +8152,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8156,33 +8161,27 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8200,7 +8199,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424611</v>
+        <v>122427586</v>
       </c>
       <c r="B58" t="n">
         <v>57383</v>
@@ -8248,10 +8247,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508820</v>
+        <v>508745</v>
       </c>
       <c r="R58" t="n">
-        <v>7008398</v>
+        <v>7008511</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8315,14 +8314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8340,7 +8334,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122429281</v>
+        <v>122427763</v>
       </c>
       <c r="B59" t="n">
         <v>57383</v>
@@ -8378,7 +8372,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8388,10 +8382,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>509109</v>
+        <v>508776</v>
       </c>
       <c r="R59" t="n">
-        <v>7008253</v>
+        <v>7008533</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8428,7 +8422,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8455,9 +8449,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8475,7 +8474,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122426823</v>
+        <v>122429281</v>
       </c>
       <c r="B60" t="n">
         <v>57383</v>
@@ -8513,7 +8512,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8523,10 +8522,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508614</v>
+        <v>509109</v>
       </c>
       <c r="R60" t="n">
-        <v>7008464</v>
+        <v>7008253</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8563,7 +8562,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8590,14 +8589,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8615,10 +8609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427763</v>
+        <v>122426947</v>
       </c>
       <c r="B61" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8631,16 +8625,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8648,12 +8642,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8663,10 +8661,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508776</v>
+        <v>508535</v>
       </c>
       <c r="R61" t="n">
-        <v>7008533</v>
+        <v>7008440</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8701,11 +8699,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8717,27 +8710,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8755,7 +8728,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424676</v>
+        <v>122427127</v>
       </c>
       <c r="B62" t="n">
         <v>57383</v>
@@ -8803,10 +8776,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508779</v>
+        <v>508631</v>
       </c>
       <c r="R62" t="n">
-        <v>7008383</v>
+        <v>7008480</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8843,7 +8816,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8857,7 +8830,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8890,7 +8863,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424707</v>
+        <v>122426823</v>
       </c>
       <c r="B63" t="n">
         <v>57383</v>
@@ -8938,10 +8911,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508781</v>
+        <v>508614</v>
       </c>
       <c r="R63" t="n">
-        <v>7008382</v>
+        <v>7008464</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9030,10 +9003,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427586</v>
+        <v>122427444</v>
       </c>
       <c r="B64" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9046,31 +9019,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9078,10 +9046,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508745</v>
+        <v>508541</v>
       </c>
       <c r="R64" t="n">
-        <v>7008511</v>
+        <v>7008422</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9118,7 +9086,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9127,27 +9095,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9165,7 +9139,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427681</v>
+        <v>122424589</v>
       </c>
       <c r="B65" t="n">
         <v>57383</v>
@@ -9213,10 +9187,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508760</v>
+        <v>508831</v>
       </c>
       <c r="R65" t="n">
-        <v>7008533</v>
+        <v>7008397</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9305,7 +9279,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427127</v>
+        <v>122424496</v>
       </c>
       <c r="B66" t="n">
         <v>57383</v>
@@ -9353,10 +9327,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508631</v>
+        <v>508891</v>
       </c>
       <c r="R66" t="n">
-        <v>7008480</v>
+        <v>7008386</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9393,7 +9367,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9407,7 +9381,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9420,9 +9394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9440,10 +9419,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122426947</v>
+        <v>122427681</v>
       </c>
       <c r="B67" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9456,16 +9435,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -9473,16 +9452,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9492,10 +9467,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508535</v>
+        <v>508760</v>
       </c>
       <c r="R67" t="n">
-        <v>7008440</v>
+        <v>7008533</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9530,6 +9505,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9541,7 +9521,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424496</v>
+        <v>122424707</v>
       </c>
       <c r="B68" t="n">
         <v>57383</v>
@@ -9597,7 +9597,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508891</v>
+        <v>508781</v>
       </c>
       <c r="R68" t="n">
-        <v>7008386</v>
+        <v>7008382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424589</v>
+        <v>122424611</v>
       </c>
       <c r="B69" t="n">
         <v>57383</v>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508831</v>
+        <v>508820</v>
       </c>
       <c r="R69" t="n">
-        <v>7008397</v>
+        <v>7008398</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -2035,10 +2035,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427629</v>
+        <v>122423988</v>
       </c>
       <c r="B12" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2047,51 +2047,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508574</v>
+        <v>508982</v>
       </c>
       <c r="R12" t="n">
-        <v>7008461</v>
+        <v>7008301</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2134,7 +2124,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2152,10 +2162,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423988</v>
+        <v>122424389</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2168,37 +2178,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508982</v>
+        <v>508892</v>
       </c>
       <c r="R13" t="n">
-        <v>7008301</v>
+        <v>7008349</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2230,6 +2245,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2256,12 +2276,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2279,10 +2299,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122424389</v>
+        <v>122427629</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>97191</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2291,31 +2311,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2324,13 +2349,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508892</v>
+        <v>508574</v>
       </c>
       <c r="R14" t="n">
-        <v>7008349</v>
+        <v>7008461</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2362,11 +2387,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2378,27 +2398,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423588</v>
+        <v>122423040</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3919,37 +3919,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508975</v>
+        <v>508845</v>
       </c>
       <c r="R26" t="n">
-        <v>7008243</v>
+        <v>7008072</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3981,6 +3991,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4007,12 +4022,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4030,7 +4045,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122429024</v>
+        <v>122423588</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -4070,13 +4085,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508746</v>
+        <v>508975</v>
       </c>
       <c r="R27" t="n">
-        <v>7008449</v>
+        <v>7008243</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4157,7 +4172,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423287</v>
+        <v>122429024</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -4193,17 +4208,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508887</v>
+        <v>508746</v>
       </c>
       <c r="R28" t="n">
-        <v>7008167</v>
+        <v>7008449</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4246,7 +4261,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4284,10 +4299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423040</v>
+        <v>122423287</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4300,47 +4315,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508845</v>
+        <v>508887</v>
       </c>
       <c r="R29" t="n">
-        <v>7008072</v>
+        <v>7008167</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4372,11 +4377,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427142</v>
+        <v>122428118</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508688</v>
+        <v>508595</v>
       </c>
       <c r="R2" t="n">
-        <v>7008395</v>
+        <v>7008516</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122423811</v>
+        <v>122426743</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,44 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508995</v>
+        <v>508764</v>
       </c>
       <c r="R3" t="n">
-        <v>7008282</v>
+        <v>7008423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122426582</v>
+        <v>122429268</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,16 +955,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508771</v>
+        <v>508765</v>
       </c>
       <c r="R4" t="n">
-        <v>7008433</v>
+        <v>7008461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,12 +1058,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1086,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122428937</v>
+        <v>122427629</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>97191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,31 +1093,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508739</v>
+        <v>508574</v>
       </c>
       <c r="R5" t="n">
-        <v>7008454</v>
+        <v>7008461</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1169,11 +1169,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1185,27 +1180,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122422838</v>
+        <v>122423588</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,47 +1214,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508855</v>
+        <v>508975</v>
       </c>
       <c r="R6" t="n">
-        <v>7008046</v>
+        <v>7008243</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,11 +1276,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1342,12 +1302,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122423133</v>
+        <v>122424308</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,47 +1341,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508834</v>
+        <v>508903</v>
       </c>
       <c r="R7" t="n">
-        <v>7008117</v>
+        <v>7008351</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1405,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,12 +1434,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1507,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429398</v>
+        <v>122428937</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,37 +1473,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508809</v>
+        <v>508739</v>
       </c>
       <c r="R8" t="n">
-        <v>7008468</v>
+        <v>7008454</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1585,6 +1540,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1611,12 +1571,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1634,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122424114</v>
+        <v>122423133</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1650,37 +1610,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508968</v>
+        <v>508834</v>
       </c>
       <c r="R9" t="n">
-        <v>7008319</v>
+        <v>7008117</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1714,7 +1684,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1743,12 +1713,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1766,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122424308</v>
+        <v>122423811</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1782,37 +1752,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508903</v>
+        <v>508995</v>
       </c>
       <c r="R10" t="n">
-        <v>7008351</v>
+        <v>7008282</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1846,7 +1826,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,12 +1855,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1898,10 +1878,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122426951</v>
+        <v>122423711</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1914,39 +1894,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508719</v>
+        <v>509001</v>
       </c>
       <c r="R11" t="n">
-        <v>7008377</v>
+        <v>7008256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1981,11 +1956,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2012,12 +1982,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2035,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423988</v>
+        <v>122424772</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2051,34 +2021,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508982</v>
+        <v>508770</v>
       </c>
       <c r="R12" t="n">
-        <v>7008301</v>
+        <v>7008381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2113,6 +2093,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2139,12 +2124,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2162,7 +2147,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122424389</v>
+        <v>122423040</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2201,16 +2186,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508892</v>
+        <v>508845</v>
       </c>
       <c r="R13" t="n">
-        <v>7008349</v>
+        <v>7008072</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2247,7 +2237,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2299,10 +2289,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122427629</v>
+        <v>122427227</v>
       </c>
       <c r="B14" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2311,51 +2301,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508574</v>
+        <v>508639</v>
       </c>
       <c r="R14" t="n">
-        <v>7008461</v>
+        <v>7008388</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2399,6 +2379,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122429268</v>
+        <v>122429398</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2432,44 +2432,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508765</v>
+        <v>508809</v>
       </c>
       <c r="R15" t="n">
-        <v>7008461</v>
+        <v>7008468</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2504,11 +2494,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2535,12 +2520,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2558,7 +2543,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423191</v>
+        <v>122424114</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2594,17 +2579,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508859</v>
+        <v>508968</v>
       </c>
       <c r="R16" t="n">
-        <v>7008134</v>
+        <v>7008319</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2636,6 +2621,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2647,7 +2637,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2662,12 +2652,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2685,7 +2675,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122428118</v>
+        <v>122430904</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2721,17 +2711,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508595</v>
+        <v>508916</v>
       </c>
       <c r="R17" t="n">
-        <v>7008516</v>
+        <v>7008122</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2763,11 +2753,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2779,7 +2764,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2794,12 +2779,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2817,10 +2802,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423113</v>
+        <v>122426582</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2833,16 +2818,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2863,17 +2848,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508834</v>
+        <v>508771</v>
       </c>
       <c r="R18" t="n">
-        <v>7008115</v>
+        <v>7008433</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2907,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2936,12 +2921,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2959,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122426743</v>
+        <v>122424389</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2975,37 +2960,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508764</v>
+        <v>508892</v>
       </c>
       <c r="R19" t="n">
-        <v>7008423</v>
+        <v>7008349</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3039,7 +3029,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3068,12 +3058,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3091,10 +3081,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122422959</v>
+        <v>122422838</v>
       </c>
       <c r="B20" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3107,27 +3097,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3136,13 +3131,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508833</v>
+        <v>508855</v>
       </c>
       <c r="R20" t="n">
-        <v>7008097</v>
+        <v>7008046</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3174,6 +3169,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122430904</v>
+        <v>122424637</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -3259,14 +3259,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508916</v>
+        <v>508814</v>
       </c>
       <c r="R21" t="n">
-        <v>7008122</v>
+        <v>7008416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122423467</v>
+        <v>122423287</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508900</v>
+        <v>508887</v>
       </c>
       <c r="R22" t="n">
-        <v>7008203</v>
+        <v>7008167</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122429239</v>
+        <v>122423191</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3493,47 +3493,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508765</v>
+        <v>508859</v>
       </c>
       <c r="R23" t="n">
-        <v>7008466</v>
+        <v>7008134</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3565,11 +3555,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack främst på stambasen.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3581,7 +3566,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3596,12 +3581,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3619,10 +3604,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424772</v>
+        <v>122427142</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3635,44 +3620,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508770</v>
+        <v>508688</v>
       </c>
       <c r="R24" t="n">
-        <v>7008381</v>
+        <v>7008395</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3707,11 +3682,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3723,7 +3693,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3738,12 +3708,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3761,7 +3731,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423935</v>
+        <v>122429239</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3797,7 +3767,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3811,13 +3781,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508980</v>
+        <v>508765</v>
       </c>
       <c r="R25" t="n">
-        <v>7008294</v>
+        <v>7008466</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3851,7 +3821,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3903,10 +3873,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423040</v>
+        <v>122423626</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3919,27 +3889,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3949,17 +3923,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508845</v>
+        <v>508994</v>
       </c>
       <c r="R26" t="n">
-        <v>7008072</v>
+        <v>7008252</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3993,7 +3967,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4008,26 +3982,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4045,10 +3999,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423588</v>
+        <v>122423935</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4061,34 +4015,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508975</v>
+        <v>508980</v>
       </c>
       <c r="R27" t="n">
-        <v>7008243</v>
+        <v>7008294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4123,6 +4087,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4149,12 +4118,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4299,7 +4268,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423287</v>
+        <v>122423988</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -4335,17 +4304,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508887</v>
+        <v>508982</v>
       </c>
       <c r="R29" t="n">
-        <v>7008167</v>
+        <v>7008301</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4388,7 +4357,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4426,10 +4395,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423711</v>
+        <v>122422959</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4442,34 +4411,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509001</v>
+        <v>508833</v>
       </c>
       <c r="R30" t="n">
-        <v>7008256</v>
+        <v>7008097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4515,7 +4489,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4530,12 +4504,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4553,7 +4527,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122427227</v>
+        <v>122423467</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -4589,17 +4563,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508639</v>
+        <v>508900</v>
       </c>
       <c r="R31" t="n">
-        <v>7008388</v>
+        <v>7008203</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4647,12 +4621,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4662,7 +4636,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4680,10 +4654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423626</v>
+        <v>122426951</v>
       </c>
       <c r="B32" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4696,36 +4670,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4734,10 +4699,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508994</v>
+        <v>508719</v>
       </c>
       <c r="R32" t="n">
-        <v>7008252</v>
+        <v>7008377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4774,7 +4739,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4789,6 +4754,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4806,10 +4791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122424637</v>
+        <v>122423113</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4822,37 +4807,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508814</v>
+        <v>508834</v>
       </c>
       <c r="R33" t="n">
-        <v>7008416</v>
+        <v>7008115</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4884,6 +4879,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423202</v>
+        <v>122429607</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4949,42 +4949,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508881</v>
+        <v>509034</v>
       </c>
       <c r="R34" t="n">
-        <v>7008130</v>
+        <v>7008306</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5019,17 +5014,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5048,14 +5039,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5073,10 +5059,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122429949</v>
+        <v>122423979</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5089,42 +5075,50 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508963</v>
+        <v>508958</v>
       </c>
       <c r="R35" t="n">
-        <v>7008307</v>
+        <v>7008338</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5159,11 +5153,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5176,26 +5165,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,10 +5182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122428462</v>
+        <v>122424038</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5229,26 +5198,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5256,7 +5230,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509040</v>
+        <v>508954</v>
       </c>
       <c r="R36" t="n">
         <v>7008336</v>
@@ -5294,13 +5268,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5311,22 +5289,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5344,7 +5322,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430707</v>
+        <v>122423484</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -5388,14 +5366,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508959</v>
+        <v>508920</v>
       </c>
       <c r="R37" t="n">
-        <v>7008280</v>
+        <v>7008181</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5432,7 +5410,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5446,17 +5424,17 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -5466,7 +5444,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5484,7 +5462,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122424126</v>
+        <v>122429553</v>
       </c>
       <c r="B38" t="n">
         <v>57383</v>
@@ -5532,10 +5510,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508950</v>
+        <v>509048</v>
       </c>
       <c r="R38" t="n">
-        <v>7008334</v>
+        <v>7008315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5624,10 +5602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122423808</v>
+        <v>122428462</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5640,31 +5618,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5672,10 +5645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508966</v>
+        <v>509040</v>
       </c>
       <c r="R39" t="n">
-        <v>7008356</v>
+        <v>7008336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5710,17 +5683,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5731,22 +5700,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5764,7 +5733,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122428725</v>
+        <v>122423808</v>
       </c>
       <c r="B40" t="n">
         <v>57383</v>
@@ -5812,10 +5781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508919</v>
+        <v>508966</v>
       </c>
       <c r="R40" t="n">
-        <v>7008295</v>
+        <v>7008356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5904,7 +5873,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122424453</v>
+        <v>122430707</v>
       </c>
       <c r="B41" t="n">
         <v>57383</v>
@@ -5952,10 +5921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508908</v>
+        <v>508959</v>
       </c>
       <c r="R41" t="n">
-        <v>7008354</v>
+        <v>7008280</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6044,7 +6013,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122424038</v>
+        <v>122422848</v>
       </c>
       <c r="B42" t="n">
         <v>57383</v>
@@ -6088,14 +6057,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508954</v>
+        <v>508847</v>
       </c>
       <c r="R42" t="n">
-        <v>7008336</v>
+        <v>7008039</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6184,10 +6153,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429210</v>
+        <v>122423202</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6200,37 +6169,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509071</v>
+        <v>508881</v>
       </c>
       <c r="R43" t="n">
-        <v>7008310</v>
+        <v>7008130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6267,7 +6241,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6276,7 +6250,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6295,9 +6268,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6446,10 +6424,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122429607</v>
+        <v>122424328</v>
       </c>
       <c r="B45" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6462,21 +6440,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6489,10 +6467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509034</v>
+        <v>508904</v>
       </c>
       <c r="R45" t="n">
-        <v>7008306</v>
+        <v>7008325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6525,6 +6503,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6572,10 +6555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122424328</v>
+        <v>122428831</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6588,26 +6571,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6615,10 +6603,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508904</v>
+        <v>508914</v>
       </c>
       <c r="R46" t="n">
-        <v>7008325</v>
+        <v>7008313</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6655,7 +6643,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6664,7 +6652,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6683,9 +6670,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6703,10 +6695,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122423524</v>
+        <v>122429210</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6719,42 +6711,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508928</v>
+        <v>509071</v>
       </c>
       <c r="R47" t="n">
-        <v>7008172</v>
+        <v>7008310</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6791,7 +6778,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6800,32 +6787,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6983,10 +6966,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122429553</v>
+        <v>122428777</v>
       </c>
       <c r="B49" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6999,29 +6982,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -7031,10 +7013,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>509048</v>
+        <v>508909</v>
       </c>
       <c r="R49" t="n">
-        <v>7008315</v>
+        <v>7008302</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7069,17 +7051,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7090,22 +7068,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7123,7 +7101,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122428831</v>
+        <v>122429949</v>
       </c>
       <c r="B50" t="n">
         <v>57383</v>
@@ -7171,10 +7149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508914</v>
+        <v>508963</v>
       </c>
       <c r="R50" t="n">
-        <v>7008313</v>
+        <v>7008307</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7263,7 +7241,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122423484</v>
+        <v>122423524</v>
       </c>
       <c r="B51" t="n">
         <v>57383</v>
@@ -7311,10 +7289,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508920</v>
+        <v>508928</v>
       </c>
       <c r="R51" t="n">
-        <v>7008181</v>
+        <v>7008172</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7403,7 +7381,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122422848</v>
+        <v>122424453</v>
       </c>
       <c r="B52" t="n">
         <v>57383</v>
@@ -7447,14 +7425,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508847</v>
+        <v>508908</v>
       </c>
       <c r="R52" t="n">
-        <v>7008039</v>
+        <v>7008354</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7683,10 +7661,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122430040</v>
+        <v>122428725</v>
       </c>
       <c r="B54" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7699,50 +7677,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508930</v>
+        <v>508919</v>
       </c>
       <c r="R54" t="n">
-        <v>7008316</v>
+        <v>7008295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7777,6 +7747,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7789,6 +7764,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7806,10 +7801,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428777</v>
+        <v>122424126</v>
       </c>
       <c r="B55" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7822,28 +7817,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7853,10 +7849,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508909</v>
+        <v>508950</v>
       </c>
       <c r="R55" t="n">
-        <v>7008302</v>
+        <v>7008334</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7891,13 +7887,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7908,22 +7908,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122423979</v>
+        <v>122430040</v>
       </c>
       <c r="B56" t="n">
         <v>57536</v>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508958</v>
+        <v>508930</v>
       </c>
       <c r="R56" t="n">
-        <v>7008338</v>
+        <v>7008316</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122424676</v>
+        <v>122427127</v>
       </c>
       <c r="B57" t="n">
         <v>57383</v>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508779</v>
+        <v>508631</v>
       </c>
       <c r="R57" t="n">
-        <v>7008383</v>
+        <v>7008480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8199,10 +8199,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427586</v>
+        <v>122426947</v>
       </c>
       <c r="B58" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8215,16 +8215,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8232,12 +8232,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8247,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508745</v>
+        <v>508535</v>
       </c>
       <c r="R58" t="n">
-        <v>7008511</v>
+        <v>7008440</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8285,11 +8289,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8301,22 +8300,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8334,7 +8318,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427763</v>
+        <v>122429281</v>
       </c>
       <c r="B59" t="n">
         <v>57383</v>
@@ -8372,7 +8356,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8382,10 +8366,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508776</v>
+        <v>509109</v>
       </c>
       <c r="R59" t="n">
-        <v>7008533</v>
+        <v>7008253</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8422,7 +8406,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8449,14 +8433,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8474,7 +8453,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122429281</v>
+        <v>122424611</v>
       </c>
       <c r="B60" t="n">
         <v>57383</v>
@@ -8522,10 +8501,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>509109</v>
+        <v>508820</v>
       </c>
       <c r="R60" t="n">
-        <v>7008253</v>
+        <v>7008398</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8589,9 +8568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8609,10 +8593,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122426947</v>
+        <v>122427681</v>
       </c>
       <c r="B61" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8625,16 +8609,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8642,16 +8626,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8661,10 +8641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508535</v>
+        <v>508760</v>
       </c>
       <c r="R61" t="n">
-        <v>7008440</v>
+        <v>7008533</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8699,6 +8679,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8710,7 +8695,27 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8728,10 +8733,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427127</v>
+        <v>122427444</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8744,31 +8749,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508631</v>
+        <v>508541</v>
       </c>
       <c r="R62" t="n">
-        <v>7008480</v>
+        <v>7008422</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8825,27 +8825,33 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8863,7 +8869,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426823</v>
+        <v>122424496</v>
       </c>
       <c r="B63" t="n">
         <v>57383</v>
@@ -8901,7 +8907,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8911,10 +8917,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508614</v>
+        <v>508891</v>
       </c>
       <c r="R63" t="n">
-        <v>7008464</v>
+        <v>7008386</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8951,7 +8957,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8980,12 +8986,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9003,10 +9009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427444</v>
+        <v>122424707</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9019,26 +9025,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9046,10 +9057,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508541</v>
+        <v>508781</v>
       </c>
       <c r="R64" t="n">
-        <v>7008422</v>
+        <v>7008382</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9086,7 +9097,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9095,33 +9106,32 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9279,7 +9289,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424496</v>
+        <v>122427586</v>
       </c>
       <c r="B66" t="n">
         <v>57383</v>
@@ -9327,10 +9337,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508891</v>
+        <v>508745</v>
       </c>
       <c r="R66" t="n">
-        <v>7008386</v>
+        <v>7008511</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9394,14 +9404,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9419,7 +9424,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427681</v>
+        <v>122427763</v>
       </c>
       <c r="B67" t="n">
         <v>57383</v>
@@ -9457,7 +9462,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9467,7 +9472,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508760</v>
+        <v>508776</v>
       </c>
       <c r="R67" t="n">
         <v>7008533</v>
@@ -9507,7 +9512,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9559,7 +9564,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424707</v>
+        <v>122424676</v>
       </c>
       <c r="B68" t="n">
         <v>57383</v>
@@ -9597,7 +9602,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9607,10 +9612,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508781</v>
+        <v>508779</v>
       </c>
       <c r="R68" t="n">
-        <v>7008382</v>
+        <v>7008383</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9647,7 +9652,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9674,14 +9679,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424611</v>
+        <v>122426823</v>
       </c>
       <c r="B69" t="n">
         <v>57383</v>
@@ -9737,7 +9737,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508820</v>
+        <v>508614</v>
       </c>
       <c r="R69" t="n">
-        <v>7008398</v>
+        <v>7008464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -2416,10 +2416,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122429398</v>
+        <v>122426582</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2432,34 +2432,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508809</v>
+        <v>508771</v>
       </c>
       <c r="R15" t="n">
-        <v>7008468</v>
+        <v>7008433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2494,6 +2504,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2520,12 +2535,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,10 +2558,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122424114</v>
+        <v>122424389</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2559,37 +2574,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508968</v>
+        <v>508892</v>
       </c>
       <c r="R16" t="n">
-        <v>7008319</v>
+        <v>7008349</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2623,7 +2643,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2652,12 +2672,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2675,10 +2695,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122430904</v>
+        <v>122422838</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2691,37 +2711,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508916</v>
+        <v>508855</v>
       </c>
       <c r="R17" t="n">
-        <v>7008122</v>
+        <v>7008046</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2751,6 +2781,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2802,10 +2837,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122426582</v>
+        <v>122429398</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,44 +2853,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508771</v>
+        <v>508809</v>
       </c>
       <c r="R18" t="n">
-        <v>7008433</v>
+        <v>7008468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2890,11 +2915,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2921,12 +2941,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,10 +2964,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122424389</v>
+        <v>122424114</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2960,42 +2980,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508892</v>
+        <v>508968</v>
       </c>
       <c r="R19" t="n">
-        <v>7008349</v>
+        <v>7008319</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3029,7 +3044,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3058,12 +3073,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3081,10 +3096,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122422838</v>
+        <v>122430904</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3097,47 +3112,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508855</v>
+        <v>508916</v>
       </c>
       <c r="R20" t="n">
-        <v>7008046</v>
+        <v>7008122</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3167,11 +3172,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122423467</v>
+        <v>122426951</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4543,37 +4543,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508900</v>
+        <v>508719</v>
       </c>
       <c r="R31" t="n">
-        <v>7008203</v>
+        <v>7008377</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4605,6 +4610,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4616,7 +4626,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4631,12 +4641,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4654,7 +4664,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122426951</v>
+        <v>122423113</v>
       </c>
       <c r="B32" t="n">
         <v>57383</v>
@@ -4693,19 +4703,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508719</v>
+        <v>508834</v>
       </c>
       <c r="R32" t="n">
-        <v>7008377</v>
+        <v>7008115</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4739,7 +4754,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4768,12 +4783,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4791,10 +4806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122423113</v>
+        <v>122423467</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4807,44 +4822,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508834</v>
+        <v>508900</v>
       </c>
       <c r="R33" t="n">
-        <v>7008115</v>
+        <v>7008203</v>
       </c>
       <c r="S33" t="n">
         <v>8</v>
@@ -4879,11 +4884,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428831</v>
+        <v>122429210</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6571,31 +6571,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6603,10 +6598,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508914</v>
+        <v>509071</v>
       </c>
       <c r="R46" t="n">
-        <v>7008313</v>
+        <v>7008310</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6643,7 +6638,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6652,6 +6647,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6670,14 +6666,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6695,10 +6686,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429210</v>
+        <v>122428831</v>
       </c>
       <c r="B47" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6711,26 +6702,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6738,10 +6734,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509071</v>
+        <v>508914</v>
       </c>
       <c r="R47" t="n">
-        <v>7008310</v>
+        <v>7008313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6778,7 +6774,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6787,7 +6783,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6806,9 +6801,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428118</v>
+        <v>122426743</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508595</v>
+        <v>508764</v>
       </c>
       <c r="R2" t="n">
-        <v>7008516</v>
+        <v>7008423</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -807,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122426743</v>
+        <v>122427227</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508764</v>
+        <v>508639</v>
       </c>
       <c r="R3" t="n">
-        <v>7008423</v>
+        <v>7008388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +885,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,17 +896,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -921,7 +916,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429268</v>
+        <v>122423935</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508765</v>
+        <v>508980</v>
       </c>
       <c r="R4" t="n">
-        <v>7008461</v>
+        <v>7008294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427629</v>
+        <v>122423711</v>
       </c>
       <c r="B5" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,51 +1088,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508574</v>
+        <v>509001</v>
       </c>
       <c r="R5" t="n">
-        <v>7008461</v>
+        <v>7008256</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1165,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122423588</v>
+        <v>122424308</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1238,13 +1243,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508975</v>
+        <v>508903</v>
       </c>
       <c r="R6" t="n">
-        <v>7008243</v>
+        <v>7008351</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,6 +1279,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,7 +1335,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122424308</v>
+        <v>122430904</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1361,17 +1371,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508903</v>
+        <v>508916</v>
       </c>
       <c r="R7" t="n">
-        <v>7008351</v>
+        <v>7008122</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1403,11 +1413,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1434,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122428937</v>
+        <v>122428118</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,39 +1478,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508739</v>
+        <v>508595</v>
       </c>
       <c r="R8" t="n">
-        <v>7008454</v>
+        <v>7008516</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423133</v>
+        <v>122423113</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1630,7 +1630,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1647,7 +1647,7 @@
         <v>508834</v>
       </c>
       <c r="R9" t="n">
-        <v>7008117</v>
+        <v>7008115</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,7 +1736,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423811</v>
+        <v>122428937</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1772,12 +1772,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1786,13 +1781,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508995</v>
+        <v>508739</v>
       </c>
       <c r="R10" t="n">
-        <v>7008282</v>
+        <v>7008454</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1826,7 +1821,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1878,7 +1873,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122423711</v>
+        <v>122423988</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509001</v>
+        <v>508982</v>
       </c>
       <c r="R11" t="n">
-        <v>7008256</v>
+        <v>7008301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2005,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122424772</v>
+        <v>122427629</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>97194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2017,31 +2012,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2055,13 +2050,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508770</v>
+        <v>508574</v>
       </c>
       <c r="R12" t="n">
-        <v>7008381</v>
+        <v>7008461</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2093,11 +2088,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2109,27 +2099,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2147,7 +2117,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423040</v>
+        <v>122426951</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2186,24 +2156,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508845</v>
+        <v>508719</v>
       </c>
       <c r="R13" t="n">
-        <v>7008072</v>
+        <v>7008377</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2237,7 +2202,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2266,12 +2231,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2289,10 +2254,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122427227</v>
+        <v>122429239</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2305,37 +2270,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508639</v>
+        <v>508765</v>
       </c>
       <c r="R14" t="n">
-        <v>7008388</v>
+        <v>7008466</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2367,6 +2342,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack främst på stambasen.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2378,27 +2358,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2416,10 +2396,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122426582</v>
+        <v>122423040</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2432,16 +2412,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2462,17 +2442,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508771</v>
+        <v>508845</v>
       </c>
       <c r="R15" t="n">
-        <v>7008433</v>
+        <v>7008072</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2506,7 +2486,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2535,12 +2515,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2558,10 +2538,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122424389</v>
+        <v>122423467</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2574,42 +2554,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508892</v>
+        <v>508900</v>
       </c>
       <c r="R16" t="n">
-        <v>7008349</v>
+        <v>7008203</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2641,11 +2616,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2657,7 +2627,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2672,12 +2642,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2695,10 +2665,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122422838</v>
+        <v>122423626</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2711,27 +2681,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2741,17 +2715,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508855</v>
+        <v>508994</v>
       </c>
       <c r="R17" t="n">
-        <v>7008046</v>
+        <v>7008252</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2785,7 +2759,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2800,26 +2774,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2837,7 +2791,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429398</v>
+        <v>122423191</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2873,17 +2827,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508809</v>
+        <v>508859</v>
       </c>
       <c r="R18" t="n">
-        <v>7008468</v>
+        <v>7008134</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2926,7 +2880,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2964,7 +2918,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122424114</v>
+        <v>122429398</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -3004,10 +2958,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508968</v>
+        <v>508809</v>
       </c>
       <c r="R19" t="n">
-        <v>7008319</v>
+        <v>7008468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3042,11 +2996,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3073,12 +3022,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3096,7 +3045,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122430904</v>
+        <v>122423287</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -3136,13 +3085,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508916</v>
+        <v>508887</v>
       </c>
       <c r="R20" t="n">
-        <v>7008122</v>
+        <v>7008167</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3185,7 +3134,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3200,12 +3149,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3223,10 +3172,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122424637</v>
+        <v>122424772</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3239,34 +3188,44 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508814</v>
+        <v>508770</v>
       </c>
       <c r="R21" t="n">
-        <v>7008416</v>
+        <v>7008381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3301,6 +3260,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3327,12 +3291,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3350,7 +3314,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122423287</v>
+        <v>122424637</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -3386,17 +3350,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508887</v>
+        <v>508814</v>
       </c>
       <c r="R22" t="n">
-        <v>7008167</v>
+        <v>7008416</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3439,7 +3403,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3477,10 +3441,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122423191</v>
+        <v>122422959</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3493,37 +3457,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508859</v>
+        <v>508833</v>
       </c>
       <c r="R23" t="n">
-        <v>7008134</v>
+        <v>7008097</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3581,12 +3550,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3604,7 +3573,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427142</v>
+        <v>122423588</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -3644,10 +3613,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508688</v>
+        <v>508975</v>
       </c>
       <c r="R24" t="n">
-        <v>7008395</v>
+        <v>7008243</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3693,7 +3662,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3708,12 +3677,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3731,7 +3700,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122429239</v>
+        <v>122423133</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3777,17 +3746,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508765</v>
+        <v>508834</v>
       </c>
       <c r="R25" t="n">
-        <v>7008466</v>
+        <v>7008117</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3821,7 +3790,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3873,10 +3842,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423626</v>
+        <v>122426582</v>
       </c>
       <c r="B26" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3889,31 +3858,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3927,10 +3892,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508994</v>
+        <v>508771</v>
       </c>
       <c r="R26" t="n">
-        <v>7008252</v>
+        <v>7008433</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3967,7 +3932,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3982,6 +3947,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3999,10 +3984,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423935</v>
+        <v>122429024</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4015,47 +4000,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508980</v>
+        <v>508746</v>
       </c>
       <c r="R27" t="n">
-        <v>7008294</v>
+        <v>7008449</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4087,11 +4062,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4118,12 +4088,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4141,7 +4111,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122429024</v>
+        <v>122427142</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -4181,13 +4151,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508746</v>
+        <v>508688</v>
       </c>
       <c r="R28" t="n">
-        <v>7008449</v>
+        <v>7008395</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4230,7 +4200,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4245,12 +4215,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4268,10 +4238,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423988</v>
+        <v>122429268</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4284,34 +4254,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508982</v>
+        <v>508765</v>
       </c>
       <c r="R29" t="n">
-        <v>7008301</v>
+        <v>7008461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4346,6 +4326,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4372,12 +4357,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4395,10 +4380,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122422959</v>
+        <v>122423811</v>
       </c>
       <c r="B30" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4411,39 +4396,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508833</v>
+        <v>508995</v>
       </c>
       <c r="R30" t="n">
-        <v>7008097</v>
+        <v>7008282</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4478,6 +4468,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4489,7 +4484,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4504,12 +4499,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4527,7 +4522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122426951</v>
+        <v>122422838</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -4566,19 +4561,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508719</v>
+        <v>508855</v>
       </c>
       <c r="R31" t="n">
-        <v>7008377</v>
+        <v>7008046</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423113</v>
+        <v>122424114</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4680,47 +4680,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508834</v>
+        <v>508968</v>
       </c>
       <c r="R32" t="n">
-        <v>7008115</v>
+        <v>7008319</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4754,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4783,12 +4773,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4806,10 +4796,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122423467</v>
+        <v>122424389</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4822,37 +4812,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508900</v>
+        <v>508892</v>
       </c>
       <c r="R33" t="n">
-        <v>7008203</v>
+        <v>7008349</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4884,6 +4879,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429607</v>
+        <v>122428777</v>
       </c>
       <c r="B34" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4949,26 +4949,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4976,10 +4980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509034</v>
+        <v>508909</v>
       </c>
       <c r="R34" t="n">
-        <v>7008306</v>
+        <v>7008302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5031,17 +5035,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5059,10 +5068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122423979</v>
+        <v>122423484</v>
       </c>
       <c r="B35" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5075,50 +5084,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508958</v>
+        <v>508920</v>
       </c>
       <c r="R35" t="n">
-        <v>7008338</v>
+        <v>7008181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5153,6 +5154,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5164,7 +5170,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5182,7 +5208,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424038</v>
+        <v>122428923</v>
       </c>
       <c r="B36" t="n">
         <v>57383</v>
@@ -5230,10 +5256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508954</v>
+        <v>508978</v>
       </c>
       <c r="R36" t="n">
-        <v>7008336</v>
+        <v>7008270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5322,7 +5348,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122423484</v>
+        <v>122428831</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -5366,14 +5392,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508920</v>
+        <v>508914</v>
       </c>
       <c r="R37" t="n">
-        <v>7008181</v>
+        <v>7008313</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5410,7 +5436,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5424,17 +5450,17 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -5444,7 +5470,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5462,10 +5488,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429553</v>
+        <v>122428462</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5478,31 +5504,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5510,10 +5531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509048</v>
+        <v>509040</v>
       </c>
       <c r="R38" t="n">
-        <v>7008315</v>
+        <v>7008336</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5548,17 +5569,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5569,22 +5586,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5602,10 +5619,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122428462</v>
+        <v>122430628</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5618,26 +5635,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5645,10 +5667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509040</v>
+        <v>508965</v>
       </c>
       <c r="R39" t="n">
-        <v>7008336</v>
+        <v>7008296</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5683,13 +5705,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5700,22 +5726,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5873,10 +5899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122430707</v>
+        <v>122429607</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5889,31 +5915,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5921,10 +5942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508959</v>
+        <v>509034</v>
       </c>
       <c r="R41" t="n">
-        <v>7008280</v>
+        <v>7008306</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5959,17 +5980,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5988,14 +6005,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6013,10 +6025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122422848</v>
+        <v>122423979</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6029,42 +6041,50 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508847</v>
+        <v>508958</v>
       </c>
       <c r="R42" t="n">
-        <v>7008039</v>
+        <v>7008338</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6099,11 +6119,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6116,26 +6131,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6153,7 +6148,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122423202</v>
+        <v>122429553</v>
       </c>
       <c r="B43" t="n">
         <v>57383</v>
@@ -6197,14 +6192,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508881</v>
+        <v>509048</v>
       </c>
       <c r="R43" t="n">
-        <v>7008130</v>
+        <v>7008315</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6293,10 +6288,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122428487</v>
+        <v>122430707</v>
       </c>
       <c r="B44" t="n">
-        <v>79773</v>
+        <v>57383</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6305,30 +6300,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509041</v>
+        <v>508959</v>
       </c>
       <c r="R44" t="n">
-        <v>7008337</v>
+        <v>7008280</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6374,13 +6374,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6391,22 +6395,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6424,7 +6428,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122424328</v>
+        <v>122424304</v>
       </c>
       <c r="B45" t="n">
         <v>79737</v>
@@ -6459,7 +6463,11 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6505,11 +6513,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6527,17 +6530,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6555,10 +6563,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429210</v>
+        <v>122428487</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6567,25 +6575,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6598,10 +6606,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509071</v>
+        <v>509041</v>
       </c>
       <c r="R46" t="n">
-        <v>7008310</v>
+        <v>7008337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6636,11 +6644,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6658,17 +6661,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6686,7 +6694,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428831</v>
+        <v>122429949</v>
       </c>
       <c r="B47" t="n">
         <v>57383</v>
@@ -6734,10 +6742,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508914</v>
+        <v>508963</v>
       </c>
       <c r="R47" t="n">
-        <v>7008313</v>
+        <v>7008307</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6826,7 +6834,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122430628</v>
+        <v>122423202</v>
       </c>
       <c r="B48" t="n">
         <v>57383</v>
@@ -6870,14 +6878,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508965</v>
+        <v>508881</v>
       </c>
       <c r="R48" t="n">
-        <v>7008296</v>
+        <v>7008130</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6966,10 +6974,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428777</v>
+        <v>122423524</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6982,41 +6990,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508909</v>
+        <v>508928</v>
       </c>
       <c r="R49" t="n">
-        <v>7008302</v>
+        <v>7008172</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7051,39 +7060,43 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7101,7 +7114,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429949</v>
+        <v>122424453</v>
       </c>
       <c r="B50" t="n">
         <v>57383</v>
@@ -7149,10 +7162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508963</v>
+        <v>508908</v>
       </c>
       <c r="R50" t="n">
-        <v>7008307</v>
+        <v>7008354</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7241,7 +7254,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122423524</v>
+        <v>122422848</v>
       </c>
       <c r="B51" t="n">
         <v>57383</v>
@@ -7289,10 +7302,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508928</v>
+        <v>508847</v>
       </c>
       <c r="R51" t="n">
-        <v>7008172</v>
+        <v>7008039</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7329,7 +7342,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7343,17 +7356,17 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -7363,7 +7376,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7381,7 +7394,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122424453</v>
+        <v>122424038</v>
       </c>
       <c r="B52" t="n">
         <v>57383</v>
@@ -7429,10 +7442,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508908</v>
+        <v>508954</v>
       </c>
       <c r="R52" t="n">
-        <v>7008354</v>
+        <v>7008336</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7521,7 +7534,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428923</v>
+        <v>122424126</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -7569,10 +7582,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508978</v>
+        <v>508950</v>
       </c>
       <c r="R53" t="n">
-        <v>7008270</v>
+        <v>7008334</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7661,10 +7674,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428725</v>
+        <v>122429210</v>
       </c>
       <c r="B54" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7677,31 +7690,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7709,10 +7717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508919</v>
+        <v>509071</v>
       </c>
       <c r="R54" t="n">
-        <v>7008295</v>
+        <v>7008310</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7749,7 +7757,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7758,6 +7766,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7776,14 +7785,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7801,7 +7805,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122424126</v>
+        <v>122428725</v>
       </c>
       <c r="B55" t="n">
         <v>57383</v>
@@ -7849,10 +7853,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508950</v>
+        <v>508919</v>
       </c>
       <c r="R55" t="n">
-        <v>7008334</v>
+        <v>7008295</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -8064,7 +8068,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427127</v>
+        <v>122427586</v>
       </c>
       <c r="B57" t="n">
         <v>57383</v>
@@ -8112,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508631</v>
+        <v>508745</v>
       </c>
       <c r="R57" t="n">
-        <v>7008480</v>
+        <v>7008511</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8152,7 +8156,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8166,7 +8170,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8199,10 +8203,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122426947</v>
+        <v>122424496</v>
       </c>
       <c r="B58" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8215,16 +8219,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8232,16 +8236,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508535</v>
+        <v>508891</v>
       </c>
       <c r="R58" t="n">
-        <v>7008440</v>
+        <v>7008386</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8289,6 +8289,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8300,7 +8305,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8318,7 +8343,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122429281</v>
+        <v>122427127</v>
       </c>
       <c r="B59" t="n">
         <v>57383</v>
@@ -8366,10 +8391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>509109</v>
+        <v>508631</v>
       </c>
       <c r="R59" t="n">
-        <v>7008253</v>
+        <v>7008480</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8406,7 +8431,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8420,7 +8445,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8453,10 +8478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122424611</v>
+        <v>122427444</v>
       </c>
       <c r="B60" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8469,31 +8494,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8501,10 +8521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508820</v>
+        <v>508541</v>
       </c>
       <c r="R60" t="n">
-        <v>7008398</v>
+        <v>7008422</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8541,7 +8561,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8550,32 +8570,33 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8593,7 +8614,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427681</v>
+        <v>122426823</v>
       </c>
       <c r="B61" t="n">
         <v>57383</v>
@@ -8631,7 +8652,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8641,10 +8662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508760</v>
+        <v>508614</v>
       </c>
       <c r="R61" t="n">
-        <v>7008533</v>
+        <v>7008464</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8681,7 +8702,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8733,10 +8754,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427444</v>
+        <v>122427681</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8749,26 +8770,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8776,10 +8802,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508541</v>
+        <v>508760</v>
       </c>
       <c r="R62" t="n">
-        <v>7008422</v>
+        <v>7008533</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8816,7 +8842,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8825,33 +8851,32 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8869,7 +8894,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424496</v>
+        <v>122424611</v>
       </c>
       <c r="B63" t="n">
         <v>57383</v>
@@ -8917,10 +8942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508891</v>
+        <v>508820</v>
       </c>
       <c r="R63" t="n">
-        <v>7008386</v>
+        <v>7008398</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8986,12 +9011,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9009,7 +9034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424707</v>
+        <v>122424676</v>
       </c>
       <c r="B64" t="n">
         <v>57383</v>
@@ -9047,7 +9072,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -9057,10 +9082,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508781</v>
+        <v>508779</v>
       </c>
       <c r="R64" t="n">
-        <v>7008382</v>
+        <v>7008383</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9097,7 +9122,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9124,14 +9149,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9149,7 +9169,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424589</v>
+        <v>122429281</v>
       </c>
       <c r="B65" t="n">
         <v>57383</v>
@@ -9197,10 +9217,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508831</v>
+        <v>509109</v>
       </c>
       <c r="R65" t="n">
-        <v>7008397</v>
+        <v>7008253</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9264,14 +9284,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9289,7 +9304,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427586</v>
+        <v>122424589</v>
       </c>
       <c r="B66" t="n">
         <v>57383</v>
@@ -9337,10 +9352,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508745</v>
+        <v>508831</v>
       </c>
       <c r="R66" t="n">
-        <v>7008511</v>
+        <v>7008397</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9404,9 +9419,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9564,7 +9584,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424676</v>
+        <v>122424707</v>
       </c>
       <c r="B68" t="n">
         <v>57383</v>
@@ -9602,7 +9622,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9612,10 +9632,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508779</v>
+        <v>508781</v>
       </c>
       <c r="R68" t="n">
-        <v>7008383</v>
+        <v>7008382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9652,7 +9672,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9679,9 +9699,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9699,10 +9724,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426823</v>
+        <v>122426947</v>
       </c>
       <c r="B69" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9715,16 +9740,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9732,12 +9757,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9747,10 +9776,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508614</v>
+        <v>508535</v>
       </c>
       <c r="R69" t="n">
-        <v>7008464</v>
+        <v>7008440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9785,11 +9814,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9801,27 +9825,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122426743</v>
+        <v>122423626</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508764</v>
+        <v>508994</v>
       </c>
       <c r="R2" t="n">
-        <v>7008423</v>
+        <v>7008252</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +784,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427227</v>
+        <v>122427142</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -847,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508639</v>
+        <v>508688</v>
       </c>
       <c r="R3" t="n">
-        <v>7008388</v>
+        <v>7008395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,22 +895,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122423935</v>
+        <v>122423133</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -970,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -980,17 +974,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508980</v>
+        <v>508834</v>
       </c>
       <c r="R4" t="n">
-        <v>7008294</v>
+        <v>7008117</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122423711</v>
+        <v>122430904</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1112,14 +1106,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509001</v>
+        <v>508916</v>
       </c>
       <c r="R5" t="n">
-        <v>7008256</v>
+        <v>7008122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,12 +1174,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122424308</v>
+        <v>122424772</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,37 +1213,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508903</v>
+        <v>508770</v>
       </c>
       <c r="R6" t="n">
-        <v>7008351</v>
+        <v>7008381</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1283,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,12 +1316,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430904</v>
+        <v>122429239</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,37 +1355,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508916</v>
+        <v>508765</v>
       </c>
       <c r="R7" t="n">
-        <v>7008122</v>
+        <v>7008466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1411,6 +1425,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1462,7 +1481,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122428118</v>
+        <v>122426743</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1502,13 +1521,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508595</v>
+        <v>508764</v>
       </c>
       <c r="R8" t="n">
-        <v>7008516</v>
+        <v>7008423</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1556,7 +1575,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1594,7 +1613,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423113</v>
+        <v>122423040</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1644,13 +1663,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508834</v>
+        <v>508845</v>
       </c>
       <c r="R9" t="n">
-        <v>7008115</v>
+        <v>7008072</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1703,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1736,10 +1755,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428937</v>
+        <v>122423988</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1752,42 +1771,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508739</v>
+        <v>508982</v>
       </c>
       <c r="R10" t="n">
-        <v>7008454</v>
+        <v>7008301</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1819,11 +1833,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1850,12 +1859,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,10 +1882,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122423988</v>
+        <v>122428937</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1889,37 +1898,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508982</v>
+        <v>508739</v>
       </c>
       <c r="R11" t="n">
-        <v>7008301</v>
+        <v>7008454</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1951,6 +1965,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1977,12 +1996,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2000,10 +2019,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427629</v>
+        <v>122423811</v>
       </c>
       <c r="B12" t="n">
-        <v>97194</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2012,31 +2031,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2050,13 +2069,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508574</v>
+        <v>508995</v>
       </c>
       <c r="R12" t="n">
-        <v>7008461</v>
+        <v>7008282</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2088,6 +2107,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2099,7 +2123,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2117,7 +2161,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122426951</v>
+        <v>122423935</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2156,16 +2200,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508719</v>
+        <v>508980</v>
       </c>
       <c r="R13" t="n">
-        <v>7008377</v>
+        <v>7008294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2231,12 +2280,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2254,10 +2303,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429239</v>
+        <v>122423191</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2270,47 +2319,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508765</v>
+        <v>508859</v>
       </c>
       <c r="R14" t="n">
-        <v>7008466</v>
+        <v>7008134</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2342,11 +2381,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack främst på stambasen.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2358,7 +2392,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2373,12 +2407,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2396,7 +2430,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122423040</v>
+        <v>122424389</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2435,21 +2469,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508845</v>
+        <v>508892</v>
       </c>
       <c r="R15" t="n">
-        <v>7008072</v>
+        <v>7008349</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -2486,7 +2515,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2538,7 +2567,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423467</v>
+        <v>122428118</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2574,14 +2603,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508900</v>
+        <v>508595</v>
       </c>
       <c r="R16" t="n">
-        <v>7008203</v>
+        <v>7008516</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2614,6 +2643,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2665,10 +2699,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122423626</v>
+        <v>122426951</v>
       </c>
       <c r="B17" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2681,36 +2715,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2719,10 +2744,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508994</v>
+        <v>508719</v>
       </c>
       <c r="R17" t="n">
-        <v>7008252</v>
+        <v>7008377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2759,7 +2784,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2774,6 +2799,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2791,7 +2836,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423191</v>
+        <v>122429398</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2827,17 +2872,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508859</v>
+        <v>508809</v>
       </c>
       <c r="R18" t="n">
-        <v>7008134</v>
+        <v>7008468</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2880,7 +2925,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2918,7 +2963,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429398</v>
+        <v>122423588</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2958,10 +3003,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508809</v>
+        <v>508975</v>
       </c>
       <c r="R19" t="n">
-        <v>7008468</v>
+        <v>7008243</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,12 +3067,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3045,10 +3090,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122423287</v>
+        <v>122427629</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>97194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3057,41 +3102,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508887</v>
+        <v>508574</v>
       </c>
       <c r="R20" t="n">
-        <v>7008167</v>
+        <v>7008461</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3135,26 +3190,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3172,10 +3207,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122424772</v>
+        <v>122422959</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3188,44 +3223,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508770</v>
+        <v>508833</v>
       </c>
       <c r="R21" t="n">
-        <v>7008381</v>
+        <v>7008097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3260,11 +3290,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3276,7 +3301,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3291,12 +3316,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3314,7 +3339,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122424637</v>
+        <v>122423287</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -3350,17 +3375,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508814</v>
+        <v>508887</v>
       </c>
       <c r="R22" t="n">
-        <v>7008416</v>
+        <v>7008167</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3403,7 +3428,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3441,10 +3466,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122422959</v>
+        <v>122429268</v>
       </c>
       <c r="B23" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3457,39 +3482,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508833</v>
+        <v>508765</v>
       </c>
       <c r="R23" t="n">
-        <v>7008097</v>
+        <v>7008461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3524,6 +3554,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3535,7 +3570,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3550,12 +3585,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3573,10 +3608,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122423588</v>
+        <v>122426582</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3589,34 +3624,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508975</v>
+        <v>508771</v>
       </c>
       <c r="R24" t="n">
-        <v>7008243</v>
+        <v>7008433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3651,6 +3696,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3677,12 +3727,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3700,10 +3750,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423133</v>
+        <v>122429024</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3716,47 +3766,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508834</v>
+        <v>508746</v>
       </c>
       <c r="R25" t="n">
-        <v>7008117</v>
+        <v>7008449</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3788,11 +3828,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3819,12 +3854,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3842,10 +3877,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122426582</v>
+        <v>122424308</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3858,47 +3893,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508771</v>
+        <v>508903</v>
       </c>
       <c r="R26" t="n">
-        <v>7008433</v>
+        <v>7008351</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3932,7 +3957,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3961,12 +3986,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3984,7 +4009,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122429024</v>
+        <v>122427227</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -4024,13 +4049,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508746</v>
+        <v>508639</v>
       </c>
       <c r="R27" t="n">
-        <v>7008449</v>
+        <v>7008388</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4073,17 +4098,17 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -4093,7 +4118,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4111,7 +4136,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122427142</v>
+        <v>122423467</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -4147,17 +4172,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508688</v>
+        <v>508900</v>
       </c>
       <c r="R28" t="n">
-        <v>7008395</v>
+        <v>7008203</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4215,12 +4240,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4238,10 +4263,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122429268</v>
+        <v>122424637</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4254,44 +4279,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508765</v>
+        <v>508814</v>
       </c>
       <c r="R29" t="n">
-        <v>7008461</v>
+        <v>7008416</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4326,11 +4341,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4357,12 +4367,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4380,10 +4390,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423811</v>
+        <v>122423711</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4396,44 +4406,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508995</v>
+        <v>509001</v>
       </c>
       <c r="R30" t="n">
-        <v>7008282</v>
+        <v>7008256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4468,11 +4468,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4499,12 +4494,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4664,10 +4659,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122424114</v>
+        <v>122423113</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4680,37 +4675,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508968</v>
+        <v>508834</v>
       </c>
       <c r="R32" t="n">
-        <v>7008319</v>
+        <v>7008115</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4773,12 +4778,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4796,10 +4801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122424389</v>
+        <v>122424114</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4812,42 +4817,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508892</v>
+        <v>508968</v>
       </c>
       <c r="R33" t="n">
-        <v>7008349</v>
+        <v>7008319</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122428777</v>
+        <v>122430040</v>
       </c>
       <c r="B34" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4949,41 +4949,50 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508909</v>
+        <v>508930</v>
       </c>
       <c r="R34" t="n">
-        <v>7008302</v>
+        <v>7008316</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5024,33 +5033,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5068,10 +5056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122423484</v>
+        <v>122423979</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5084,42 +5072,50 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508920</v>
+        <v>508958</v>
       </c>
       <c r="R35" t="n">
-        <v>7008181</v>
+        <v>7008338</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5154,11 +5150,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5170,27 +5161,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5208,7 +5179,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122428923</v>
+        <v>122424453</v>
       </c>
       <c r="B36" t="n">
         <v>57383</v>
@@ -5256,10 +5227,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508978</v>
+        <v>508908</v>
       </c>
       <c r="R36" t="n">
-        <v>7008270</v>
+        <v>7008354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5348,7 +5319,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122428831</v>
+        <v>122430628</v>
       </c>
       <c r="B37" t="n">
         <v>57383</v>
@@ -5396,10 +5367,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508914</v>
+        <v>508965</v>
       </c>
       <c r="R37" t="n">
-        <v>7008313</v>
+        <v>7008296</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5488,10 +5459,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122428462</v>
+        <v>122424038</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5504,26 +5475,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5531,7 +5507,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509040</v>
+        <v>508954</v>
       </c>
       <c r="R38" t="n">
         <v>7008336</v>
@@ -5569,13 +5545,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5586,22 +5566,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5619,10 +5599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430628</v>
+        <v>122429210</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5635,31 +5615,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5667,10 +5642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508965</v>
+        <v>509071</v>
       </c>
       <c r="R39" t="n">
-        <v>7008296</v>
+        <v>7008310</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5707,7 +5682,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5716,6 +5691,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5734,14 +5710,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5759,7 +5730,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122423808</v>
+        <v>122429553</v>
       </c>
       <c r="B40" t="n">
         <v>57383</v>
@@ -5807,10 +5778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508966</v>
+        <v>509048</v>
       </c>
       <c r="R40" t="n">
-        <v>7008356</v>
+        <v>7008315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5899,10 +5870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122429607</v>
+        <v>122429949</v>
       </c>
       <c r="B41" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5915,26 +5886,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5942,10 +5918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509034</v>
+        <v>508963</v>
       </c>
       <c r="R41" t="n">
-        <v>7008306</v>
+        <v>7008307</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5980,13 +5956,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6005,9 +5985,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6025,10 +6010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122423979</v>
+        <v>122423202</v>
       </c>
       <c r="B42" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6041,50 +6026,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508958</v>
+        <v>508881</v>
       </c>
       <c r="R42" t="n">
-        <v>7008338</v>
+        <v>7008130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6119,6 +6096,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6131,6 +6113,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,10 +6150,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429553</v>
+        <v>122429607</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6164,31 +6166,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6196,10 +6193,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509048</v>
+        <v>509034</v>
       </c>
       <c r="R43" t="n">
-        <v>7008315</v>
+        <v>7008306</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6234,17 +6231,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6263,14 +6256,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6288,10 +6276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122430707</v>
+        <v>122428777</v>
       </c>
       <c r="B44" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6304,29 +6292,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6336,10 +6323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508959</v>
+        <v>508909</v>
       </c>
       <c r="R44" t="n">
-        <v>7008280</v>
+        <v>7008302</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6374,17 +6361,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6395,22 +6378,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6428,10 +6411,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122424304</v>
+        <v>122424126</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6444,28 +6427,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6475,10 +6459,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508904</v>
+        <v>508950</v>
       </c>
       <c r="R45" t="n">
-        <v>7008325</v>
+        <v>7008334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6513,13 +6497,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6530,22 +6518,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6563,10 +6551,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428487</v>
+        <v>122428923</v>
       </c>
       <c r="B46" t="n">
-        <v>79773</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6575,30 +6563,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6606,10 +6599,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509041</v>
+        <v>508978</v>
       </c>
       <c r="R46" t="n">
-        <v>7008337</v>
+        <v>7008270</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6644,13 +6637,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6661,22 +6658,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429949</v>
+        <v>122430707</v>
       </c>
       <c r="B47" t="n">
         <v>57383</v>
@@ -6742,10 +6739,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508963</v>
+        <v>508959</v>
       </c>
       <c r="R47" t="n">
-        <v>7008307</v>
+        <v>7008280</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6834,10 +6831,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122423202</v>
+        <v>122424304</v>
       </c>
       <c r="B48" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6850,42 +6847,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508881</v>
+        <v>508904</v>
       </c>
       <c r="R48" t="n">
-        <v>7008130</v>
+        <v>7008325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6920,17 +6916,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6941,22 +6933,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6974,7 +6966,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122423524</v>
+        <v>122423808</v>
       </c>
       <c r="B49" t="n">
         <v>57383</v>
@@ -7018,14 +7010,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508928</v>
+        <v>508966</v>
       </c>
       <c r="R49" t="n">
-        <v>7008172</v>
+        <v>7008356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7062,7 +7054,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7076,17 +7068,17 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -7096,7 +7088,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7114,7 +7106,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122424453</v>
+        <v>122422848</v>
       </c>
       <c r="B50" t="n">
         <v>57383</v>
@@ -7158,14 +7150,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508908</v>
+        <v>508847</v>
       </c>
       <c r="R50" t="n">
-        <v>7008354</v>
+        <v>7008039</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7254,7 +7246,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122422848</v>
+        <v>122428831</v>
       </c>
       <c r="B51" t="n">
         <v>57383</v>
@@ -7298,14 +7290,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508847</v>
+        <v>508914</v>
       </c>
       <c r="R51" t="n">
-        <v>7008039</v>
+        <v>7008313</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7394,7 +7386,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122424038</v>
+        <v>122423484</v>
       </c>
       <c r="B52" t="n">
         <v>57383</v>
@@ -7438,14 +7430,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508954</v>
+        <v>508920</v>
       </c>
       <c r="R52" t="n">
-        <v>7008336</v>
+        <v>7008181</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7482,7 +7474,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7496,17 +7488,17 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7516,7 +7508,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7534,7 +7526,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122424126</v>
+        <v>122428725</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -7582,10 +7574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508950</v>
+        <v>508919</v>
       </c>
       <c r="R53" t="n">
-        <v>7008334</v>
+        <v>7008295</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7674,10 +7666,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429210</v>
+        <v>122423524</v>
       </c>
       <c r="B54" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7690,37 +7682,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509071</v>
+        <v>508928</v>
       </c>
       <c r="R54" t="n">
-        <v>7008310</v>
+        <v>7008172</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7757,7 +7754,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7766,28 +7763,32 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7805,10 +7806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428725</v>
+        <v>122428487</v>
       </c>
       <c r="B55" t="n">
-        <v>57383</v>
+        <v>79773</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7817,35 +7818,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7853,10 +7849,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508919</v>
+        <v>509041</v>
       </c>
       <c r="R55" t="n">
-        <v>7008295</v>
+        <v>7008337</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7891,17 +7887,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7912,22 +7904,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7945,10 +7937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430040</v>
+        <v>122428462</v>
       </c>
       <c r="B56" t="n">
-        <v>57536</v>
+        <v>79737</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7961,50 +7953,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508930</v>
+        <v>509040</v>
       </c>
       <c r="R56" t="n">
-        <v>7008316</v>
+        <v>7008336</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8045,12 +8024,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427586</v>
+        <v>122427444</v>
       </c>
       <c r="B57" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8084,31 +8084,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8116,10 +8111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508745</v>
+        <v>508541</v>
       </c>
       <c r="R57" t="n">
-        <v>7008511</v>
+        <v>7008422</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8156,7 +8151,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8165,27 +8160,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8203,7 +8204,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424496</v>
+        <v>122424611</v>
       </c>
       <c r="B58" t="n">
         <v>57383</v>
@@ -8251,10 +8252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508891</v>
+        <v>508820</v>
       </c>
       <c r="R58" t="n">
-        <v>7008386</v>
+        <v>7008398</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8320,12 +8321,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8343,7 +8344,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427127</v>
+        <v>122424676</v>
       </c>
       <c r="B59" t="n">
         <v>57383</v>
@@ -8391,10 +8392,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508631</v>
+        <v>508779</v>
       </c>
       <c r="R59" t="n">
-        <v>7008480</v>
+        <v>7008383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8431,7 +8432,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8445,7 +8446,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8478,10 +8479,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427444</v>
+        <v>122424707</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8494,26 +8495,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8521,10 +8527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508541</v>
+        <v>508781</v>
       </c>
       <c r="R60" t="n">
-        <v>7008422</v>
+        <v>7008382</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8561,7 +8567,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8570,33 +8576,32 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8614,7 +8619,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122426823</v>
+        <v>122424589</v>
       </c>
       <c r="B61" t="n">
         <v>57383</v>
@@ -8652,7 +8657,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8662,10 +8667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508614</v>
+        <v>508831</v>
       </c>
       <c r="R61" t="n">
-        <v>7008464</v>
+        <v>7008397</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8702,7 +8707,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8754,7 +8759,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427681</v>
+        <v>122427763</v>
       </c>
       <c r="B62" t="n">
         <v>57383</v>
@@ -8792,7 +8797,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8802,7 +8807,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508760</v>
+        <v>508776</v>
       </c>
       <c r="R62" t="n">
         <v>7008533</v>
@@ -8842,7 +8847,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8894,7 +8899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424611</v>
+        <v>122429281</v>
       </c>
       <c r="B63" t="n">
         <v>57383</v>
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508820</v>
+        <v>509109</v>
       </c>
       <c r="R63" t="n">
-        <v>7008398</v>
+        <v>7008253</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9009,14 +9014,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424676</v>
+        <v>122426947</v>
       </c>
       <c r="B64" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9067,12 +9067,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -9082,10 +9086,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508779</v>
+        <v>508535</v>
       </c>
       <c r="R64" t="n">
-        <v>7008383</v>
+        <v>7008440</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9120,11 +9124,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -9136,22 +9135,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9169,7 +9153,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429281</v>
+        <v>122427127</v>
       </c>
       <c r="B65" t="n">
         <v>57383</v>
@@ -9217,10 +9201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>509109</v>
+        <v>508631</v>
       </c>
       <c r="R65" t="n">
-        <v>7008253</v>
+        <v>7008480</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9257,7 +9241,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9271,7 +9255,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -9304,7 +9288,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424589</v>
+        <v>122427586</v>
       </c>
       <c r="B66" t="n">
         <v>57383</v>
@@ -9352,10 +9336,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508831</v>
+        <v>508745</v>
       </c>
       <c r="R66" t="n">
-        <v>7008397</v>
+        <v>7008511</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9419,14 +9403,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9444,7 +9423,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427763</v>
+        <v>122426823</v>
       </c>
       <c r="B67" t="n">
         <v>57383</v>
@@ -9492,10 +9471,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508776</v>
+        <v>508614</v>
       </c>
       <c r="R67" t="n">
-        <v>7008533</v>
+        <v>7008464</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9584,7 +9563,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424707</v>
+        <v>122424496</v>
       </c>
       <c r="B68" t="n">
         <v>57383</v>
@@ -9622,7 +9601,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9632,10 +9611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508781</v>
+        <v>508891</v>
       </c>
       <c r="R68" t="n">
-        <v>7008382</v>
+        <v>7008386</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9672,7 +9651,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9701,12 +9680,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9724,10 +9703,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426947</v>
+        <v>122427681</v>
       </c>
       <c r="B69" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9740,16 +9719,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9757,16 +9736,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9776,10 +9751,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508535</v>
+        <v>508760</v>
       </c>
       <c r="R69" t="n">
-        <v>7008440</v>
+        <v>7008533</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9814,6 +9789,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9825,7 +9805,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122423626</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427142</v>
+        <v>122424389</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508688</v>
+        <v>508892</v>
       </c>
       <c r="R3" t="n">
-        <v>7008395</v>
+        <v>7008349</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,6 +884,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -890,7 +900,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -905,12 +915,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122423133</v>
+        <v>122423113</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +974,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -981,7 +991,7 @@
         <v>508834</v>
       </c>
       <c r="R4" t="n">
-        <v>7008117</v>
+        <v>7008115</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -1018,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430904</v>
+        <v>122424308</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,17 +1116,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508916</v>
+        <v>508903</v>
       </c>
       <c r="R5" t="n">
-        <v>7008122</v>
+        <v>7008351</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,6 +1158,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1174,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122424772</v>
+        <v>122427142</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,44 +1228,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508770</v>
+        <v>508688</v>
       </c>
       <c r="R6" t="n">
-        <v>7008381</v>
+        <v>7008395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,11 +1290,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429239</v>
+        <v>122426582</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508765</v>
+        <v>508771</v>
       </c>
       <c r="R7" t="n">
-        <v>7008466</v>
+        <v>7008433</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122426743</v>
+        <v>122423811</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,34 +1497,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508764</v>
+        <v>508995</v>
       </c>
       <c r="R8" t="n">
-        <v>7008423</v>
+        <v>7008282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1561,7 +1571,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,12 +1600,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1613,10 +1623,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423040</v>
+        <v>122426743</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1629,47 +1639,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508845</v>
+        <v>508764</v>
       </c>
       <c r="R9" t="n">
-        <v>7008072</v>
+        <v>7008423</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122423988</v>
+        <v>122426951</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1771,34 +1771,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508982</v>
+        <v>508719</v>
       </c>
       <c r="R10" t="n">
-        <v>7008301</v>
+        <v>7008377</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,6 +1838,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1859,12 +1869,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1882,10 +1892,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122428937</v>
+        <v>122422838</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,19 +1928,24 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508739</v>
+        <v>508855</v>
       </c>
       <c r="R11" t="n">
-        <v>7008454</v>
+        <v>7008046</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1967,7 +1982,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,10 +2034,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423811</v>
+        <v>122424637</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,44 +2050,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508995</v>
+        <v>508814</v>
       </c>
       <c r="R12" t="n">
-        <v>7008282</v>
+        <v>7008416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,11 +2112,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122423935</v>
+        <v>122422959</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2177,44 +2177,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508980</v>
+        <v>508833</v>
       </c>
       <c r="R13" t="n">
-        <v>7008294</v>
+        <v>7008097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2249,11 +2244,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2265,7 +2255,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2280,12 +2270,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2303,10 +2293,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423191</v>
+        <v>122428937</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2319,34 +2309,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508859</v>
+        <v>508739</v>
       </c>
       <c r="R14" t="n">
-        <v>7008134</v>
+        <v>7008454</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2381,6 +2376,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122424389</v>
+        <v>122423133</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2466,22 +2466,27 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508892</v>
+        <v>508834</v>
       </c>
       <c r="R15" t="n">
-        <v>7008349</v>
+        <v>7008117</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2515,7 +2520,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2567,10 +2572,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122428118</v>
+        <v>122429398</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2607,13 +2612,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508595</v>
+        <v>508809</v>
       </c>
       <c r="R16" t="n">
-        <v>7008516</v>
+        <v>7008468</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2645,11 +2650,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426951</v>
+        <v>122423588</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2715,39 +2715,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508719</v>
+        <v>508975</v>
       </c>
       <c r="R17" t="n">
-        <v>7008377</v>
+        <v>7008243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2782,11 +2777,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2813,12 +2803,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2836,10 +2826,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429398</v>
+        <v>122423040</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2852,37 +2842,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508809</v>
+        <v>508845</v>
       </c>
       <c r="R18" t="n">
-        <v>7008468</v>
+        <v>7008072</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2914,6 +2914,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2940,12 +2945,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2963,10 +2968,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122423588</v>
+        <v>122423467</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2999,17 +3004,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508975</v>
+        <v>508900</v>
       </c>
       <c r="R19" t="n">
-        <v>7008243</v>
+        <v>7008203</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3052,7 +3057,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3090,10 +3095,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122427629</v>
+        <v>122429024</v>
       </c>
       <c r="B20" t="n">
-        <v>97194</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3102,51 +3107,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508574</v>
+        <v>508746</v>
       </c>
       <c r="R20" t="n">
-        <v>7008461</v>
+        <v>7008449</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3189,7 +3184,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3207,10 +3222,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122422959</v>
+        <v>122423191</v>
       </c>
       <c r="B21" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3223,42 +3238,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508833</v>
+        <v>508859</v>
       </c>
       <c r="R21" t="n">
-        <v>7008097</v>
+        <v>7008134</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3316,12 +3326,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3339,10 +3349,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122423287</v>
+        <v>122427227</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3375,17 +3385,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508887</v>
+        <v>508639</v>
       </c>
       <c r="R22" t="n">
-        <v>7008167</v>
+        <v>7008388</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3433,12 +3443,12 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3448,7 +3458,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3466,10 +3476,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122429268</v>
+        <v>122430904</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3482,44 +3492,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508765</v>
+        <v>508916</v>
       </c>
       <c r="R23" t="n">
-        <v>7008461</v>
+        <v>7008122</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3552,11 +3552,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3608,10 +3603,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122426582</v>
+        <v>122423287</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3624,47 +3619,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508771</v>
+        <v>508887</v>
       </c>
       <c r="R24" t="n">
-        <v>7008433</v>
+        <v>7008167</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3696,11 +3681,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3712,7 +3692,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3727,12 +3707,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3750,10 +3730,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122429024</v>
+        <v>122423935</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3766,37 +3746,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508746</v>
+        <v>508980</v>
       </c>
       <c r="R25" t="n">
-        <v>7008449</v>
+        <v>7008294</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3828,6 +3818,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3854,12 +3849,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3877,10 +3872,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122424308</v>
+        <v>122424114</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3917,13 +3912,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508903</v>
+        <v>508968</v>
       </c>
       <c r="R26" t="n">
-        <v>7008351</v>
+        <v>7008319</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4009,10 +4004,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427227</v>
+        <v>122427629</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>97195</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4021,41 +4016,51 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508639</v>
+        <v>508574</v>
       </c>
       <c r="R27" t="n">
-        <v>7008388</v>
+        <v>7008461</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4099,26 +4104,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4136,10 +4121,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423467</v>
+        <v>122423988</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4172,17 +4157,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508900</v>
+        <v>508982</v>
       </c>
       <c r="R28" t="n">
-        <v>7008203</v>
+        <v>7008301</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4210,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4263,10 +4248,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122424637</v>
+        <v>122428118</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4303,13 +4288,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508814</v>
+        <v>508595</v>
       </c>
       <c r="R29" t="n">
-        <v>7008416</v>
+        <v>7008516</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4341,6 +4326,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4352,7 +4342,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4390,10 +4380,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423711</v>
+        <v>122429268</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4406,34 +4396,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509001</v>
+        <v>508765</v>
       </c>
       <c r="R30" t="n">
-        <v>7008256</v>
+        <v>7008461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4468,6 +4468,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4494,12 +4499,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4517,10 +4522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122422838</v>
+        <v>122429239</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4553,7 +4558,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4563,17 +4568,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508855</v>
+        <v>508765</v>
       </c>
       <c r="R31" t="n">
-        <v>7008046</v>
+        <v>7008466</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4607,7 +4612,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4659,10 +4664,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423113</v>
+        <v>122423711</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4675,47 +4680,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508834</v>
+        <v>509001</v>
       </c>
       <c r="R32" t="n">
-        <v>7008115</v>
+        <v>7008256</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4747,11 +4742,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4778,12 +4768,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4801,10 +4791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122424114</v>
+        <v>122424772</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4817,34 +4807,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508968</v>
+        <v>508770</v>
       </c>
       <c r="R33" t="n">
-        <v>7008319</v>
+        <v>7008381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122430040</v>
+        <v>122429949</v>
       </c>
       <c r="B34" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4949,50 +4949,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508930</v>
+        <v>508963</v>
       </c>
       <c r="R34" t="n">
-        <v>7008316</v>
+        <v>7008307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5027,6 +5019,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5039,6 +5036,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5056,10 +5073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122423979</v>
+        <v>122430040</v>
       </c>
       <c r="B35" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5091,7 +5108,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -5112,10 +5129,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508958</v>
+        <v>508930</v>
       </c>
       <c r="R35" t="n">
-        <v>7008338</v>
+        <v>7008316</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5179,10 +5196,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424453</v>
+        <v>122424126</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5227,10 +5244,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508908</v>
+        <v>508950</v>
       </c>
       <c r="R36" t="n">
-        <v>7008354</v>
+        <v>7008334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5322,7 +5339,7 @@
         <v>122430628</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5459,10 +5476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122424038</v>
+        <v>122428725</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5507,10 +5524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508954</v>
+        <v>508919</v>
       </c>
       <c r="R38" t="n">
-        <v>7008336</v>
+        <v>7008295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5599,10 +5616,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122429210</v>
+        <v>122424304</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5634,7 +5651,11 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5642,10 +5663,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509071</v>
+        <v>508904</v>
       </c>
       <c r="R39" t="n">
-        <v>7008310</v>
+        <v>7008325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5680,11 +5701,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5702,17 +5718,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5730,10 +5751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122429553</v>
+        <v>122423808</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5778,10 +5799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509048</v>
+        <v>508966</v>
       </c>
       <c r="R40" t="n">
-        <v>7008315</v>
+        <v>7008356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5870,10 +5891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122429949</v>
+        <v>122428462</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5886,31 +5907,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5918,10 +5934,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508963</v>
+        <v>509040</v>
       </c>
       <c r="R41" t="n">
-        <v>7008307</v>
+        <v>7008336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5956,17 +5972,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5977,22 +5989,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6010,10 +6022,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122423202</v>
+        <v>122423524</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6058,10 +6070,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508881</v>
+        <v>508928</v>
       </c>
       <c r="R42" t="n">
-        <v>7008130</v>
+        <v>7008172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6098,7 +6110,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6112,17 +6124,17 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6132,7 +6144,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6150,10 +6162,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429607</v>
+        <v>122428923</v>
       </c>
       <c r="B43" t="n">
-        <v>82443</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6166,26 +6178,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6193,10 +6210,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509034</v>
+        <v>508978</v>
       </c>
       <c r="R43" t="n">
-        <v>7008306</v>
+        <v>7008270</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6231,13 +6248,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6256,9 +6277,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,10 +6302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122428777</v>
+        <v>122423979</v>
       </c>
       <c r="B44" t="n">
-        <v>79737</v>
+        <v>57537</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6292,41 +6318,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508909</v>
+        <v>508958</v>
       </c>
       <c r="R44" t="n">
-        <v>7008302</v>
+        <v>7008338</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6367,33 +6402,12 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6411,10 +6425,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122424126</v>
+        <v>122429607</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>82444</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6427,31 +6441,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6459,10 +6468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508950</v>
+        <v>509034</v>
       </c>
       <c r="R45" t="n">
-        <v>7008334</v>
+        <v>7008306</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6497,17 +6506,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6526,14 +6531,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428923</v>
+        <v>122428487</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>79774</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6563,35 +6563,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508978</v>
+        <v>509041</v>
       </c>
       <c r="R46" t="n">
-        <v>7008270</v>
+        <v>7008337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6637,17 +6632,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6658,22 +6649,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6691,10 +6682,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122430707</v>
+        <v>122428777</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6707,29 +6698,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6739,10 +6729,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508959</v>
+        <v>508909</v>
       </c>
       <c r="R47" t="n">
-        <v>7008280</v>
+        <v>7008302</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6777,17 +6767,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6798,22 +6784,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6831,10 +6817,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122424304</v>
+        <v>122424038</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6847,28 +6833,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6878,10 +6865,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508904</v>
+        <v>508954</v>
       </c>
       <c r="R48" t="n">
-        <v>7008325</v>
+        <v>7008336</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6916,13 +6903,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6933,22 +6924,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6966,10 +6957,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122423808</v>
+        <v>122430707</v>
       </c>
       <c r="B49" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7014,10 +7005,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508966</v>
+        <v>508959</v>
       </c>
       <c r="R49" t="n">
-        <v>7008356</v>
+        <v>7008280</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7109,7 +7100,7 @@
         <v>122422848</v>
       </c>
       <c r="B50" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7246,10 +7237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428831</v>
+        <v>122423202</v>
       </c>
       <c r="B51" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7290,14 +7281,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508914</v>
+        <v>508881</v>
       </c>
       <c r="R51" t="n">
-        <v>7008313</v>
+        <v>7008130</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7386,10 +7377,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122423484</v>
+        <v>122424453</v>
       </c>
       <c r="B52" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7430,14 +7421,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508920</v>
+        <v>508908</v>
       </c>
       <c r="R52" t="n">
-        <v>7008181</v>
+        <v>7008354</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7474,7 +7465,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7488,17 +7479,17 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7508,7 +7499,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7526,10 +7517,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428725</v>
+        <v>122429553</v>
       </c>
       <c r="B53" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7574,10 +7565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508919</v>
+        <v>509048</v>
       </c>
       <c r="R53" t="n">
-        <v>7008295</v>
+        <v>7008315</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7666,10 +7657,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122423524</v>
+        <v>122429210</v>
       </c>
       <c r="B54" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7682,42 +7673,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508928</v>
+        <v>509071</v>
       </c>
       <c r="R54" t="n">
-        <v>7008172</v>
+        <v>7008310</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7754,7 +7740,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7763,32 +7749,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7806,10 +7788,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428487</v>
+        <v>122423484</v>
       </c>
       <c r="B55" t="n">
-        <v>79773</v>
+        <v>57384</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7818,41 +7800,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509041</v>
+        <v>508920</v>
       </c>
       <c r="R55" t="n">
-        <v>7008337</v>
+        <v>7008181</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7887,39 +7874,43 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7937,10 +7928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122428462</v>
+        <v>122428831</v>
       </c>
       <c r="B56" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7953,26 +7944,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7980,10 +7976,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>509040</v>
+        <v>508914</v>
       </c>
       <c r="R56" t="n">
-        <v>7008336</v>
+        <v>7008313</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8018,13 +8014,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -8035,22 +8035,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8071,7 +8071,7 @@
         <v>122427444</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8204,10 +8204,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424611</v>
+        <v>122426823</v>
       </c>
       <c r="B58" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8252,10 +8252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508820</v>
+        <v>508614</v>
       </c>
       <c r="R58" t="n">
-        <v>7008398</v>
+        <v>7008464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8344,10 +8344,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424676</v>
+        <v>122424611</v>
       </c>
       <c r="B59" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508779</v>
+        <v>508820</v>
       </c>
       <c r="R59" t="n">
-        <v>7008383</v>
+        <v>7008398</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8459,9 +8459,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8479,10 +8484,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122424707</v>
+        <v>122427763</v>
       </c>
       <c r="B60" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508781</v>
+        <v>508776</v>
       </c>
       <c r="R60" t="n">
-        <v>7008382</v>
+        <v>7008533</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8619,10 +8624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424589</v>
+        <v>122426947</v>
       </c>
       <c r="B61" t="n">
-        <v>57383</v>
+        <v>56586</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8635,16 +8640,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8652,12 +8657,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8667,10 +8676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508831</v>
+        <v>508535</v>
       </c>
       <c r="R61" t="n">
-        <v>7008397</v>
+        <v>7008440</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8705,11 +8714,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8721,27 +8725,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8759,10 +8743,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427763</v>
+        <v>122427586</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8797,7 +8781,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8807,10 +8791,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508776</v>
+        <v>508745</v>
       </c>
       <c r="R62" t="n">
-        <v>7008533</v>
+        <v>7008511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8847,7 +8831,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8874,14 +8858,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8899,10 +8878,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122429281</v>
+        <v>122424676</v>
       </c>
       <c r="B63" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8947,10 +8926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>509109</v>
+        <v>508779</v>
       </c>
       <c r="R63" t="n">
-        <v>7008253</v>
+        <v>7008383</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9034,10 +9013,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122426947</v>
+        <v>122424589</v>
       </c>
       <c r="B64" t="n">
-        <v>56585</v>
+        <v>57384</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9050,16 +9029,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9067,16 +9046,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -9086,10 +9061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508535</v>
+        <v>508831</v>
       </c>
       <c r="R64" t="n">
-        <v>7008440</v>
+        <v>7008397</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9124,6 +9099,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -9135,7 +9115,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427127</v>
+        <v>122424707</v>
       </c>
       <c r="B65" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508631</v>
+        <v>508781</v>
       </c>
       <c r="R65" t="n">
-        <v>7008480</v>
+        <v>7008382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -9268,9 +9268,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9288,10 +9293,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427586</v>
+        <v>122427681</v>
       </c>
       <c r="B66" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9336,10 +9341,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508745</v>
+        <v>508760</v>
       </c>
       <c r="R66" t="n">
-        <v>7008511</v>
+        <v>7008533</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9403,9 +9408,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9423,10 +9433,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122426823</v>
+        <v>122429281</v>
       </c>
       <c r="B67" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9461,7 +9471,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9471,10 +9481,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508614</v>
+        <v>509109</v>
       </c>
       <c r="R67" t="n">
-        <v>7008464</v>
+        <v>7008253</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9511,7 +9521,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9538,14 +9548,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9563,10 +9568,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424496</v>
+        <v>122427127</v>
       </c>
       <c r="B68" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9611,10 +9616,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508891</v>
+        <v>508631</v>
       </c>
       <c r="R68" t="n">
-        <v>7008386</v>
+        <v>7008480</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9651,7 +9656,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9665,7 +9670,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9678,14 +9683,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9703,10 +9703,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122427681</v>
+        <v>122424496</v>
       </c>
       <c r="B69" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508760</v>
+        <v>508891</v>
       </c>
       <c r="R69" t="n">
-        <v>7008533</v>
+        <v>7008386</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9820,12 +9820,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -3730,10 +3730,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423935</v>
+        <v>122424114</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3746,44 +3746,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508980</v>
+        <v>508968</v>
       </c>
       <c r="R25" t="n">
-        <v>7008294</v>
+        <v>7008319</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3820,7 +3810,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3849,12 +3839,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3872,10 +3862,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122424114</v>
+        <v>122423935</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3888,34 +3878,44 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508968</v>
+        <v>508980</v>
       </c>
       <c r="R26" t="n">
-        <v>7008319</v>
+        <v>7008294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122423524</v>
+        <v>122429607</v>
       </c>
       <c r="B42" t="n">
-        <v>57384</v>
+        <v>82444</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6038,42 +6038,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508928</v>
+        <v>509034</v>
       </c>
       <c r="R42" t="n">
-        <v>7008172</v>
+        <v>7008306</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6108,43 +6103,34 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6162,10 +6148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122428923</v>
+        <v>122423979</v>
       </c>
       <c r="B43" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6178,42 +6164,50 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508978</v>
+        <v>508958</v>
       </c>
       <c r="R43" t="n">
-        <v>7008270</v>
+        <v>7008338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6248,11 +6242,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6265,26 +6254,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6302,10 +6271,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423979</v>
+        <v>122423524</v>
       </c>
       <c r="B44" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6318,50 +6287,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508958</v>
+        <v>508928</v>
       </c>
       <c r="R44" t="n">
-        <v>7008338</v>
+        <v>7008172</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6396,6 +6357,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6407,7 +6373,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6425,10 +6411,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122429607</v>
+        <v>122428923</v>
       </c>
       <c r="B45" t="n">
-        <v>82444</v>
+        <v>57384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6441,26 +6427,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6468,10 +6459,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509034</v>
+        <v>508978</v>
       </c>
       <c r="R45" t="n">
-        <v>7008306</v>
+        <v>7008270</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6506,13 +6497,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6531,9 +6526,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428487</v>
+        <v>122428777</v>
       </c>
       <c r="B46" t="n">
-        <v>79774</v>
+        <v>79738</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6563,30 +6563,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6594,10 +6598,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509041</v>
+        <v>508909</v>
       </c>
       <c r="R46" t="n">
-        <v>7008337</v>
+        <v>7008302</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6682,10 +6686,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428777</v>
+        <v>122424038</v>
       </c>
       <c r="B47" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6698,28 +6702,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6729,10 +6734,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508909</v>
+        <v>508954</v>
       </c>
       <c r="R47" t="n">
-        <v>7008302</v>
+        <v>7008336</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6767,13 +6772,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6784,22 +6793,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6817,10 +6826,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122424038</v>
+        <v>122428487</v>
       </c>
       <c r="B48" t="n">
-        <v>57384</v>
+        <v>79774</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6829,35 +6838,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6865,10 +6869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508954</v>
+        <v>509041</v>
       </c>
       <c r="R48" t="n">
-        <v>7008336</v>
+        <v>7008337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6903,17 +6907,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6924,22 +6924,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7237,7 +7237,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122423202</v>
+        <v>122424453</v>
       </c>
       <c r="B51" t="n">
         <v>57384</v>
@@ -7281,14 +7281,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508881</v>
+        <v>508908</v>
       </c>
       <c r="R51" t="n">
-        <v>7008130</v>
+        <v>7008354</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122424453</v>
+        <v>122429553</v>
       </c>
       <c r="B52" t="n">
         <v>57384</v>
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508908</v>
+        <v>509048</v>
       </c>
       <c r="R52" t="n">
-        <v>7008354</v>
+        <v>7008315</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122429553</v>
+        <v>122423202</v>
       </c>
       <c r="B53" t="n">
         <v>57384</v>
@@ -7561,14 +7561,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509048</v>
+        <v>508881</v>
       </c>
       <c r="R53" t="n">
-        <v>7008315</v>
+        <v>7008130</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122423626</v>
+        <v>122429268</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508994</v>
+        <v>508765</v>
       </c>
       <c r="R2" t="n">
-        <v>7008252</v>
+        <v>7008461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +780,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424389</v>
+        <v>122424637</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,42 +833,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508892</v>
+        <v>508814</v>
       </c>
       <c r="R3" t="n">
-        <v>7008349</v>
+        <v>7008416</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,11 +895,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122423113</v>
+        <v>122422959</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,32 +960,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -988,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508834</v>
+        <v>508833</v>
       </c>
       <c r="R4" t="n">
-        <v>7008115</v>
+        <v>7008097</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,11 +1027,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1057,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122424308</v>
+        <v>122429024</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1120,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508903</v>
+        <v>508746</v>
       </c>
       <c r="R5" t="n">
-        <v>7008351</v>
+        <v>7008449</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1156,11 +1152,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427142</v>
+        <v>122428937</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,37 +1219,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508688</v>
+        <v>508739</v>
       </c>
       <c r="R6" t="n">
-        <v>7008395</v>
+        <v>7008454</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1290,6 +1286,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1316,12 +1317,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1339,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122426582</v>
+        <v>122424114</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1355,44 +1356,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508771</v>
+        <v>508968</v>
       </c>
       <c r="R7" t="n">
-        <v>7008433</v>
+        <v>7008319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1458,12 +1449,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1481,10 +1472,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122423811</v>
+        <v>122423191</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,47 +1488,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508995</v>
+        <v>508859</v>
       </c>
       <c r="R8" t="n">
-        <v>7008282</v>
+        <v>7008134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1569,11 +1550,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1585,7 +1561,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1600,12 +1576,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1623,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122426743</v>
+        <v>122423988</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508764</v>
+        <v>508982</v>
       </c>
       <c r="R9" t="n">
-        <v>7008423</v>
+        <v>7008301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,11 +1675,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1755,10 +1726,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122426951</v>
+        <v>122427227</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1771,39 +1742,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508719</v>
+        <v>508639</v>
       </c>
       <c r="R10" t="n">
-        <v>7008377</v>
+        <v>7008388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1838,11 +1804,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1854,27 +1815,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1892,10 +1853,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122422838</v>
+        <v>122424772</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1908,16 +1869,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1938,17 +1899,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508855</v>
+        <v>508770</v>
       </c>
       <c r="R11" t="n">
-        <v>7008046</v>
+        <v>7008381</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1982,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2034,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122424637</v>
+        <v>122423711</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2074,10 +2035,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508814</v>
+        <v>509001</v>
       </c>
       <c r="R12" t="n">
-        <v>7008416</v>
+        <v>7008256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2161,10 +2122,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122422959</v>
+        <v>122426951</v>
       </c>
       <c r="B13" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2177,39 +2138,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508833</v>
+        <v>508719</v>
       </c>
       <c r="R13" t="n">
-        <v>7008097</v>
+        <v>7008377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2244,6 +2205,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2221,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2293,10 +2259,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122428937</v>
+        <v>122426582</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2309,16 +2275,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2329,7 +2295,12 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2338,13 +2309,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508739</v>
+        <v>508771</v>
       </c>
       <c r="R14" t="n">
-        <v>7008454</v>
+        <v>7008433</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2378,7 +2349,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2407,12 +2378,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2430,7 +2401,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122423133</v>
+        <v>122422838</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2466,7 +2437,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2480,10 +2451,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508834</v>
+        <v>508855</v>
       </c>
       <c r="R15" t="n">
-        <v>7008117</v>
+        <v>7008046</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2520,7 +2491,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2572,10 +2543,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122429398</v>
+        <v>122423811</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2588,34 +2559,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508809</v>
+        <v>508995</v>
       </c>
       <c r="R16" t="n">
-        <v>7008468</v>
+        <v>7008282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2650,6 +2631,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2676,12 +2662,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2699,10 +2685,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122423588</v>
+        <v>122427142</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2739,10 +2725,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508975</v>
+        <v>508688</v>
       </c>
       <c r="R17" t="n">
-        <v>7008243</v>
+        <v>7008395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2788,7 +2774,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2803,12 +2789,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2826,7 +2812,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122423040</v>
+        <v>122424389</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2865,21 +2851,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508845</v>
+        <v>508892</v>
       </c>
       <c r="R18" t="n">
-        <v>7008072</v>
+        <v>7008349</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -2916,7 +2897,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2968,10 +2949,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122423467</v>
+        <v>122430904</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3008,13 +2989,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508900</v>
+        <v>508916</v>
       </c>
       <c r="R19" t="n">
-        <v>7008203</v>
+        <v>7008122</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3057,7 +3038,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3072,12 +3053,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3095,10 +3076,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429024</v>
+        <v>122427629</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>97198</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3107,41 +3088,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508746</v>
+        <v>508574</v>
       </c>
       <c r="R20" t="n">
-        <v>7008449</v>
+        <v>7008461</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3184,27 +3175,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3222,10 +3193,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122423191</v>
+        <v>122429398</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3258,17 +3229,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508859</v>
+        <v>508809</v>
       </c>
       <c r="R21" t="n">
-        <v>7008134</v>
+        <v>7008468</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3311,7 +3282,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3349,10 +3320,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427227</v>
+        <v>122423467</v>
       </c>
       <c r="B22" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3385,17 +3356,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508639</v>
+        <v>508900</v>
       </c>
       <c r="R22" t="n">
-        <v>7008388</v>
+        <v>7008203</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3443,12 +3414,12 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3458,7 +3429,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3476,10 +3447,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122430904</v>
+        <v>122428118</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3512,17 +3483,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508916</v>
+        <v>508595</v>
       </c>
       <c r="R23" t="n">
-        <v>7008122</v>
+        <v>7008516</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3554,6 +3525,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3565,7 +3541,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3580,12 +3556,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3606,7 +3582,7 @@
         <v>122423287</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3730,10 +3706,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122424114</v>
+        <v>122423113</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3746,37 +3722,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508968</v>
+        <v>508834</v>
       </c>
       <c r="R25" t="n">
-        <v>7008319</v>
+        <v>7008115</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3810,7 +3796,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3839,12 +3825,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3862,7 +3848,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423935</v>
+        <v>122429239</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3898,7 +3884,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3912,13 +3898,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508980</v>
+        <v>508765</v>
       </c>
       <c r="R26" t="n">
-        <v>7008294</v>
+        <v>7008466</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3952,7 +3938,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4004,10 +3990,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427629</v>
+        <v>122423040</v>
       </c>
       <c r="B27" t="n">
-        <v>97195</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4016,31 +4002,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4050,17 +4036,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508574</v>
+        <v>508845</v>
       </c>
       <c r="R27" t="n">
-        <v>7008461</v>
+        <v>7008072</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4092,6 +4078,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4103,7 +4094,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4121,10 +4132,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423988</v>
+        <v>122426743</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4161,10 +4172,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508982</v>
+        <v>508764</v>
       </c>
       <c r="R28" t="n">
-        <v>7008301</v>
+        <v>7008423</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4197,6 +4208,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4248,10 +4264,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122428118</v>
+        <v>122423935</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4264,37 +4280,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508595</v>
+        <v>508980</v>
       </c>
       <c r="R29" t="n">
-        <v>7008516</v>
+        <v>7008294</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4328,7 +4354,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4342,7 +4368,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4357,12 +4383,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4380,7 +4406,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122429268</v>
+        <v>122423133</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -4416,7 +4442,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4426,17 +4452,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508765</v>
+        <v>508834</v>
       </c>
       <c r="R30" t="n">
-        <v>7008461</v>
+        <v>7008117</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4470,7 +4496,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4522,10 +4548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122429239</v>
+        <v>122423626</v>
       </c>
       <c r="B31" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4538,27 +4564,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4572,13 +4602,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508765</v>
+        <v>508994</v>
       </c>
       <c r="R31" t="n">
-        <v>7008466</v>
+        <v>7008252</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4612,7 +4642,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4627,26 +4657,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4664,10 +4674,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423711</v>
+        <v>122423588</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4704,10 +4714,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509001</v>
+        <v>508975</v>
       </c>
       <c r="R32" t="n">
-        <v>7008256</v>
+        <v>7008243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4791,10 +4801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122424772</v>
+        <v>122424308</v>
       </c>
       <c r="B33" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4807,47 +4817,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508770</v>
+        <v>508903</v>
       </c>
       <c r="R33" t="n">
-        <v>7008381</v>
+        <v>7008351</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429949</v>
+        <v>122424453</v>
       </c>
       <c r="B34" t="n">
         <v>57384</v>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508963</v>
+        <v>508908</v>
       </c>
       <c r="R34" t="n">
-        <v>7008307</v>
+        <v>7008354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122430040</v>
+        <v>122428831</v>
       </c>
       <c r="B35" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5089,50 +5089,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508930</v>
+        <v>508914</v>
       </c>
       <c r="R35" t="n">
-        <v>7008316</v>
+        <v>7008313</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5167,6 +5159,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5179,6 +5176,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5196,7 +5213,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424126</v>
+        <v>122430707</v>
       </c>
       <c r="B36" t="n">
         <v>57384</v>
@@ -5244,10 +5261,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508950</v>
+        <v>508959</v>
       </c>
       <c r="R36" t="n">
-        <v>7008334</v>
+        <v>7008280</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5336,7 +5353,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430628</v>
+        <v>122429553</v>
       </c>
       <c r="B37" t="n">
         <v>57384</v>
@@ -5384,10 +5401,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508965</v>
+        <v>509048</v>
       </c>
       <c r="R37" t="n">
-        <v>7008296</v>
+        <v>7008315</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5476,7 +5493,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122428725</v>
+        <v>122429949</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -5524,10 +5541,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508919</v>
+        <v>508963</v>
       </c>
       <c r="R38" t="n">
-        <v>7008295</v>
+        <v>7008307</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5616,10 +5633,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122424304</v>
+        <v>122423202</v>
       </c>
       <c r="B39" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5632,41 +5649,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508904</v>
+        <v>508881</v>
       </c>
       <c r="R39" t="n">
-        <v>7008325</v>
+        <v>7008130</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5701,13 +5719,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5718,22 +5740,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5751,10 +5773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122423808</v>
+        <v>122430040</v>
       </c>
       <c r="B40" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5767,42 +5789,50 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508966</v>
+        <v>508930</v>
       </c>
       <c r="R40" t="n">
-        <v>7008356</v>
+        <v>7008316</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5837,11 +5867,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5854,26 +5879,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5891,10 +5896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122428462</v>
+        <v>122424038</v>
       </c>
       <c r="B41" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5907,26 +5912,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5934,7 +5944,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509040</v>
+        <v>508954</v>
       </c>
       <c r="R41" t="n">
         <v>7008336</v>
@@ -5972,13 +5982,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5989,22 +6003,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6022,10 +6036,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122429607</v>
+        <v>122428462</v>
       </c>
       <c r="B42" t="n">
-        <v>82444</v>
+        <v>79741</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6038,21 +6052,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6065,10 +6079,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509034</v>
+        <v>509040</v>
       </c>
       <c r="R42" t="n">
-        <v>7008306</v>
+        <v>7008336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6120,17 +6134,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,10 +6167,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122423979</v>
+        <v>122429210</v>
       </c>
       <c r="B43" t="n">
-        <v>57537</v>
+        <v>79741</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6164,50 +6183,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508958</v>
+        <v>509071</v>
       </c>
       <c r="R43" t="n">
-        <v>7008338</v>
+        <v>7008310</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6242,18 +6248,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6271,7 +6298,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423524</v>
+        <v>122423808</v>
       </c>
       <c r="B44" t="n">
         <v>57384</v>
@@ -6315,14 +6342,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508928</v>
+        <v>508966</v>
       </c>
       <c r="R44" t="n">
-        <v>7008172</v>
+        <v>7008356</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6359,7 +6386,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6373,17 +6400,17 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6393,7 +6420,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6411,10 +6438,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122428923</v>
+        <v>122428777</v>
       </c>
       <c r="B45" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6427,29 +6454,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6459,10 +6485,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508978</v>
+        <v>508909</v>
       </c>
       <c r="R45" t="n">
-        <v>7008270</v>
+        <v>7008302</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6497,17 +6523,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6518,22 +6540,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6551,10 +6573,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428777</v>
+        <v>122423979</v>
       </c>
       <c r="B46" t="n">
-        <v>79738</v>
+        <v>57537</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6567,41 +6589,50 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508909</v>
+        <v>508958</v>
       </c>
       <c r="R46" t="n">
-        <v>7008302</v>
+        <v>7008338</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6642,33 +6673,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6686,10 +6696,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122424038</v>
+        <v>122428487</v>
       </c>
       <c r="B47" t="n">
-        <v>57384</v>
+        <v>79777</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6698,35 +6708,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6734,10 +6739,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508954</v>
+        <v>509041</v>
       </c>
       <c r="R47" t="n">
-        <v>7008336</v>
+        <v>7008337</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6772,17 +6777,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6793,22 +6794,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6826,10 +6827,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122428487</v>
+        <v>122429607</v>
       </c>
       <c r="B48" t="n">
-        <v>79774</v>
+        <v>82447</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6838,25 +6839,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6869,10 +6870,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509041</v>
+        <v>509034</v>
       </c>
       <c r="R48" t="n">
-        <v>7008337</v>
+        <v>7008306</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6924,22 +6925,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6957,7 +6953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430707</v>
+        <v>122422848</v>
       </c>
       <c r="B49" t="n">
         <v>57384</v>
@@ -7001,14 +6997,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508959</v>
+        <v>508847</v>
       </c>
       <c r="R49" t="n">
-        <v>7008280</v>
+        <v>7008039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7097,7 +7093,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122422848</v>
+        <v>122423524</v>
       </c>
       <c r="B50" t="n">
         <v>57384</v>
@@ -7145,10 +7141,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508847</v>
+        <v>508928</v>
       </c>
       <c r="R50" t="n">
-        <v>7008039</v>
+        <v>7008172</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7185,7 +7181,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7199,17 +7195,17 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -7219,7 +7215,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7237,7 +7233,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122424453</v>
+        <v>122428725</v>
       </c>
       <c r="B51" t="n">
         <v>57384</v>
@@ -7285,10 +7281,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508908</v>
+        <v>508919</v>
       </c>
       <c r="R51" t="n">
-        <v>7008354</v>
+        <v>7008295</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7377,10 +7373,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122429553</v>
+        <v>122424304</v>
       </c>
       <c r="B52" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7393,29 +7389,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7425,10 +7420,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>509048</v>
+        <v>508904</v>
       </c>
       <c r="R52" t="n">
-        <v>7008315</v>
+        <v>7008325</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7463,17 +7458,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7484,22 +7475,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7517,7 +7508,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122423202</v>
+        <v>122430628</v>
       </c>
       <c r="B53" t="n">
         <v>57384</v>
@@ -7561,14 +7552,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508881</v>
+        <v>508965</v>
       </c>
       <c r="R53" t="n">
-        <v>7008130</v>
+        <v>7008296</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7657,10 +7648,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429210</v>
+        <v>122428923</v>
       </c>
       <c r="B54" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7673,26 +7664,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7700,10 +7696,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509071</v>
+        <v>508978</v>
       </c>
       <c r="R54" t="n">
-        <v>7008310</v>
+        <v>7008270</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7740,7 +7736,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7749,7 +7745,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7768,9 +7763,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122423484</v>
+        <v>122424126</v>
       </c>
       <c r="B55" t="n">
         <v>57384</v>
@@ -7832,14 +7832,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508920</v>
+        <v>508950</v>
       </c>
       <c r="R55" t="n">
-        <v>7008181</v>
+        <v>7008334</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7890,17 +7890,17 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122428831</v>
+        <v>122423484</v>
       </c>
       <c r="B56" t="n">
         <v>57384</v>
@@ -7972,14 +7972,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508914</v>
+        <v>508920</v>
       </c>
       <c r="R56" t="n">
-        <v>7008313</v>
+        <v>7008181</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8030,17 +8030,17 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427444</v>
+        <v>122427586</v>
       </c>
       <c r="B57" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8084,26 +8084,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8111,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508541</v>
+        <v>508745</v>
       </c>
       <c r="R57" t="n">
-        <v>7008422</v>
+        <v>7008511</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8151,7 +8156,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8160,33 +8165,27 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8204,7 +8203,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122426823</v>
+        <v>122424589</v>
       </c>
       <c r="B58" t="n">
         <v>57384</v>
@@ -8242,7 +8241,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8252,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508614</v>
+        <v>508831</v>
       </c>
       <c r="R58" t="n">
-        <v>7008464</v>
+        <v>7008397</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8292,7 +8291,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8344,7 +8343,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424611</v>
+        <v>122424496</v>
       </c>
       <c r="B59" t="n">
         <v>57384</v>
@@ -8392,10 +8391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508820</v>
+        <v>508891</v>
       </c>
       <c r="R59" t="n">
-        <v>7008398</v>
+        <v>7008386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8461,12 +8460,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8484,7 +8483,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427763</v>
+        <v>122427127</v>
       </c>
       <c r="B60" t="n">
         <v>57384</v>
@@ -8522,7 +8521,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8532,10 +8531,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508776</v>
+        <v>508631</v>
       </c>
       <c r="R60" t="n">
-        <v>7008533</v>
+        <v>7008480</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8572,7 +8571,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8586,7 +8585,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8599,14 +8598,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8624,10 +8618,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122426947</v>
+        <v>122424611</v>
       </c>
       <c r="B61" t="n">
-        <v>56586</v>
+        <v>57384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8640,16 +8634,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8657,16 +8651,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8676,10 +8666,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508535</v>
+        <v>508820</v>
       </c>
       <c r="R61" t="n">
-        <v>7008440</v>
+        <v>7008398</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8714,6 +8704,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8725,7 +8720,27 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8743,7 +8758,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427586</v>
+        <v>122424676</v>
       </c>
       <c r="B62" t="n">
         <v>57384</v>
@@ -8791,10 +8806,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508745</v>
+        <v>508779</v>
       </c>
       <c r="R62" t="n">
-        <v>7008511</v>
+        <v>7008383</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8878,10 +8893,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424676</v>
+        <v>122427444</v>
       </c>
       <c r="B63" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8894,31 +8909,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8926,10 +8936,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508779</v>
+        <v>508541</v>
       </c>
       <c r="R63" t="n">
-        <v>7008383</v>
+        <v>7008422</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8966,7 +8976,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8975,27 +8985,33 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9013,7 +9029,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424589</v>
+        <v>122427681</v>
       </c>
       <c r="B64" t="n">
         <v>57384</v>
@@ -9061,10 +9077,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508831</v>
+        <v>508760</v>
       </c>
       <c r="R64" t="n">
-        <v>7008397</v>
+        <v>7008533</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9153,7 +9169,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424707</v>
+        <v>122429281</v>
       </c>
       <c r="B65" t="n">
         <v>57384</v>
@@ -9191,7 +9207,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9201,10 +9217,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508781</v>
+        <v>509109</v>
       </c>
       <c r="R65" t="n">
-        <v>7008382</v>
+        <v>7008253</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9241,7 +9257,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9268,14 +9284,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9293,10 +9304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427681</v>
+        <v>122426947</v>
       </c>
       <c r="B66" t="n">
-        <v>57384</v>
+        <v>56586</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9309,16 +9320,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9326,12 +9337,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9341,10 +9356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508760</v>
+        <v>508535</v>
       </c>
       <c r="R66" t="n">
-        <v>7008533</v>
+        <v>7008440</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9379,11 +9394,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9395,27 +9405,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9433,7 +9423,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429281</v>
+        <v>122427763</v>
       </c>
       <c r="B67" t="n">
         <v>57384</v>
@@ -9471,7 +9461,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9481,10 +9471,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509109</v>
+        <v>508776</v>
       </c>
       <c r="R67" t="n">
-        <v>7008253</v>
+        <v>7008533</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9521,7 +9511,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9548,9 +9538,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9568,7 +9563,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122427127</v>
+        <v>122424707</v>
       </c>
       <c r="B68" t="n">
         <v>57384</v>
@@ -9606,7 +9601,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9616,10 +9611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508631</v>
+        <v>508781</v>
       </c>
       <c r="R68" t="n">
-        <v>7008480</v>
+        <v>7008382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9656,7 +9651,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9670,7 +9665,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9683,9 +9678,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9703,7 +9703,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424496</v>
+        <v>122426823</v>
       </c>
       <c r="B69" t="n">
         <v>57384</v>
@@ -9741,7 +9741,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508891</v>
+        <v>508614</v>
       </c>
       <c r="R69" t="n">
-        <v>7008386</v>
+        <v>7008464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122429268</v>
+        <v>122428118</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508765</v>
+        <v>508595</v>
       </c>
       <c r="R2" t="n">
-        <v>7008461</v>
+        <v>7008516</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424637</v>
+        <v>122422838</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,37 +823,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508814</v>
+        <v>508855</v>
       </c>
       <c r="R3" t="n">
-        <v>7008416</v>
+        <v>7008046</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,6 +895,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -921,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122422959</v>
+        <v>122423988</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,39 +965,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508833</v>
+        <v>508982</v>
       </c>
       <c r="R4" t="n">
-        <v>7008097</v>
+        <v>7008301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429024</v>
+        <v>122423711</v>
       </c>
       <c r="B5" t="n">
         <v>78660</v>
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508746</v>
+        <v>509001</v>
       </c>
       <c r="R5" t="n">
-        <v>7008449</v>
+        <v>7008256</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122428937</v>
+        <v>122427629</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>97198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,31 +1215,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508739</v>
+        <v>508574</v>
       </c>
       <c r="R6" t="n">
-        <v>7008454</v>
+        <v>7008461</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1286,11 +1291,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1302,27 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,7 +1320,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122424114</v>
+        <v>122429398</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1380,10 +1360,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508968</v>
+        <v>508809</v>
       </c>
       <c r="R7" t="n">
-        <v>7008319</v>
+        <v>7008468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,11 +1398,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1449,12 +1424,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1472,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122423191</v>
+        <v>122423935</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1488,37 +1463,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508859</v>
+        <v>508980</v>
       </c>
       <c r="R8" t="n">
-        <v>7008134</v>
+        <v>7008294</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1550,6 +1535,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1561,7 +1551,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1576,12 +1566,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,7 +1589,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423988</v>
+        <v>122423191</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1635,17 +1625,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508982</v>
+        <v>508859</v>
       </c>
       <c r="R9" t="n">
-        <v>7008301</v>
+        <v>7008134</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1688,7 +1678,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1703,12 +1693,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1726,7 +1716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122427227</v>
+        <v>122430904</v>
       </c>
       <c r="B10" t="n">
         <v>78660</v>
@@ -1762,14 +1752,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508639</v>
+        <v>508916</v>
       </c>
       <c r="R10" t="n">
-        <v>7008388</v>
+        <v>7008122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,27 +1805,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1853,10 +1843,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122424772</v>
+        <v>122424637</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1869,44 +1859,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508770</v>
+        <v>508814</v>
       </c>
       <c r="R11" t="n">
-        <v>7008381</v>
+        <v>7008416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1941,11 +1921,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1972,12 +1947,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1995,7 +1970,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423711</v>
+        <v>122423588</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -2035,10 +2010,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509001</v>
+        <v>508975</v>
       </c>
       <c r="R12" t="n">
-        <v>7008256</v>
+        <v>7008243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2122,7 +2097,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122426951</v>
+        <v>122429268</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -2161,16 +2136,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508719</v>
+        <v>508765</v>
       </c>
       <c r="R13" t="n">
-        <v>7008377</v>
+        <v>7008461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2207,7 +2187,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2236,12 +2216,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2259,7 +2239,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122426582</v>
+        <v>122424772</v>
       </c>
       <c r="B14" t="n">
         <v>57400</v>
@@ -2309,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508771</v>
+        <v>508770</v>
       </c>
       <c r="R14" t="n">
-        <v>7008433</v>
+        <v>7008381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,7 +2329,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2378,12 +2358,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2401,7 +2381,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122422838</v>
+        <v>122423133</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2437,7 +2417,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2451,10 +2431,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508855</v>
+        <v>508834</v>
       </c>
       <c r="R15" t="n">
-        <v>7008046</v>
+        <v>7008117</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2491,7 +2471,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2543,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423811</v>
+        <v>122426582</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2559,16 +2539,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2593,10 +2573,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508995</v>
+        <v>508771</v>
       </c>
       <c r="R16" t="n">
-        <v>7008282</v>
+        <v>7008433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2633,7 +2613,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2662,12 +2642,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2685,10 +2665,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122427142</v>
+        <v>122423113</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2701,37 +2681,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508688</v>
+        <v>508834</v>
       </c>
       <c r="R17" t="n">
-        <v>7008395</v>
+        <v>7008115</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2763,6 +2753,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2789,12 +2784,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2812,7 +2807,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122424389</v>
+        <v>122428937</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2848,7 +2843,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2857,13 +2852,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508892</v>
+        <v>508739</v>
       </c>
       <c r="R18" t="n">
-        <v>7008349</v>
+        <v>7008454</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2897,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2949,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122430904</v>
+        <v>122423626</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2965,34 +2960,48 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508916</v>
+        <v>508994</v>
       </c>
       <c r="R19" t="n">
-        <v>7008122</v>
+        <v>7008252</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,6 +3036,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst två individer, möjligen fler.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3039,26 +3053,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3076,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122427629</v>
+        <v>122424114</v>
       </c>
       <c r="B20" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3088,51 +3082,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508574</v>
+        <v>508968</v>
       </c>
       <c r="R20" t="n">
-        <v>7008461</v>
+        <v>7008319</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3164,6 +3148,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3175,7 +3164,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3193,10 +3202,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122429398</v>
+        <v>122426951</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3209,34 +3218,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508809</v>
+        <v>508719</v>
       </c>
       <c r="R21" t="n">
-        <v>7008468</v>
+        <v>7008377</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3271,6 +3285,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3297,12 +3316,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3320,7 +3339,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122423467</v>
+        <v>122424308</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -3356,17 +3375,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508900</v>
+        <v>508903</v>
       </c>
       <c r="R22" t="n">
-        <v>7008203</v>
+        <v>7008351</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3398,6 +3417,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3409,7 +3433,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3447,7 +3471,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122428118</v>
+        <v>122427227</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -3487,13 +3511,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508595</v>
+        <v>508639</v>
       </c>
       <c r="R23" t="n">
-        <v>7008516</v>
+        <v>7008388</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3525,11 +3549,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3546,12 +3565,12 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3561,7 +3580,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3706,10 +3725,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423113</v>
+        <v>122426743</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3722,47 +3741,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508834</v>
+        <v>508764</v>
       </c>
       <c r="R25" t="n">
-        <v>7008115</v>
+        <v>7008423</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3796,7 +3805,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3825,12 +3834,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3848,7 +3857,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429239</v>
+        <v>122424389</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3884,12 +3893,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3898,10 +3902,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508765</v>
+        <v>508892</v>
       </c>
       <c r="R26" t="n">
-        <v>7008466</v>
+        <v>7008349</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3938,7 +3942,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3990,7 +3994,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423040</v>
+        <v>122429239</v>
       </c>
       <c r="B27" t="n">
         <v>57384</v>
@@ -4026,7 +4030,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4036,14 +4040,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508845</v>
+        <v>508765</v>
       </c>
       <c r="R27" t="n">
-        <v>7008072</v>
+        <v>7008466</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -4080,7 +4084,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4132,10 +4136,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122426743</v>
+        <v>122422959</v>
       </c>
       <c r="B28" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4148,34 +4152,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508764</v>
+        <v>508833</v>
       </c>
       <c r="R28" t="n">
-        <v>7008423</v>
+        <v>7008097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4210,11 +4219,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4226,7 +4230,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4241,12 +4245,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423935</v>
+        <v>122427142</v>
       </c>
       <c r="B29" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4280,44 +4284,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508980</v>
+        <v>508688</v>
       </c>
       <c r="R29" t="n">
-        <v>7008294</v>
+        <v>7008395</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4352,11 +4346,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4357,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4383,12 +4372,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4406,7 +4395,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423133</v>
+        <v>122423811</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -4442,7 +4431,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4452,17 +4441,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508834</v>
+        <v>508995</v>
       </c>
       <c r="R30" t="n">
-        <v>7008117</v>
+        <v>7008282</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4496,7 +4485,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4548,10 +4537,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122423626</v>
+        <v>122423040</v>
       </c>
       <c r="B31" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4564,31 +4553,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4598,17 +4583,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508994</v>
+        <v>508845</v>
       </c>
       <c r="R31" t="n">
-        <v>7008252</v>
+        <v>7008072</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4642,7 +4627,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4657,6 +4642,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4674,7 +4679,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423588</v>
+        <v>122429024</v>
       </c>
       <c r="B32" t="n">
         <v>78660</v>
@@ -4714,13 +4719,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508975</v>
+        <v>508746</v>
       </c>
       <c r="R32" t="n">
-        <v>7008243</v>
+        <v>7008449</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122424308</v>
+        <v>122423467</v>
       </c>
       <c r="B33" t="n">
         <v>78660</v>
@@ -4837,17 +4842,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508903</v>
+        <v>508900</v>
       </c>
       <c r="R33" t="n">
-        <v>7008351</v>
+        <v>7008203</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4879,11 +4884,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122424453</v>
+        <v>122429949</v>
       </c>
       <c r="B34" t="n">
         <v>57384</v>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508908</v>
+        <v>508963</v>
       </c>
       <c r="R34" t="n">
-        <v>7008354</v>
+        <v>7008307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122428831</v>
+        <v>122428725</v>
       </c>
       <c r="B35" t="n">
         <v>57384</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508914</v>
+        <v>508919</v>
       </c>
       <c r="R35" t="n">
-        <v>7008313</v>
+        <v>7008295</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122430707</v>
+        <v>122422848</v>
       </c>
       <c r="B36" t="n">
         <v>57384</v>
@@ -5257,14 +5257,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508959</v>
+        <v>508847</v>
       </c>
       <c r="R36" t="n">
-        <v>7008280</v>
+        <v>7008039</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429553</v>
+        <v>122424328</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5369,31 +5369,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5401,10 +5396,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509048</v>
+        <v>508904</v>
       </c>
       <c r="R37" t="n">
-        <v>7008315</v>
+        <v>7008325</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5441,7 +5436,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5450,6 +5445,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5468,14 +5464,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5493,7 +5484,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429949</v>
+        <v>122423202</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -5537,14 +5528,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508963</v>
+        <v>508881</v>
       </c>
       <c r="R38" t="n">
-        <v>7008307</v>
+        <v>7008130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5633,7 +5624,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122423202</v>
+        <v>122423808</v>
       </c>
       <c r="B39" t="n">
         <v>57384</v>
@@ -5677,14 +5668,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508881</v>
+        <v>508966</v>
       </c>
       <c r="R39" t="n">
-        <v>7008130</v>
+        <v>7008356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5773,10 +5764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430040</v>
+        <v>122430707</v>
       </c>
       <c r="B40" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5789,50 +5780,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508930</v>
+        <v>508959</v>
       </c>
       <c r="R40" t="n">
-        <v>7008316</v>
+        <v>7008280</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5867,6 +5850,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5879,6 +5867,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5896,10 +5904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122424038</v>
+        <v>122428462</v>
       </c>
       <c r="B41" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5912,31 +5920,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5944,7 +5947,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508954</v>
+        <v>509040</v>
       </c>
       <c r="R41" t="n">
         <v>7008336</v>
@@ -5982,17 +5985,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6003,22 +6002,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6036,7 +6035,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122428462</v>
+        <v>122429210</v>
       </c>
       <c r="B42" t="n">
         <v>79741</v>
@@ -6079,10 +6078,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509040</v>
+        <v>509071</v>
       </c>
       <c r="R42" t="n">
-        <v>7008336</v>
+        <v>7008310</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6117,6 +6116,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6134,22 +6138,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6167,10 +6166,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429210</v>
+        <v>122429607</v>
       </c>
       <c r="B43" t="n">
-        <v>79741</v>
+        <v>82447</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6183,21 +6182,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6210,10 +6209,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509071</v>
+        <v>509034</v>
       </c>
       <c r="R43" t="n">
-        <v>7008310</v>
+        <v>7008306</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6246,11 +6245,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6298,7 +6292,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423808</v>
+        <v>122428923</v>
       </c>
       <c r="B44" t="n">
         <v>57384</v>
@@ -6346,10 +6340,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508966</v>
+        <v>508978</v>
       </c>
       <c r="R44" t="n">
-        <v>7008356</v>
+        <v>7008270</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6438,10 +6432,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122428777</v>
+        <v>122423484</v>
       </c>
       <c r="B45" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6454,41 +6448,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508909</v>
+        <v>508920</v>
       </c>
       <c r="R45" t="n">
-        <v>7008302</v>
+        <v>7008181</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6523,39 +6518,43 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6573,10 +6572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122423979</v>
+        <v>122429553</v>
       </c>
       <c r="B46" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6589,50 +6588,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508958</v>
+        <v>509048</v>
       </c>
       <c r="R46" t="n">
-        <v>7008338</v>
+        <v>7008315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6667,6 +6658,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6679,6 +6675,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6696,10 +6712,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428487</v>
+        <v>122424453</v>
       </c>
       <c r="B47" t="n">
-        <v>79777</v>
+        <v>57384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6708,30 +6724,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6739,10 +6760,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509041</v>
+        <v>508908</v>
       </c>
       <c r="R47" t="n">
-        <v>7008337</v>
+        <v>7008354</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6777,13 +6798,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6794,22 +6819,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6827,10 +6852,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122429607</v>
+        <v>122430040</v>
       </c>
       <c r="B48" t="n">
-        <v>82447</v>
+        <v>57537</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6843,37 +6868,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509034</v>
+        <v>508930</v>
       </c>
       <c r="R48" t="n">
-        <v>7008306</v>
+        <v>7008316</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6914,28 +6952,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6953,7 +6975,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122422848</v>
+        <v>122423524</v>
       </c>
       <c r="B49" t="n">
         <v>57384</v>
@@ -7001,10 +7023,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508847</v>
+        <v>508928</v>
       </c>
       <c r="R49" t="n">
-        <v>7008039</v>
+        <v>7008172</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7041,7 +7063,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7055,17 +7077,17 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -7075,7 +7097,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7093,7 +7115,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122423524</v>
+        <v>122424038</v>
       </c>
       <c r="B50" t="n">
         <v>57384</v>
@@ -7137,14 +7159,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508928</v>
+        <v>508954</v>
       </c>
       <c r="R50" t="n">
-        <v>7008172</v>
+        <v>7008336</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7181,7 +7203,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7195,17 +7217,17 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -7215,7 +7237,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7233,7 +7255,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428725</v>
+        <v>122428831</v>
       </c>
       <c r="B51" t="n">
         <v>57384</v>
@@ -7281,10 +7303,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508919</v>
+        <v>508914</v>
       </c>
       <c r="R51" t="n">
-        <v>7008295</v>
+        <v>7008313</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7373,10 +7395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122424304</v>
+        <v>122430628</v>
       </c>
       <c r="B52" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7389,28 +7411,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7420,10 +7443,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508904</v>
+        <v>508965</v>
       </c>
       <c r="R52" t="n">
-        <v>7008325</v>
+        <v>7008296</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7458,13 +7481,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7475,22 +7502,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7508,10 +7535,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430628</v>
+        <v>122428487</v>
       </c>
       <c r="B53" t="n">
-        <v>57384</v>
+        <v>79777</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7520,35 +7547,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7556,10 +7578,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508965</v>
+        <v>509041</v>
       </c>
       <c r="R53" t="n">
-        <v>7008296</v>
+        <v>7008337</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7594,17 +7616,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7615,22 +7633,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7648,7 +7666,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428923</v>
+        <v>122424126</v>
       </c>
       <c r="B54" t="n">
         <v>57384</v>
@@ -7696,10 +7714,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508978</v>
+        <v>508950</v>
       </c>
       <c r="R54" t="n">
-        <v>7008270</v>
+        <v>7008334</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7788,10 +7806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122424126</v>
+        <v>122428777</v>
       </c>
       <c r="B55" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7804,29 +7822,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7836,10 +7853,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508950</v>
+        <v>508909</v>
       </c>
       <c r="R55" t="n">
-        <v>7008334</v>
+        <v>7008302</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7874,17 +7891,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7895,22 +7908,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7928,10 +7941,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122423484</v>
+        <v>122423979</v>
       </c>
       <c r="B56" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7944,42 +7957,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508920</v>
+        <v>508958</v>
       </c>
       <c r="R56" t="n">
-        <v>7008181</v>
+        <v>7008338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8014,11 +8035,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8030,27 +8046,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8203,7 +8199,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424589</v>
+        <v>122424676</v>
       </c>
       <c r="B58" t="n">
         <v>57384</v>
@@ -8251,10 +8247,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508831</v>
+        <v>508779</v>
       </c>
       <c r="R58" t="n">
-        <v>7008397</v>
+        <v>7008383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8318,14 +8314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8343,10 +8334,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424496</v>
+        <v>122426947</v>
       </c>
       <c r="B59" t="n">
-        <v>57384</v>
+        <v>56586</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8359,16 +8350,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8376,12 +8367,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8391,10 +8386,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508891</v>
+        <v>508535</v>
       </c>
       <c r="R59" t="n">
-        <v>7008386</v>
+        <v>7008440</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8429,11 +8424,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8445,27 +8435,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8483,7 +8453,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427127</v>
+        <v>122426823</v>
       </c>
       <c r="B60" t="n">
         <v>57384</v>
@@ -8521,7 +8491,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8531,10 +8501,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508631</v>
+        <v>508614</v>
       </c>
       <c r="R60" t="n">
-        <v>7008480</v>
+        <v>7008464</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8571,7 +8541,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8585,7 +8555,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8598,9 +8568,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8618,7 +8593,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424611</v>
+        <v>122429281</v>
       </c>
       <c r="B61" t="n">
         <v>57384</v>
@@ -8666,10 +8641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508820</v>
+        <v>509109</v>
       </c>
       <c r="R61" t="n">
-        <v>7008398</v>
+        <v>7008253</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8733,14 +8708,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8758,7 +8728,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424676</v>
+        <v>122424496</v>
       </c>
       <c r="B62" t="n">
         <v>57384</v>
@@ -8806,10 +8776,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508779</v>
+        <v>508891</v>
       </c>
       <c r="R62" t="n">
-        <v>7008383</v>
+        <v>7008386</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8873,9 +8843,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8893,10 +8868,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122427444</v>
+        <v>122424707</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8909,26 +8884,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8936,10 +8916,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508541</v>
+        <v>508781</v>
       </c>
       <c r="R63" t="n">
-        <v>7008422</v>
+        <v>7008382</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8976,7 +8956,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8985,33 +8965,32 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9029,7 +9008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427681</v>
+        <v>122427127</v>
       </c>
       <c r="B64" t="n">
         <v>57384</v>
@@ -9077,10 +9056,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508760</v>
+        <v>508631</v>
       </c>
       <c r="R64" t="n">
-        <v>7008533</v>
+        <v>7008480</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9117,7 +9096,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9131,7 +9110,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -9144,14 +9123,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9169,10 +9143,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429281</v>
+        <v>122427444</v>
       </c>
       <c r="B65" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9185,31 +9159,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9217,10 +9186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>509109</v>
+        <v>508541</v>
       </c>
       <c r="R65" t="n">
-        <v>7008253</v>
+        <v>7008422</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9257,7 +9226,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9266,27 +9235,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9304,10 +9279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122426947</v>
+        <v>122424611</v>
       </c>
       <c r="B66" t="n">
-        <v>56586</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9320,16 +9295,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9337,16 +9312,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9356,10 +9327,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508535</v>
+        <v>508820</v>
       </c>
       <c r="R66" t="n">
-        <v>7008440</v>
+        <v>7008398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9394,6 +9365,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9405,7 +9381,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9423,7 +9419,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427763</v>
+        <v>122427681</v>
       </c>
       <c r="B67" t="n">
         <v>57384</v>
@@ -9461,7 +9457,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9471,7 +9467,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508776</v>
+        <v>508760</v>
       </c>
       <c r="R67" t="n">
         <v>7008533</v>
@@ -9511,7 +9507,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9563,7 +9559,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424707</v>
+        <v>122424589</v>
       </c>
       <c r="B68" t="n">
         <v>57384</v>
@@ -9601,7 +9597,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9611,10 +9607,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508781</v>
+        <v>508831</v>
       </c>
       <c r="R68" t="n">
-        <v>7008382</v>
+        <v>7008397</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9651,7 +9647,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9703,7 +9699,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426823</v>
+        <v>122427763</v>
       </c>
       <c r="B69" t="n">
         <v>57384</v>
@@ -9751,10 +9747,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508614</v>
+        <v>508776</v>
       </c>
       <c r="R69" t="n">
-        <v>7008464</v>
+        <v>7008533</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428118</v>
+        <v>122422838</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508595</v>
+        <v>508855</v>
       </c>
       <c r="R2" t="n">
-        <v>7008516</v>
+        <v>7008046</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -784,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122422838</v>
+        <v>122428118</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508855</v>
+        <v>508595</v>
       </c>
       <c r="R3" t="n">
-        <v>7008046</v>
+        <v>7008516</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122423133</v>
+        <v>122426582</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2417,7 +2417,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508834</v>
+        <v>508771</v>
       </c>
       <c r="R15" t="n">
-        <v>7008117</v>
+        <v>7008433</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122426582</v>
+        <v>122423133</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2539,16 +2539,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2559,7 +2559,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508771</v>
+        <v>508834</v>
       </c>
       <c r="R16" t="n">
-        <v>7008433</v>
+        <v>7008117</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122423287</v>
+        <v>122424389</v>
       </c>
       <c r="B24" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3614,37 +3614,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508887</v>
+        <v>508892</v>
       </c>
       <c r="R24" t="n">
-        <v>7008167</v>
+        <v>7008349</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3676,6 +3681,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3687,7 +3697,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3702,12 +3712,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3725,10 +3735,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122426743</v>
+        <v>122429239</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3741,37 +3751,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508764</v>
+        <v>508765</v>
       </c>
       <c r="R25" t="n">
-        <v>7008423</v>
+        <v>7008466</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3805,7 +3825,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3834,12 +3854,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3857,10 +3877,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122424389</v>
+        <v>122423287</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3873,42 +3893,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508892</v>
+        <v>508887</v>
       </c>
       <c r="R26" t="n">
-        <v>7008349</v>
+        <v>7008167</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3940,11 +3955,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3956,7 +3966,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3971,12 +3981,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3994,10 +4004,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122429239</v>
+        <v>122426743</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4010,47 +4020,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508765</v>
+        <v>508764</v>
       </c>
       <c r="R27" t="n">
-        <v>7008466</v>
+        <v>7008423</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427444</v>
+        <v>122424611</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9159,26 +9159,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9186,10 +9191,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508541</v>
+        <v>508820</v>
       </c>
       <c r="R65" t="n">
-        <v>7008422</v>
+        <v>7008398</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9226,7 +9231,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9235,33 +9240,32 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9279,10 +9283,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424611</v>
+        <v>122427444</v>
       </c>
       <c r="B66" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9295,31 +9299,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9327,10 +9326,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508820</v>
+        <v>508541</v>
       </c>
       <c r="R66" t="n">
-        <v>7008398</v>
+        <v>7008422</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9367,7 +9366,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9376,32 +9375,33 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122422838</v>
+        <v>122428118</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508855</v>
+        <v>508595</v>
       </c>
       <c r="R2" t="n">
-        <v>7008046</v>
+        <v>7008516</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -765,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428118</v>
+        <v>122422838</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,34 +823,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508595</v>
+        <v>508855</v>
       </c>
       <c r="R3" t="n">
-        <v>7008516</v>
+        <v>7008046</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122426582</v>
+        <v>122423133</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2417,7 +2417,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508771</v>
+        <v>508834</v>
       </c>
       <c r="R15" t="n">
-        <v>7008433</v>
+        <v>7008117</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122423133</v>
+        <v>122426582</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2539,16 +2539,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2559,7 +2559,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508834</v>
+        <v>508771</v>
       </c>
       <c r="R16" t="n">
-        <v>7008117</v>
+        <v>7008433</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424389</v>
+        <v>122423287</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3614,42 +3614,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508892</v>
+        <v>508887</v>
       </c>
       <c r="R24" t="n">
-        <v>7008349</v>
+        <v>7008167</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3681,11 +3676,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3697,7 +3687,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3712,12 +3702,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3735,10 +3725,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122429239</v>
+        <v>122426743</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3751,47 +3741,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508765</v>
+        <v>508764</v>
       </c>
       <c r="R25" t="n">
-        <v>7008466</v>
+        <v>7008423</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3825,7 +3805,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3854,12 +3834,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3877,10 +3857,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122423287</v>
+        <v>122424389</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3893,37 +3873,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508887</v>
+        <v>508892</v>
       </c>
       <c r="R26" t="n">
-        <v>7008167</v>
+        <v>7008349</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3955,6 +3940,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3966,7 +3956,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3981,12 +3971,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4004,10 +3994,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122426743</v>
+        <v>122429239</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4020,37 +4010,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508764</v>
+        <v>508765</v>
       </c>
       <c r="R27" t="n">
-        <v>7008423</v>
+        <v>7008466</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack främst på stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424611</v>
+        <v>122427444</v>
       </c>
       <c r="B65" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9159,31 +9159,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9191,10 +9186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508820</v>
+        <v>508541</v>
       </c>
       <c r="R65" t="n">
-        <v>7008398</v>
+        <v>7008422</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9231,7 +9226,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9240,32 +9235,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9283,10 +9279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427444</v>
+        <v>122424611</v>
       </c>
       <c r="B66" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9299,26 +9295,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9326,10 +9327,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508541</v>
+        <v>508820</v>
       </c>
       <c r="R66" t="n">
-        <v>7008422</v>
+        <v>7008398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9366,7 +9367,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9375,33 +9376,32 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428118</v>
+        <v>122422838</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508595</v>
+        <v>508855</v>
       </c>
       <c r="R2" t="n">
-        <v>7008516</v>
+        <v>7008046</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -784,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122422838</v>
+        <v>122428118</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508855</v>
+        <v>508595</v>
       </c>
       <c r="R3" t="n">
-        <v>7008046</v>
+        <v>7008516</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -2273,7 +2273,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423467</v>
+        <v>122430904</v>
       </c>
       <c r="B14" t="n">
         <v>78762</v>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508900</v>
+        <v>508916</v>
       </c>
       <c r="R14" t="n">
-        <v>7008203</v>
+        <v>7008122</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122430904</v>
+        <v>122423467</v>
       </c>
       <c r="B15" t="n">
         <v>78762</v>
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508916</v>
+        <v>508900</v>
       </c>
       <c r="R15" t="n">
-        <v>7008122</v>
+        <v>7008203</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122429398</v>
+        <v>122423935</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4040,34 +4040,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508809</v>
+        <v>508980</v>
       </c>
       <c r="R27" t="n">
-        <v>7008468</v>
+        <v>7008294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4102,6 +4112,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4128,12 +4143,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4166,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122423588</v>
+        <v>122428937</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4167,37 +4182,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508975</v>
+        <v>508739</v>
       </c>
       <c r="R28" t="n">
-        <v>7008243</v>
+        <v>7008454</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4229,6 +4249,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4255,12 +4280,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4278,10 +4303,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122423935</v>
+        <v>122429398</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4294,44 +4319,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508980</v>
+        <v>508809</v>
       </c>
       <c r="R29" t="n">
-        <v>7008294</v>
+        <v>7008468</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,11 +4381,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4397,12 +4407,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4420,10 +4430,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122428937</v>
+        <v>122423588</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4436,42 +4446,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508739</v>
+        <v>508975</v>
       </c>
       <c r="R30" t="n">
-        <v>7008454</v>
+        <v>7008243</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4503,11 +4508,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack som bedöms skapade inom 5 år tillbaks.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -2273,7 +2273,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122430904</v>
+        <v>122423467</v>
       </c>
       <c r="B14" t="n">
         <v>78762</v>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508916</v>
+        <v>508900</v>
       </c>
       <c r="R14" t="n">
-        <v>7008122</v>
+        <v>7008203</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122423467</v>
+        <v>122430904</v>
       </c>
       <c r="B15" t="n">
         <v>78762</v>
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508900</v>
+        <v>508916</v>
       </c>
       <c r="R15" t="n">
-        <v>7008203</v>
+        <v>7008122</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423524</v>
+        <v>122430628</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4977,14 +4977,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508928</v>
+        <v>508965</v>
       </c>
       <c r="R34" t="n">
-        <v>7008172</v>
+        <v>7008296</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5035,17 +5035,17 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5076,7 +5076,7 @@
         <v>122428777</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122423808</v>
+        <v>122424038</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508966</v>
+        <v>508954</v>
       </c>
       <c r="R36" t="n">
-        <v>7008356</v>
+        <v>7008336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429949</v>
+        <v>122423524</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5392,14 +5392,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508963</v>
+        <v>508928</v>
       </c>
       <c r="R37" t="n">
-        <v>7008307</v>
+        <v>7008172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429210</v>
+        <v>122429553</v>
       </c>
       <c r="B38" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5504,26 +5504,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509071</v>
+        <v>509048</v>
       </c>
       <c r="R38" t="n">
-        <v>7008310</v>
+        <v>7008315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5571,7 +5576,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5580,7 +5585,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5599,9 +5603,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5619,10 +5628,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430707</v>
+        <v>122428462</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5635,31 +5644,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5667,10 +5671,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508959</v>
+        <v>509040</v>
       </c>
       <c r="R39" t="n">
-        <v>7008280</v>
+        <v>7008336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5705,17 +5709,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5726,22 +5726,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122428923</v>
+        <v>122429210</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5775,31 +5775,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5807,10 +5802,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508978</v>
+        <v>509071</v>
       </c>
       <c r="R40" t="n">
-        <v>7008270</v>
+        <v>7008310</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5847,7 +5842,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5856,6 +5851,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5874,14 +5870,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5899,10 +5890,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122423979</v>
+        <v>122424126</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5915,50 +5906,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508958</v>
+        <v>508950</v>
       </c>
       <c r="R41" t="n">
-        <v>7008338</v>
+        <v>7008334</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5993,6 +5976,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -6005,6 +5993,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6022,10 +6030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122424304</v>
+        <v>122422848</v>
       </c>
       <c r="B42" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6038,41 +6046,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508904</v>
+        <v>508847</v>
       </c>
       <c r="R42" t="n">
-        <v>7008325</v>
+        <v>7008039</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6107,13 +6116,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6124,22 +6137,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6157,7 +6170,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429553</v>
+        <v>122428725</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -6205,10 +6218,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509048</v>
+        <v>508919</v>
       </c>
       <c r="R43" t="n">
-        <v>7008315</v>
+        <v>7008295</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6297,7 +6310,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122424038</v>
+        <v>122423808</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6345,10 +6358,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508954</v>
+        <v>508966</v>
       </c>
       <c r="R44" t="n">
-        <v>7008336</v>
+        <v>7008356</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6577,7 +6590,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122424126</v>
+        <v>122424453</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -6625,10 +6638,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508950</v>
+        <v>508908</v>
       </c>
       <c r="R46" t="n">
-        <v>7008334</v>
+        <v>7008354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6717,10 +6730,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428487</v>
+        <v>122428923</v>
       </c>
       <c r="B47" t="n">
-        <v>79879</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6729,30 +6742,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6760,10 +6778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509041</v>
+        <v>508978</v>
       </c>
       <c r="R47" t="n">
-        <v>7008337</v>
+        <v>7008270</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6798,13 +6816,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6815,22 +6837,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6848,10 +6870,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122428831</v>
+        <v>122424304</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6864,29 +6886,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6896,10 +6917,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508914</v>
+        <v>508904</v>
       </c>
       <c r="R48" t="n">
-        <v>7008313</v>
+        <v>7008325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6934,17 +6955,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6955,22 +6972,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6988,7 +7005,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428725</v>
+        <v>122430707</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -7036,10 +7053,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508919</v>
+        <v>508959</v>
       </c>
       <c r="R49" t="n">
-        <v>7008295</v>
+        <v>7008280</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7128,7 +7145,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122424453</v>
+        <v>122429949</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -7176,10 +7193,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508908</v>
+        <v>508963</v>
       </c>
       <c r="R50" t="n">
-        <v>7008354</v>
+        <v>7008307</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7268,10 +7285,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122430628</v>
+        <v>122428487</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7280,35 +7297,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7316,10 +7328,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508965</v>
+        <v>509041</v>
       </c>
       <c r="R51" t="n">
-        <v>7008296</v>
+        <v>7008337</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7354,17 +7366,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7375,22 +7383,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7408,10 +7416,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122422848</v>
+        <v>122430040</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7424,42 +7432,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508847</v>
+        <v>508930</v>
       </c>
       <c r="R52" t="n">
-        <v>7008039</v>
+        <v>7008316</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7494,11 +7510,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7511,26 +7522,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7551,7 +7542,7 @@
         <v>122429607</v>
       </c>
       <c r="B53" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7674,10 +7665,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428462</v>
+        <v>122428831</v>
       </c>
       <c r="B54" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7690,26 +7681,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7717,10 +7713,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>509040</v>
+        <v>508914</v>
       </c>
       <c r="R54" t="n">
-        <v>7008336</v>
+        <v>7008313</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7755,13 +7751,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7772,22 +7772,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430040</v>
+        <v>122423979</v>
       </c>
       <c r="B56" t="n">
         <v>57631</v>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -8001,10 +8001,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508930</v>
+        <v>508958</v>
       </c>
       <c r="R56" t="n">
-        <v>7008316</v>
+        <v>7008338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122426947</v>
+        <v>122424496</v>
       </c>
       <c r="B57" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8084,16 +8084,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8101,16 +8101,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8120,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508535</v>
+        <v>508891</v>
       </c>
       <c r="R57" t="n">
-        <v>7008440</v>
+        <v>7008386</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8158,6 +8154,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8169,7 +8170,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8187,7 +8208,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424611</v>
+        <v>122424707</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8225,7 +8246,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8235,10 +8256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508820</v>
+        <v>508781</v>
       </c>
       <c r="R58" t="n">
-        <v>7008398</v>
+        <v>7008382</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8275,7 +8296,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8327,7 +8348,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427586</v>
+        <v>122424611</v>
       </c>
       <c r="B59" t="n">
         <v>57478</v>
@@ -8375,10 +8396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508745</v>
+        <v>508820</v>
       </c>
       <c r="R59" t="n">
-        <v>7008511</v>
+        <v>7008398</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8442,9 +8463,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8462,7 +8488,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122429281</v>
+        <v>122427586</v>
       </c>
       <c r="B60" t="n">
         <v>57478</v>
@@ -8510,10 +8536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>509109</v>
+        <v>508745</v>
       </c>
       <c r="R60" t="n">
-        <v>7008253</v>
+        <v>7008511</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8597,7 +8623,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424589</v>
+        <v>122427681</v>
       </c>
       <c r="B61" t="n">
         <v>57478</v>
@@ -8645,10 +8671,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508831</v>
+        <v>508760</v>
       </c>
       <c r="R61" t="n">
-        <v>7008397</v>
+        <v>7008533</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8737,7 +8763,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427127</v>
+        <v>122424589</v>
       </c>
       <c r="B62" t="n">
         <v>57478</v>
@@ -8785,10 +8811,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508631</v>
+        <v>508831</v>
       </c>
       <c r="R62" t="n">
-        <v>7008480</v>
+        <v>7008397</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8825,7 +8851,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8839,7 +8865,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8852,9 +8878,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8872,7 +8903,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122427681</v>
+        <v>122424676</v>
       </c>
       <c r="B63" t="n">
         <v>57478</v>
@@ -8920,10 +8951,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508760</v>
+        <v>508779</v>
       </c>
       <c r="R63" t="n">
-        <v>7008533</v>
+        <v>7008383</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8987,14 +9018,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9012,7 +9038,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424676</v>
+        <v>122429281</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -9060,10 +9086,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508779</v>
+        <v>509109</v>
       </c>
       <c r="R64" t="n">
-        <v>7008383</v>
+        <v>7008253</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9147,10 +9173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424496</v>
+        <v>122426947</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9163,16 +9189,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9180,12 +9206,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9195,10 +9225,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508891</v>
+        <v>508535</v>
       </c>
       <c r="R65" t="n">
-        <v>7008386</v>
+        <v>7008440</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9233,11 +9263,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9249,27 +9274,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9287,7 +9292,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424707</v>
+        <v>122427763</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -9335,10 +9340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508781</v>
+        <v>508776</v>
       </c>
       <c r="R66" t="n">
-        <v>7008382</v>
+        <v>7008533</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9427,7 +9432,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427763</v>
+        <v>122427127</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -9465,7 +9470,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9475,10 +9480,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508776</v>
+        <v>508631</v>
       </c>
       <c r="R67" t="n">
-        <v>7008533</v>
+        <v>7008480</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9529,7 +9534,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9542,14 +9547,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9570,7 +9570,7 @@
         <v>122427444</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122430628</v>
+        <v>122423524</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4977,14 +4977,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508965</v>
+        <v>508928</v>
       </c>
       <c r="R34" t="n">
-        <v>7008296</v>
+        <v>7008172</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5035,17 +5035,17 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122428777</v>
+        <v>122424304</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508909</v>
+        <v>508904</v>
       </c>
       <c r="R35" t="n">
-        <v>7008302</v>
+        <v>7008325</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122424038</v>
+        <v>122422848</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5252,14 +5252,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508954</v>
+        <v>508847</v>
       </c>
       <c r="R36" t="n">
-        <v>7008336</v>
+        <v>7008039</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122423524</v>
+        <v>122429607</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5364,42 +5364,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508928</v>
+        <v>509034</v>
       </c>
       <c r="R37" t="n">
-        <v>7008172</v>
+        <v>7008306</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5434,43 +5429,34 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5488,7 +5474,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429553</v>
+        <v>122423202</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5532,14 +5518,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509048</v>
+        <v>508881</v>
       </c>
       <c r="R38" t="n">
-        <v>7008315</v>
+        <v>7008130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5628,10 +5614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122428462</v>
+        <v>122424453</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5644,26 +5630,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5671,10 +5662,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509040</v>
+        <v>508908</v>
       </c>
       <c r="R39" t="n">
-        <v>7008336</v>
+        <v>7008354</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5709,13 +5700,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5726,22 +5721,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5759,10 +5754,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122429210</v>
+        <v>122430707</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5775,26 +5770,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509071</v>
+        <v>508959</v>
       </c>
       <c r="R40" t="n">
-        <v>7008310</v>
+        <v>7008280</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5851,7 +5851,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5870,9 +5869,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5890,10 +5894,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122424126</v>
+        <v>122430040</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5906,42 +5910,50 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508950</v>
+        <v>508930</v>
       </c>
       <c r="R41" t="n">
-        <v>7008334</v>
+        <v>7008316</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,11 +5988,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5993,26 +6000,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6030,7 +6017,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122422848</v>
+        <v>122428923</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -6074,14 +6061,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508847</v>
+        <v>508978</v>
       </c>
       <c r="R42" t="n">
-        <v>7008039</v>
+        <v>7008270</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6170,10 +6157,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122428725</v>
+        <v>122423979</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6186,42 +6173,50 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508919</v>
+        <v>508958</v>
       </c>
       <c r="R43" t="n">
-        <v>7008295</v>
+        <v>7008338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6256,11 +6251,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6273,26 +6263,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6310,10 +6280,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122423808</v>
+        <v>122428487</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6322,35 +6292,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6358,10 +6323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>508966</v>
+        <v>509041</v>
       </c>
       <c r="R44" t="n">
-        <v>7008356</v>
+        <v>7008337</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6396,17 +6361,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6417,22 +6378,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6450,10 +6411,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122423202</v>
+        <v>122428777</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6466,42 +6427,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508881</v>
+        <v>508909</v>
       </c>
       <c r="R45" t="n">
-        <v>7008130</v>
+        <v>7008302</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6536,17 +6496,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6557,22 +6513,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6590,7 +6546,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122424453</v>
+        <v>122423808</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -6638,10 +6594,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508908</v>
+        <v>508966</v>
       </c>
       <c r="R46" t="n">
-        <v>7008354</v>
+        <v>7008356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6730,7 +6686,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428923</v>
+        <v>122429553</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -6778,10 +6734,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508978</v>
+        <v>509048</v>
       </c>
       <c r="R47" t="n">
-        <v>7008270</v>
+        <v>7008315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6870,10 +6826,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122424304</v>
+        <v>122430628</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6886,28 +6842,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6917,10 +6874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508904</v>
+        <v>508965</v>
       </c>
       <c r="R48" t="n">
-        <v>7008325</v>
+        <v>7008296</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6955,13 +6912,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6972,22 +6933,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7005,10 +6966,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430707</v>
+        <v>122429210</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7021,31 +6982,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -7053,10 +7009,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508959</v>
+        <v>509071</v>
       </c>
       <c r="R49" t="n">
-        <v>7008280</v>
+        <v>7008310</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7093,7 +7049,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7102,6 +7058,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7120,14 +7077,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7145,7 +7097,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429949</v>
+        <v>122424126</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -7193,10 +7145,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508963</v>
+        <v>508950</v>
       </c>
       <c r="R50" t="n">
-        <v>7008307</v>
+        <v>7008334</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7285,10 +7237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428487</v>
+        <v>122429949</v>
       </c>
       <c r="B51" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7297,30 +7249,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7328,10 +7285,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509041</v>
+        <v>508963</v>
       </c>
       <c r="R51" t="n">
-        <v>7008337</v>
+        <v>7008307</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7366,13 +7323,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7383,22 +7344,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7416,10 +7377,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122430040</v>
+        <v>122428831</v>
       </c>
       <c r="B52" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7432,50 +7393,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508930</v>
+        <v>508914</v>
       </c>
       <c r="R52" t="n">
-        <v>7008316</v>
+        <v>7008313</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7510,6 +7463,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7522,6 +7480,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7539,10 +7517,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122429607</v>
+        <v>122428725</v>
       </c>
       <c r="B53" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7555,26 +7533,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7582,10 +7565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>509034</v>
+        <v>508919</v>
       </c>
       <c r="R53" t="n">
-        <v>7008306</v>
+        <v>7008295</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7620,13 +7603,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7645,9 +7632,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7665,7 +7657,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428831</v>
+        <v>122423484</v>
       </c>
       <c r="B54" t="n">
         <v>57478</v>
@@ -7709,14 +7701,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508914</v>
+        <v>508920</v>
       </c>
       <c r="R54" t="n">
-        <v>7008313</v>
+        <v>7008181</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7753,7 +7745,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7767,17 +7759,17 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -7787,7 +7779,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7805,10 +7797,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122423484</v>
+        <v>122428462</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7821,42 +7813,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508920</v>
+        <v>509040</v>
       </c>
       <c r="R55" t="n">
-        <v>7008181</v>
+        <v>7008336</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7891,43 +7878,39 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7945,10 +7928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122423979</v>
+        <v>122424038</v>
       </c>
       <c r="B56" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7961,50 +7944,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508958</v>
+        <v>508954</v>
       </c>
       <c r="R56" t="n">
-        <v>7008338</v>
+        <v>7008336</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8039,6 +8014,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8051,6 +8031,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122424496</v>
+        <v>122427444</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8084,31 +8084,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8116,10 +8111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508891</v>
+        <v>508541</v>
       </c>
       <c r="R57" t="n">
-        <v>7008386</v>
+        <v>7008422</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8156,7 +8151,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8165,32 +8160,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8208,7 +8204,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424707</v>
+        <v>122429281</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8246,7 +8242,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8256,10 +8252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508781</v>
+        <v>509109</v>
       </c>
       <c r="R58" t="n">
-        <v>7008382</v>
+        <v>7008253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8296,7 +8292,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8323,14 +8319,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8348,7 +8339,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424611</v>
+        <v>122424496</v>
       </c>
       <c r="B59" t="n">
         <v>57478</v>
@@ -8396,10 +8387,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508820</v>
+        <v>508891</v>
       </c>
       <c r="R59" t="n">
-        <v>7008398</v>
+        <v>7008386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8465,12 +8456,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8488,7 +8479,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427586</v>
+        <v>122427763</v>
       </c>
       <c r="B60" t="n">
         <v>57478</v>
@@ -8526,7 +8517,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8536,10 +8527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508745</v>
+        <v>508776</v>
       </c>
       <c r="R60" t="n">
-        <v>7008511</v>
+        <v>7008533</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8576,7 +8567,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8603,9 +8594,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8623,7 +8619,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427681</v>
+        <v>122427127</v>
       </c>
       <c r="B61" t="n">
         <v>57478</v>
@@ -8671,10 +8667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508760</v>
+        <v>508631</v>
       </c>
       <c r="R61" t="n">
-        <v>7008533</v>
+        <v>7008480</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8711,7 +8707,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8725,7 +8721,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8738,14 +8734,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8763,7 +8754,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424589</v>
+        <v>122427586</v>
       </c>
       <c r="B62" t="n">
         <v>57478</v>
@@ -8811,10 +8802,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508831</v>
+        <v>508745</v>
       </c>
       <c r="R62" t="n">
-        <v>7008397</v>
+        <v>7008511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8878,14 +8869,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8903,7 +8889,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424676</v>
+        <v>122426823</v>
       </c>
       <c r="B63" t="n">
         <v>57478</v>
@@ -8941,7 +8927,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8951,10 +8937,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508779</v>
+        <v>508614</v>
       </c>
       <c r="R63" t="n">
-        <v>7008383</v>
+        <v>7008464</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8991,7 +8977,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9018,9 +9004,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9038,7 +9029,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122429281</v>
+        <v>122424707</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -9076,7 +9067,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -9086,10 +9077,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509109</v>
+        <v>508781</v>
       </c>
       <c r="R64" t="n">
-        <v>7008253</v>
+        <v>7008382</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9126,7 +9117,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9153,9 +9144,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9173,10 +9169,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122426947</v>
+        <v>122424589</v>
       </c>
       <c r="B65" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9189,16 +9185,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9206,16 +9202,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9225,10 +9217,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508535</v>
+        <v>508831</v>
       </c>
       <c r="R65" t="n">
-        <v>7008440</v>
+        <v>7008397</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9263,6 +9255,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9274,7 +9271,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9292,7 +9309,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427763</v>
+        <v>122424611</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -9330,7 +9347,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9340,10 +9357,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508776</v>
+        <v>508820</v>
       </c>
       <c r="R66" t="n">
-        <v>7008533</v>
+        <v>7008398</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9380,7 +9397,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9432,7 +9449,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427127</v>
+        <v>122427681</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -9480,10 +9497,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508631</v>
+        <v>508760</v>
       </c>
       <c r="R67" t="n">
-        <v>7008480</v>
+        <v>7008533</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9520,7 +9537,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9534,7 +9551,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9547,9 +9564,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9567,10 +9589,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122427444</v>
+        <v>122426947</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9583,26 +9605,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9610,10 +9641,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508541</v>
+        <v>508535</v>
       </c>
       <c r="R68" t="n">
-        <v>7008422</v>
+        <v>7008440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9648,44 +9679,18 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
           <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9703,7 +9708,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426823</v>
+        <v>122424676</v>
       </c>
       <c r="B69" t="n">
         <v>57478</v>
@@ -9741,7 +9746,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9751,10 +9756,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508614</v>
+        <v>508779</v>
       </c>
       <c r="R69" t="n">
-        <v>7008464</v>
+        <v>7008383</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9791,7 +9796,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9818,14 +9823,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -8068,10 +8068,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427444</v>
+        <v>122429281</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8084,26 +8084,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8111,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508541</v>
+        <v>509109</v>
       </c>
       <c r="R57" t="n">
-        <v>7008422</v>
+        <v>7008253</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8151,7 +8156,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8160,33 +8165,27 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8204,7 +8203,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122429281</v>
+        <v>122427586</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8252,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>509109</v>
+        <v>508745</v>
       </c>
       <c r="R58" t="n">
-        <v>7008253</v>
+        <v>7008511</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8339,10 +8338,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424496</v>
+        <v>122427444</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8355,31 +8354,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8387,10 +8381,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508891</v>
+        <v>508541</v>
       </c>
       <c r="R59" t="n">
-        <v>7008386</v>
+        <v>7008422</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8427,7 +8421,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8436,32 +8430,33 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8479,7 +8474,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427763</v>
+        <v>122427681</v>
       </c>
       <c r="B60" t="n">
         <v>57478</v>
@@ -8517,7 +8512,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8527,7 +8522,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508776</v>
+        <v>508760</v>
       </c>
       <c r="R60" t="n">
         <v>7008533</v>
@@ -8567,7 +8562,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8619,7 +8614,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427127</v>
+        <v>122424676</v>
       </c>
       <c r="B61" t="n">
         <v>57478</v>
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508631</v>
+        <v>508779</v>
       </c>
       <c r="R61" t="n">
-        <v>7008480</v>
+        <v>7008383</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8707,7 +8702,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8721,7 +8716,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8754,7 +8749,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427586</v>
+        <v>122424611</v>
       </c>
       <c r="B62" t="n">
         <v>57478</v>
@@ -8802,10 +8797,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508745</v>
+        <v>508820</v>
       </c>
       <c r="R62" t="n">
-        <v>7008511</v>
+        <v>7008398</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8869,9 +8864,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426823</v>
+        <v>122426947</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8922,12 +8922,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8937,10 +8941,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508614</v>
+        <v>508535</v>
       </c>
       <c r="R63" t="n">
-        <v>7008464</v>
+        <v>7008440</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8975,11 +8979,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8991,27 +8990,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9029,7 +9008,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424707</v>
+        <v>122426823</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -9077,10 +9056,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508781</v>
+        <v>508614</v>
       </c>
       <c r="R64" t="n">
-        <v>7008382</v>
+        <v>7008464</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9169,7 +9148,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122424589</v>
+        <v>122427763</v>
       </c>
       <c r="B65" t="n">
         <v>57478</v>
@@ -9207,7 +9186,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9217,10 +9196,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508831</v>
+        <v>508776</v>
       </c>
       <c r="R65" t="n">
-        <v>7008397</v>
+        <v>7008533</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9257,7 +9236,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9309,7 +9288,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424611</v>
+        <v>122424707</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -9347,7 +9326,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9357,10 +9336,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508820</v>
+        <v>508781</v>
       </c>
       <c r="R66" t="n">
-        <v>7008398</v>
+        <v>7008382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9397,7 +9376,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9449,7 +9428,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427681</v>
+        <v>122424496</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -9497,10 +9476,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508760</v>
+        <v>508891</v>
       </c>
       <c r="R67" t="n">
-        <v>7008533</v>
+        <v>7008386</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9566,12 +9545,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9589,10 +9568,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122426947</v>
+        <v>122427127</v>
       </c>
       <c r="B68" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9605,16 +9584,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9622,16 +9601,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9641,10 +9616,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508535</v>
+        <v>508631</v>
       </c>
       <c r="R68" t="n">
-        <v>7008440</v>
+        <v>7008480</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9679,6 +9654,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9690,7 +9670,22 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9708,7 +9703,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424676</v>
+        <v>122424589</v>
       </c>
       <c r="B69" t="n">
         <v>57478</v>
@@ -9756,10 +9751,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508779</v>
+        <v>508831</v>
       </c>
       <c r="R69" t="n">
-        <v>7008383</v>
+        <v>7008397</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9823,9 +9818,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -8749,10 +8749,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424611</v>
+        <v>122426947</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8765,16 +8765,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8782,12 +8782,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8797,10 +8801,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508820</v>
+        <v>508535</v>
       </c>
       <c r="R62" t="n">
-        <v>7008398</v>
+        <v>7008440</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8835,11 +8839,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8851,27 +8850,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8889,10 +8868,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426947</v>
+        <v>122424611</v>
       </c>
       <c r="B63" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8905,16 +8884,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8922,16 +8901,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8941,10 +8916,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508535</v>
+        <v>508820</v>
       </c>
       <c r="R63" t="n">
-        <v>7008440</v>
+        <v>7008398</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8979,6 +8954,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8990,7 +8970,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -8068,7 +8068,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122429281</v>
+        <v>122427586</v>
       </c>
       <c r="B57" t="n">
         <v>57478</v>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>509109</v>
+        <v>508745</v>
       </c>
       <c r="R57" t="n">
-        <v>7008253</v>
+        <v>7008511</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427586</v>
+        <v>122424589</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508745</v>
+        <v>508831</v>
       </c>
       <c r="R58" t="n">
-        <v>7008511</v>
+        <v>7008397</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8318,9 +8318,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8338,10 +8343,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427444</v>
+        <v>122427763</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8354,26 +8359,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8381,10 +8391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508541</v>
+        <v>508776</v>
       </c>
       <c r="R59" t="n">
-        <v>7008422</v>
+        <v>7008533</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8421,7 +8431,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8430,33 +8440,32 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8474,10 +8483,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427681</v>
+        <v>122427444</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8490,31 +8499,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8522,10 +8526,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508760</v>
+        <v>508541</v>
       </c>
       <c r="R60" t="n">
-        <v>7008533</v>
+        <v>7008422</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8562,7 +8566,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8571,32 +8575,33 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8614,7 +8619,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424676</v>
+        <v>122424496</v>
       </c>
       <c r="B61" t="n">
         <v>57478</v>
@@ -8662,10 +8667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508779</v>
+        <v>508891</v>
       </c>
       <c r="R61" t="n">
-        <v>7008383</v>
+        <v>7008386</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8729,9 +8734,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8749,10 +8759,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122426947</v>
+        <v>122424611</v>
       </c>
       <c r="B62" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8765,16 +8775,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8782,16 +8792,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8801,10 +8807,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508535</v>
+        <v>508820</v>
       </c>
       <c r="R62" t="n">
-        <v>7008440</v>
+        <v>7008398</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8839,6 +8845,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8850,7 +8861,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8868,7 +8899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122424611</v>
+        <v>122427681</v>
       </c>
       <c r="B63" t="n">
         <v>57478</v>
@@ -8916,10 +8947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508820</v>
+        <v>508760</v>
       </c>
       <c r="R63" t="n">
-        <v>7008398</v>
+        <v>7008533</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9008,7 +9039,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122426823</v>
+        <v>122424707</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -9056,10 +9087,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508614</v>
+        <v>508781</v>
       </c>
       <c r="R64" t="n">
-        <v>7008464</v>
+        <v>7008382</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9148,10 +9179,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427763</v>
+        <v>122426947</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9164,16 +9195,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9181,12 +9212,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9196,10 +9231,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508776</v>
+        <v>508535</v>
       </c>
       <c r="R65" t="n">
-        <v>7008533</v>
+        <v>7008440</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9234,11 +9269,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9250,27 +9280,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9288,7 +9298,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424707</v>
+        <v>122427127</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -9326,7 +9336,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9336,10 +9346,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508781</v>
+        <v>508631</v>
       </c>
       <c r="R66" t="n">
-        <v>7008382</v>
+        <v>7008480</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9376,7 +9386,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9390,7 +9400,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9403,14 +9413,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9428,7 +9433,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122424496</v>
+        <v>122429281</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -9476,10 +9481,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508891</v>
+        <v>509109</v>
       </c>
       <c r="R67" t="n">
-        <v>7008386</v>
+        <v>7008253</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9543,14 +9548,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122427127</v>
+        <v>122426823</v>
       </c>
       <c r="B68" t="n">
         <v>57478</v>
@@ -9606,7 +9606,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508631</v>
+        <v>508614</v>
       </c>
       <c r="R68" t="n">
-        <v>7008480</v>
+        <v>7008464</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9683,9 +9683,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9703,7 +9708,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424589</v>
+        <v>122424676</v>
       </c>
       <c r="B69" t="n">
         <v>57478</v>
@@ -9751,10 +9756,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508831</v>
+        <v>508779</v>
       </c>
       <c r="R69" t="n">
-        <v>7008397</v>
+        <v>7008383</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9818,14 +9823,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -8203,7 +8203,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424589</v>
+        <v>122427763</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8241,7 +8241,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508831</v>
+        <v>508776</v>
       </c>
       <c r="R58" t="n">
-        <v>7008397</v>
+        <v>7008533</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8343,7 +8343,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427763</v>
+        <v>122424589</v>
       </c>
       <c r="B59" t="n">
         <v>57478</v>
@@ -8381,7 +8381,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508776</v>
+        <v>508831</v>
       </c>
       <c r="R59" t="n">
-        <v>7008533</v>
+        <v>7008397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -8068,7 +8068,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427586</v>
+        <v>122426823</v>
       </c>
       <c r="B57" t="n">
         <v>57478</v>
@@ -8106,7 +8106,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508745</v>
+        <v>508614</v>
       </c>
       <c r="R57" t="n">
-        <v>7008511</v>
+        <v>7008464</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8183,9 +8183,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8203,7 +8208,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427763</v>
+        <v>122424611</v>
       </c>
       <c r="B58" t="n">
         <v>57478</v>
@@ -8241,7 +8246,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508776</v>
+        <v>508820</v>
       </c>
       <c r="R58" t="n">
-        <v>7008533</v>
+        <v>7008398</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8291,7 +8296,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8343,7 +8348,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122424589</v>
+        <v>122427763</v>
       </c>
       <c r="B59" t="n">
         <v>57478</v>
@@ -8381,7 +8386,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8391,10 +8396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508831</v>
+        <v>508776</v>
       </c>
       <c r="R59" t="n">
-        <v>7008397</v>
+        <v>7008533</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8431,7 +8436,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8483,10 +8488,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427444</v>
+        <v>122426947</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8499,26 +8504,35 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8526,10 +8540,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508541</v>
+        <v>508535</v>
       </c>
       <c r="R60" t="n">
-        <v>7008422</v>
+        <v>7008440</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8564,44 +8578,18 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Tallsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8619,7 +8607,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424496</v>
+        <v>122424707</v>
       </c>
       <c r="B61" t="n">
         <v>57478</v>
@@ -8657,7 +8645,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8667,10 +8655,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508891</v>
+        <v>508781</v>
       </c>
       <c r="R61" t="n">
-        <v>7008386</v>
+        <v>7008382</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8707,7 +8695,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8736,12 +8724,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8759,10 +8747,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122424611</v>
+        <v>122427444</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8775,31 +8763,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8807,10 +8790,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508820</v>
+        <v>508541</v>
       </c>
       <c r="R62" t="n">
-        <v>7008398</v>
+        <v>7008422</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8847,7 +8830,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8856,32 +8839,33 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9039,7 +9023,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122424707</v>
+        <v>122429281</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -9077,7 +9061,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -9087,10 +9071,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508781</v>
+        <v>509109</v>
       </c>
       <c r="R64" t="n">
-        <v>7008382</v>
+        <v>7008253</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9127,7 +9111,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9154,14 +9138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9179,10 +9158,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122426947</v>
+        <v>122427127</v>
       </c>
       <c r="B65" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9195,16 +9174,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9212,16 +9191,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -9231,10 +9206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508535</v>
+        <v>508631</v>
       </c>
       <c r="R65" t="n">
-        <v>7008440</v>
+        <v>7008480</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9269,6 +9244,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9280,7 +9260,22 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9298,7 +9293,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427127</v>
+        <v>122424676</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -9346,10 +9341,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508631</v>
+        <v>508779</v>
       </c>
       <c r="R66" t="n">
-        <v>7008480</v>
+        <v>7008383</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9386,7 +9381,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9400,7 +9395,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9433,7 +9428,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429281</v>
+        <v>122427586</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -9481,10 +9476,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509109</v>
+        <v>508745</v>
       </c>
       <c r="R67" t="n">
-        <v>7008253</v>
+        <v>7008511</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9568,7 +9563,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122426823</v>
+        <v>122424496</v>
       </c>
       <c r="B68" t="n">
         <v>57478</v>
@@ -9606,7 +9601,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9616,10 +9611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508614</v>
+        <v>508891</v>
       </c>
       <c r="R68" t="n">
-        <v>7008464</v>
+        <v>7008386</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9656,7 +9651,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9685,12 +9680,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9708,7 +9703,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424676</v>
+        <v>122424589</v>
       </c>
       <c r="B69" t="n">
         <v>57478</v>
@@ -9756,10 +9751,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508779</v>
+        <v>508831</v>
       </c>
       <c r="R69" t="n">
-        <v>7008383</v>
+        <v>7008397</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9823,9 +9818,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>122424637</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -802,19 +797,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122423287</v>
+        <v>122426743</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -838,17 +828,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508887</v>
+        <v>508764</v>
       </c>
       <c r="R3" t="n">
-        <v>7008167</v>
+        <v>7008423</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +870,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +886,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -929,63 +924,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122422838</v>
+        <v>122427142</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508855</v>
+        <v>508688</v>
       </c>
       <c r="R4" t="n">
-        <v>7008046</v>
+        <v>7008395</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,11 +997,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,7 +1008,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1048,12 +1023,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,19 +1046,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122423711</v>
+        <v>122427227</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1111,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509001</v>
+        <v>508639</v>
       </c>
       <c r="R5" t="n">
-        <v>7008256</v>
+        <v>7008388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,17 +1130,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1180,7 +1150,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,64 +1168,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122423626</v>
+        <v>122427444</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508994</v>
+        <v>508541</v>
       </c>
       <c r="R6" t="n">
-        <v>7008252</v>
+        <v>7008422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,7 +1246,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst två individer, möjligen fler.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,12 +1255,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1324,63 +1299,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429239</v>
+        <v>122428118</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508765</v>
+        <v>508595</v>
       </c>
       <c r="R7" t="n">
-        <v>7008466</v>
+        <v>7008516</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1414,7 +1374,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack främst på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1388,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1443,12 +1403,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,55 +1426,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122426951</v>
+        <v>122428174</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508719</v>
+        <v>508570</v>
       </c>
       <c r="R8" t="n">
-        <v>7008377</v>
+        <v>7008514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,11 +1499,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1565,7 +1510,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1580,12 +1525,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,63 +1548,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122423133</v>
+        <v>122429024</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508834</v>
+        <v>508746</v>
       </c>
       <c r="R9" t="n">
-        <v>7008117</v>
+        <v>7008449</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1691,11 +1621,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1722,12 +1647,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1745,19 +1670,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122426743</v>
+        <v>122429398</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1785,10 +1705,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508764</v>
+        <v>508809</v>
       </c>
       <c r="R10" t="n">
-        <v>7008423</v>
+        <v>7008468</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,11 +1743,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1854,12 +1769,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1877,32 +1792,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122423040</v>
+        <v>122424772</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1923,17 +1833,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508845</v>
+        <v>508770</v>
       </c>
       <c r="R11" t="n">
-        <v>7008072</v>
+        <v>7008381</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1967,7 +1877,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,50 +1929,55 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122423988</v>
+        <v>122426582</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508982</v>
+        <v>508771</v>
       </c>
       <c r="R12" t="n">
-        <v>7008301</v>
+        <v>7008433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2097,6 +2012,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2123,12 +2043,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2146,15 +2066,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122427227</v>
+        <v>122422846</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,34 +2077,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508639</v>
+        <v>508853</v>
       </c>
       <c r="R13" t="n">
-        <v>7008388</v>
+        <v>7008030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2224,6 +2149,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2235,27 +2165,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2273,15 +2203,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122423467</v>
+        <v>122422848</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,37 +2214,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508900</v>
+        <v>508847</v>
       </c>
       <c r="R14" t="n">
-        <v>7008203</v>
+        <v>7008039</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2351,6 +2284,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2362,7 +2300,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2377,12 +2315,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2400,15 +2338,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122430904</v>
+        <v>122423040</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2416,37 +2349,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508916</v>
+        <v>508845</v>
       </c>
       <c r="R15" t="n">
-        <v>7008122</v>
+        <v>7008072</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2476,6 +2419,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack uppskattningsvis skapade inom 5 - 10 år tillbaks.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2527,15 +2475,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122422959</v>
+        <v>122423113</v>
       </c>
       <c r="B16" t="n">
-        <v>90958</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2543,27 +2486,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2572,13 +2520,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508833</v>
+        <v>508834</v>
       </c>
       <c r="R16" t="n">
-        <v>7008097</v>
+        <v>7008115</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2610,6 +2558,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2574,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2636,12 +2589,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2659,15 +2612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122424308</v>
+        <v>122423133</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,37 +2623,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508903</v>
+        <v>508834</v>
       </c>
       <c r="R17" t="n">
-        <v>7008351</v>
+        <v>7008117</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,7 +2697,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka färska ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2768,12 +2726,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2791,15 +2749,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122424772</v>
+        <v>122424589</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2807,16 +2760,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2825,26 +2778,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508770</v>
+        <v>508831</v>
       </c>
       <c r="R18" t="n">
-        <v>7008381</v>
+        <v>7008397</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2881,7 +2832,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2933,15 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429268</v>
+        <v>122424611</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,26 +2913,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508765</v>
+        <v>508820</v>
       </c>
       <c r="R19" t="n">
-        <v>7008461</v>
+        <v>7008398</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3023,7 +2967,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3075,15 +3019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122426582</v>
+        <v>122424676</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3091,16 +3030,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3109,26 +3048,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508771</v>
+        <v>508779</v>
       </c>
       <c r="R20" t="n">
-        <v>7008433</v>
+        <v>7008383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3165,7 +3102,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3192,14 +3129,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3217,15 +3149,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122424114</v>
+        <v>122424707</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3233,34 +3160,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508968</v>
+        <v>508781</v>
       </c>
       <c r="R21" t="n">
-        <v>7008319</v>
+        <v>7008382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3297,7 +3232,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3326,12 +3261,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3349,15 +3284,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427142</v>
+        <v>122426823</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3365,34 +3295,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508688</v>
+        <v>508614</v>
       </c>
       <c r="R22" t="n">
-        <v>7008395</v>
+        <v>7008464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3427,6 +3365,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3438,7 +3381,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3453,12 +3396,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3476,15 +3419,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122423811</v>
+        <v>122426951</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3515,21 +3453,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508995</v>
+        <v>508719</v>
       </c>
       <c r="R23" t="n">
-        <v>7008282</v>
+        <v>7008377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3566,7 +3499,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,12 +3528,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3618,15 +3551,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122424389</v>
+        <v>122427127</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3652,24 +3580,27 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>508892</v>
+        <v>508631</v>
       </c>
       <c r="R24" t="n">
-        <v>7008349</v>
+        <v>7008480</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3703,7 +3634,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack äldre.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3717,7 +3648,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3730,14 +3661,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3755,15 +3681,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122423113</v>
+        <v>122427586</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3789,29 +3710,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508834</v>
+        <v>508745</v>
       </c>
       <c r="R25" t="n">
-        <v>7008115</v>
+        <v>7008511</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3845,7 +3764,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3872,14 +3791,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3897,15 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429024</v>
+        <v>122427681</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3913,37 +3822,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508746</v>
+        <v>508760</v>
       </c>
       <c r="R26" t="n">
-        <v>7008449</v>
+        <v>7008533</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3975,6 +3892,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4001,12 +3923,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4024,15 +3946,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122423935</v>
+        <v>122427763</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4058,26 +3975,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508980</v>
+        <v>508776</v>
       </c>
       <c r="R27" t="n">
-        <v>7008294</v>
+        <v>7008533</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4114,7 +4029,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack, färska och äldre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4169,12 +4084,7 @@
         <v>122428937</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4303,15 +4213,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122429398</v>
+        <v>122429239</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4319,37 +4224,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508809</v>
+        <v>508765</v>
       </c>
       <c r="R29" t="n">
-        <v>7008468</v>
+        <v>7008466</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4381,6 +4296,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack främst på stambasen.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4407,12 +4327,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4430,15 +4350,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122423588</v>
+        <v>122429268</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4446,34 +4361,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508975</v>
+        <v>508765</v>
       </c>
       <c r="R30" t="n">
-        <v>7008243</v>
+        <v>7008461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4508,6 +4433,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4534,12 +4464,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4557,15 +4487,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122427629</v>
+        <v>122426947</v>
       </c>
       <c r="B31" t="n">
-        <v>97301</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4573,47 +4498,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508574</v>
+        <v>508535</v>
       </c>
       <c r="R31" t="n">
-        <v>7008461</v>
+        <v>7008440</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4656,7 +4583,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4674,50 +4601,55 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122423191</v>
+        <v>122427629</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508859</v>
+        <v>508574</v>
       </c>
       <c r="R32" t="n">
-        <v>7008134</v>
+        <v>7008461</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4764,26 +4696,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4801,15 +4713,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122428118</v>
+        <v>122429607</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,37 +4724,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508595</v>
+        <v>509034</v>
       </c>
       <c r="R33" t="n">
-        <v>7008516</v>
+        <v>7008306</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4879,23 +4789,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4908,14 +4814,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4933,61 +4834,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122423524</v>
+        <v>122423191</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>508928</v>
+        <v>508859</v>
       </c>
       <c r="R34" t="n">
-        <v>7008172</v>
+        <v>7008134</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5019,11 +4907,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5040,22 +4923,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5073,60 +4956,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122424304</v>
+        <v>122423287</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508904</v>
+        <v>508887</v>
       </c>
       <c r="R35" t="n">
-        <v>7008325</v>
+        <v>7008167</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5164,33 +5035,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5208,61 +5078,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122422848</v>
+        <v>122423467</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508847</v>
+        <v>508900</v>
       </c>
       <c r="R36" t="n">
-        <v>7008039</v>
+        <v>7008203</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5294,11 +5151,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5310,7 +5162,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5325,12 +5177,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5348,53 +5200,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429607</v>
+        <v>122423588</v>
       </c>
       <c r="B37" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509034</v>
+        <v>508975</v>
       </c>
       <c r="R37" t="n">
-        <v>7008306</v>
+        <v>7008243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5435,7 +5279,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5454,9 +5297,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5474,58 +5322,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122423202</v>
+        <v>122423711</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508881</v>
+        <v>509001</v>
       </c>
       <c r="R38" t="n">
-        <v>7008130</v>
+        <v>7008256</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5560,11 +5395,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5591,12 +5421,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5614,58 +5444,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122424453</v>
+        <v>122423988</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508908</v>
+        <v>508982</v>
       </c>
       <c r="R39" t="n">
-        <v>7008354</v>
+        <v>7008301</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5700,11 +5517,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5731,12 +5543,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5754,58 +5566,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430707</v>
+        <v>122424114</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>508959</v>
+        <v>508968</v>
       </c>
       <c r="R40" t="n">
-        <v>7008280</v>
+        <v>7008319</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5842,7 +5641,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5871,12 +5670,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5894,69 +5693,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122430040</v>
+        <v>122424308</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508930</v>
+        <v>508903</v>
       </c>
       <c r="R41" t="n">
-        <v>7008316</v>
+        <v>7008351</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5988,6 +5766,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -6000,6 +5783,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6017,58 +5820,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122428923</v>
+        <v>122430904</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>508978</v>
+        <v>508916</v>
       </c>
       <c r="R42" t="n">
-        <v>7008270</v>
+        <v>7008122</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6101,11 +5891,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6157,15 +5942,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122423979</v>
+        <v>122424304</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6173,50 +5953,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508958</v>
+        <v>508904</v>
       </c>
       <c r="R43" t="n">
-        <v>7008338</v>
+        <v>7008325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6257,12 +6028,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6280,37 +6072,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122428487</v>
+        <v>122428462</v>
       </c>
       <c r="B44" t="n">
-        <v>79883</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6323,10 +6110,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509041</v>
+        <v>509040</v>
       </c>
       <c r="R44" t="n">
-        <v>7008337</v>
+        <v>7008336</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6414,12 +6201,7 @@
         <v>122428777</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6546,15 +6328,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122423808</v>
+        <v>122429210</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6562,31 +6339,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6594,10 +6366,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>508966</v>
+        <v>509071</v>
       </c>
       <c r="R46" t="n">
-        <v>7008356</v>
+        <v>7008310</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6634,7 +6406,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6643,6 +6415,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6661,14 +6434,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6686,47 +6454,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429553</v>
+        <v>122428487</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6734,10 +6492,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509048</v>
+        <v>509041</v>
       </c>
       <c r="R47" t="n">
-        <v>7008315</v>
+        <v>7008337</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6772,17 +6530,13 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6793,22 +6547,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6826,15 +6580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122430628</v>
+        <v>122422838</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6860,27 +6609,29 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>508965</v>
+        <v>508855</v>
       </c>
       <c r="R48" t="n">
-        <v>7008296</v>
+        <v>7008046</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6914,7 +6665,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6966,15 +6717,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122429210</v>
+        <v>122423202</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6982,37 +6728,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>509071</v>
+        <v>508881</v>
       </c>
       <c r="R49" t="n">
-        <v>7008310</v>
+        <v>7008130</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7049,7 +6800,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7058,7 +6809,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7077,9 +6827,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7097,15 +6852,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122424126</v>
+        <v>122423484</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7141,14 +6891,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508950</v>
+        <v>508920</v>
       </c>
       <c r="R50" t="n">
-        <v>7008334</v>
+        <v>7008181</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7185,7 +6935,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7199,17 +6949,17 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -7219,7 +6969,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7237,15 +6987,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122429949</v>
+        <v>122423524</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7281,14 +7026,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sandudden, Sandudden, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508963</v>
+        <v>508928</v>
       </c>
       <c r="R51" t="n">
-        <v>7008307</v>
+        <v>7008172</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7325,7 +7070,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7339,17 +7084,17 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -7359,7 +7104,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7377,15 +7122,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122428831</v>
+        <v>122423808</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7425,10 +7165,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508914</v>
+        <v>508966</v>
       </c>
       <c r="R52" t="n">
-        <v>7008313</v>
+        <v>7008356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7517,15 +7257,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428725</v>
+        <v>122423811</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7551,24 +7286,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508919</v>
+        <v>508995</v>
       </c>
       <c r="R53" t="n">
-        <v>7008295</v>
+        <v>7008282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7605,7 +7342,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Äldre ringhack med tydliga kådaflöden.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7657,15 +7394,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122423484</v>
+        <v>122423935</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7691,24 +7423,26 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508920</v>
+        <v>508980</v>
       </c>
       <c r="R54" t="n">
-        <v>7008181</v>
+        <v>7008294</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7745,7 +7479,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7759,17 +7493,17 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -7779,7 +7513,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7797,15 +7531,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428462</v>
+        <v>122424038</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7813,26 +7542,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7840,7 +7574,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>509040</v>
+        <v>508954</v>
       </c>
       <c r="R55" t="n">
         <v>7008336</v>
@@ -7878,13 +7612,17 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7895,22 +7633,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7928,15 +7666,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122424038</v>
+        <v>122424126</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7976,10 +7709,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508954</v>
+        <v>508950</v>
       </c>
       <c r="R56" t="n">
-        <v>7008336</v>
+        <v>7008334</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8068,15 +7801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122426823</v>
+        <v>122424389</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8102,27 +7830,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>508614</v>
+        <v>508892</v>
       </c>
       <c r="R57" t="n">
-        <v>7008464</v>
+        <v>7008349</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8156,7 +7881,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8208,15 +7933,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122424611</v>
+        <v>122424453</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8256,10 +7976,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508820</v>
+        <v>508908</v>
       </c>
       <c r="R58" t="n">
-        <v>7008398</v>
+        <v>7008354</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8348,15 +8068,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427763</v>
+        <v>122424496</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8386,7 +8101,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8396,10 +8111,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>508776</v>
+        <v>508891</v>
       </c>
       <c r="R59" t="n">
-        <v>7008533</v>
+        <v>7008386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8436,7 +8151,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8465,12 +8180,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8488,15 +8203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122426947</v>
+        <v>122428725</v>
       </c>
       <c r="B60" t="n">
-        <v>56680</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8504,16 +8214,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8521,16 +8231,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8540,10 +8246,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508535</v>
+        <v>508919</v>
       </c>
       <c r="R60" t="n">
-        <v>7008440</v>
+        <v>7008295</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8578,6 +8284,11 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8589,7 +8300,27 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8607,15 +8338,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122424707</v>
+        <v>122428831</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8645,7 +8371,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8655,10 +8381,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508781</v>
+        <v>508914</v>
       </c>
       <c r="R61" t="n">
-        <v>7008382</v>
+        <v>7008313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8695,7 +8421,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8747,15 +8473,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427444</v>
+        <v>122428923</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8763,26 +8484,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8790,10 +8516,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>508541</v>
+        <v>508978</v>
       </c>
       <c r="R62" t="n">
-        <v>7008422</v>
+        <v>7008270</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8830,7 +8556,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8839,33 +8565,32 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Tallsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8883,15 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122427681</v>
+        <v>122429281</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8931,10 +8651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>508760</v>
+        <v>509109</v>
       </c>
       <c r="R63" t="n">
-        <v>7008533</v>
+        <v>7008253</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8998,14 +8718,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9023,15 +8738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122429281</v>
+        <v>122429553</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9071,10 +8781,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>509109</v>
+        <v>509048</v>
       </c>
       <c r="R64" t="n">
-        <v>7008253</v>
+        <v>7008315</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9138,9 +8848,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9158,15 +8873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427127</v>
+        <v>122429949</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9206,10 +8916,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508631</v>
+        <v>508963</v>
       </c>
       <c r="R65" t="n">
-        <v>7008480</v>
+        <v>7008307</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9246,7 +8956,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9260,7 +8970,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -9273,9 +8983,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9293,15 +9008,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122424676</v>
+        <v>122430628</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9341,10 +9051,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508779</v>
+        <v>508965</v>
       </c>
       <c r="R66" t="n">
-        <v>7008383</v>
+        <v>7008296</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9408,9 +9118,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9428,15 +9143,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427586</v>
+        <v>122430707</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9476,10 +9186,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508745</v>
+        <v>508959</v>
       </c>
       <c r="R67" t="n">
-        <v>7008511</v>
+        <v>7008280</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9543,9 +9253,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9563,15 +9278,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122424496</v>
+        <v>122423626</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9579,42 +9289,48 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>508891</v>
+        <v>508994</v>
       </c>
       <c r="R68" t="n">
-        <v>7008386</v>
+        <v>7008252</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9651,7 +9367,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Minst två individer, möjligen fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9666,26 +9382,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9703,15 +9399,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122424589</v>
+        <v>122423979</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9719,42 +9410,50 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandudden, Sandudden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508831</v>
+        <v>508958</v>
       </c>
       <c r="R69" t="n">
-        <v>7008397</v>
+        <v>7008338</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9789,11 +9488,6 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9806,26 +9500,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9840,6 +9514,124 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122430040</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sandudden, Sandudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>508930</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7008316</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61766-2024 artfynd.xlsx
+++ b/artfynd/A 61766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429607</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423191</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423467</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1281,6 +1306,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1403,6 +1433,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423711</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1525,6 +1560,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1652,6 +1692,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424114</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1779,6 +1824,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424308</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1901,6 +1951,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424637</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2028,6 +2083,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122426743</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2150,6 +2210,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427142</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2272,6 +2337,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427227</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2403,6 +2473,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427444</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2530,6 +2605,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428118</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2652,6 +2732,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2774,6 +2859,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2896,6 +2986,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429398</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3018,6 +3113,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122430904</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3148,6 +3248,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424304</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3274,6 +3379,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428462</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3404,6 +3514,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428777</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3530,6 +3645,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429210</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3656,6 +3776,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428487</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3793,6 +3918,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424772</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3930,6 +4060,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122426582</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4067,6 +4202,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122422838</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4204,6 +4344,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122422846</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4339,6 +4484,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122422848</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4476,6 +4626,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423040</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4613,6 +4768,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423113</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4750,6 +4910,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423133</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4885,6 +5050,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423202</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5020,6 +5190,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423484</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5155,6 +5330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423524</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5290,6 +5470,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423808</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5427,6 +5612,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423811</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5564,6 +5754,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423935</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5699,6 +5894,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5834,6 +6034,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424126</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5966,6 +6171,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424389</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6101,6 +6311,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424453</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6236,6 +6451,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424496</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6371,6 +6591,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424589</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6506,6 +6731,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424611</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6636,6 +6866,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424676</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6771,6 +7006,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424707</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6906,6 +7146,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122426823</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7038,6 +7283,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122426951</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7168,6 +7418,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427127</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7298,6 +7553,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427586</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7433,6 +7693,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427681</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7568,6 +7833,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427763</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7703,6 +7973,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428725</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7838,6 +8113,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428831</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7973,6 +8253,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428923</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8105,6 +8390,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122428937</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8242,6 +8532,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429239</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8379,6 +8674,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429268</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8509,6 +8809,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429281</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8644,6 +8949,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429553</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8779,6 +9089,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122429949</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8914,6 +9229,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122430628</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9049,6 +9369,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122430707</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9163,6 +9488,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122426947</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9284,6 +9614,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423626</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9402,6 +9737,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122423979</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9520,6 +9860,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122430040</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9632,8 +9977,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122427629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/200